--- a/reports/appium/appium-test-results.xlsx
+++ b/reports/appium/appium-test-results.xlsx
@@ -30,7 +30,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/27/2026, 8:23:08 AM</t>
+    <t>7/27/2026, 8:28:29 AM</t>
   </si>
   <si>
     <t>Total Tests Executed</t>
@@ -3930,7 +3930,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>14153</v>
+        <v>13878</v>
       </c>
     </row>
   </sheetData>
@@ -4198,7 +4198,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
@@ -4215,7 +4215,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
@@ -4232,7 +4232,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -4249,7 +4249,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -4266,7 +4266,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -4283,7 +4283,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -4300,7 +4300,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -4317,7 +4317,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -4334,7 +4334,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -4351,7 +4351,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -4368,7 +4368,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -4385,7 +4385,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -4402,7 +4402,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -4419,7 +4419,7 @@
         <v>32</v>
       </c>
       <c r="D15" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>33</v>
@@ -4436,7 +4436,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -4453,7 +4453,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -4470,7 +4470,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -4487,7 +4487,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -4504,7 +4504,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>33</v>
@@ -4521,7 +4521,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>33</v>
@@ -4538,7 +4538,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>33</v>
@@ -4555,7 +4555,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>33</v>
@@ -4572,7 +4572,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>33</v>
@@ -4589,7 +4589,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>33</v>
@@ -4606,7 +4606,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>33</v>
@@ -4623,7 +4623,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>33</v>
@@ -4640,7 +4640,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>33</v>
@@ -4657,7 +4657,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>33</v>
@@ -4674,7 +4674,7 @@
         <v>32</v>
       </c>
       <c r="D30" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>33</v>
@@ -4691,7 +4691,7 @@
         <v>32</v>
       </c>
       <c r="D31" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>33</v>
@@ -4708,7 +4708,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>33</v>
@@ -4725,7 +4725,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>33</v>
@@ -4742,7 +4742,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>33</v>
@@ -4776,7 +4776,7 @@
         <v>32</v>
       </c>
       <c r="D36" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>33</v>
@@ -4793,7 +4793,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>33</v>
@@ -4810,7 +4810,7 @@
         <v>32</v>
       </c>
       <c r="D38" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>33</v>
@@ -4827,7 +4827,7 @@
         <v>32</v>
       </c>
       <c r="D39" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>33</v>
@@ -4844,7 +4844,7 @@
         <v>32</v>
       </c>
       <c r="D40" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>33</v>
@@ -4861,7 +4861,7 @@
         <v>32</v>
       </c>
       <c r="D41" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>33</v>
@@ -4878,7 +4878,7 @@
         <v>32</v>
       </c>
       <c r="D42" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>33</v>
@@ -4895,7 +4895,7 @@
         <v>32</v>
       </c>
       <c r="D43" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>33</v>
@@ -4912,7 +4912,7 @@
         <v>32</v>
       </c>
       <c r="D44" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>33</v>
@@ -4929,7 +4929,7 @@
         <v>32</v>
       </c>
       <c r="D45" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>33</v>
@@ -4946,7 +4946,7 @@
         <v>32</v>
       </c>
       <c r="D46" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>33</v>
@@ -4963,7 +4963,7 @@
         <v>32</v>
       </c>
       <c r="D47" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>33</v>
@@ -4980,7 +4980,7 @@
         <v>32</v>
       </c>
       <c r="D48" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>33</v>
@@ -4997,7 +4997,7 @@
         <v>32</v>
       </c>
       <c r="D49" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>33</v>
@@ -5014,7 +5014,7 @@
         <v>32</v>
       </c>
       <c r="D50" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>33</v>
@@ -5031,7 +5031,7 @@
         <v>32</v>
       </c>
       <c r="D51" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>33</v>
@@ -5048,7 +5048,7 @@
         <v>32</v>
       </c>
       <c r="D52" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>33</v>
@@ -5065,7 +5065,7 @@
         <v>32</v>
       </c>
       <c r="D53" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>33</v>
@@ -5082,7 +5082,7 @@
         <v>32</v>
       </c>
       <c r="D54" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>33</v>
@@ -5099,7 +5099,7 @@
         <v>32</v>
       </c>
       <c r="D55" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>33</v>
@@ -5116,7 +5116,7 @@
         <v>32</v>
       </c>
       <c r="D56" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>33</v>
@@ -5133,7 +5133,7 @@
         <v>32</v>
       </c>
       <c r="D57" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>33</v>
@@ -5150,7 +5150,7 @@
         <v>32</v>
       </c>
       <c r="D58" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>33</v>
@@ -5167,7 +5167,7 @@
         <v>32</v>
       </c>
       <c r="D59" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>33</v>
@@ -5184,7 +5184,7 @@
         <v>32</v>
       </c>
       <c r="D60" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>33</v>
@@ -5201,7 +5201,7 @@
         <v>32</v>
       </c>
       <c r="D61" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>33</v>
@@ -5218,7 +5218,7 @@
         <v>32</v>
       </c>
       <c r="D62" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>33</v>
@@ -5235,7 +5235,7 @@
         <v>32</v>
       </c>
       <c r="D63" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>33</v>
@@ -5252,7 +5252,7 @@
         <v>32</v>
       </c>
       <c r="D64" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>33</v>
@@ -5269,7 +5269,7 @@
         <v>32</v>
       </c>
       <c r="D65" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>33</v>
@@ -5286,7 +5286,7 @@
         <v>32</v>
       </c>
       <c r="D66" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>33</v>
@@ -5303,7 +5303,7 @@
         <v>32</v>
       </c>
       <c r="D67" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>33</v>
@@ -5320,7 +5320,7 @@
         <v>32</v>
       </c>
       <c r="D68" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>33</v>
@@ -5337,7 +5337,7 @@
         <v>32</v>
       </c>
       <c r="D69" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>33</v>
@@ -5354,7 +5354,7 @@
         <v>32</v>
       </c>
       <c r="D70" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>33</v>
@@ -5371,7 +5371,7 @@
         <v>32</v>
       </c>
       <c r="D71" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>33</v>
@@ -5422,7 +5422,7 @@
         <v>32</v>
       </c>
       <c r="D74" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>33</v>
@@ -5439,7 +5439,7 @@
         <v>32</v>
       </c>
       <c r="D75" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>33</v>
@@ -5456,7 +5456,7 @@
         <v>32</v>
       </c>
       <c r="D76" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>33</v>
@@ -5473,7 +5473,7 @@
         <v>32</v>
       </c>
       <c r="D77" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>33</v>
@@ -5490,7 +5490,7 @@
         <v>32</v>
       </c>
       <c r="D78" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>33</v>
@@ -5507,7 +5507,7 @@
         <v>32</v>
       </c>
       <c r="D79" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>33</v>
@@ -5524,7 +5524,7 @@
         <v>32</v>
       </c>
       <c r="D80" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>33</v>
@@ -5541,7 +5541,7 @@
         <v>32</v>
       </c>
       <c r="D81" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>33</v>
@@ -5558,7 +5558,7 @@
         <v>32</v>
       </c>
       <c r="D82" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>33</v>
@@ -5575,7 +5575,7 @@
         <v>32</v>
       </c>
       <c r="D83" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>33</v>
@@ -5592,7 +5592,7 @@
         <v>32</v>
       </c>
       <c r="D84" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>33</v>
@@ -5609,7 +5609,7 @@
         <v>32</v>
       </c>
       <c r="D85" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>33</v>
@@ -5626,7 +5626,7 @@
         <v>32</v>
       </c>
       <c r="D86" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>33</v>
@@ -5643,7 +5643,7 @@
         <v>32</v>
       </c>
       <c r="D87" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>33</v>
@@ -5660,7 +5660,7 @@
         <v>32</v>
       </c>
       <c r="D88" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>33</v>
@@ -5677,7 +5677,7 @@
         <v>32</v>
       </c>
       <c r="D89" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>33</v>
@@ -5694,7 +5694,7 @@
         <v>32</v>
       </c>
       <c r="D90" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>33</v>
@@ -5711,7 +5711,7 @@
         <v>32</v>
       </c>
       <c r="D91" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>33</v>
@@ -5728,7 +5728,7 @@
         <v>32</v>
       </c>
       <c r="D92" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>33</v>
@@ -5745,7 +5745,7 @@
         <v>32</v>
       </c>
       <c r="D93" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>33</v>
@@ -5762,7 +5762,7 @@
         <v>32</v>
       </c>
       <c r="D94" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>33</v>
@@ -5779,7 +5779,7 @@
         <v>32</v>
       </c>
       <c r="D95" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>33</v>
@@ -5796,7 +5796,7 @@
         <v>32</v>
       </c>
       <c r="D96" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>33</v>
@@ -5813,7 +5813,7 @@
         <v>32</v>
       </c>
       <c r="D97" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>33</v>
@@ -5830,7 +5830,7 @@
         <v>32</v>
       </c>
       <c r="D98" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>33</v>
@@ -5847,7 +5847,7 @@
         <v>32</v>
       </c>
       <c r="D99" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>33</v>
@@ -5864,7 +5864,7 @@
         <v>32</v>
       </c>
       <c r="D100" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>33</v>
@@ -5881,7 +5881,7 @@
         <v>32</v>
       </c>
       <c r="D101" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>33</v>
@@ -5898,7 +5898,7 @@
         <v>32</v>
       </c>
       <c r="D102" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>33</v>
@@ -5915,7 +5915,7 @@
         <v>32</v>
       </c>
       <c r="D103" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>33</v>
@@ -5932,7 +5932,7 @@
         <v>32</v>
       </c>
       <c r="D104" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>33</v>
@@ -5949,7 +5949,7 @@
         <v>32</v>
       </c>
       <c r="D105" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>33</v>
@@ -5966,7 +5966,7 @@
         <v>32</v>
       </c>
       <c r="D106" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>33</v>
@@ -5983,7 +5983,7 @@
         <v>32</v>
       </c>
       <c r="D107" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>32</v>
       </c>
       <c r="D108" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>33</v>
@@ -6017,7 +6017,7 @@
         <v>32</v>
       </c>
       <c r="D109" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>33</v>
@@ -6034,7 +6034,7 @@
         <v>32</v>
       </c>
       <c r="D110" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>33</v>
@@ -6051,7 +6051,7 @@
         <v>32</v>
       </c>
       <c r="D111" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>33</v>
@@ -6068,7 +6068,7 @@
         <v>32</v>
       </c>
       <c r="D112" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>33</v>
@@ -6085,7 +6085,7 @@
         <v>32</v>
       </c>
       <c r="D113" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>33</v>
@@ -6102,7 +6102,7 @@
         <v>32</v>
       </c>
       <c r="D114" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>33</v>
@@ -6119,7 +6119,7 @@
         <v>32</v>
       </c>
       <c r="D115" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>33</v>
@@ -6136,7 +6136,7 @@
         <v>32</v>
       </c>
       <c r="D116" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>33</v>
@@ -6153,7 +6153,7 @@
         <v>32</v>
       </c>
       <c r="D117" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>33</v>
@@ -6170,7 +6170,7 @@
         <v>32</v>
       </c>
       <c r="D118" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>33</v>
@@ -6187,7 +6187,7 @@
         <v>32</v>
       </c>
       <c r="D119" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>33</v>
@@ -6204,7 +6204,7 @@
         <v>32</v>
       </c>
       <c r="D120" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>33</v>
@@ -6221,7 +6221,7 @@
         <v>32</v>
       </c>
       <c r="D121" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>33</v>
@@ -6238,7 +6238,7 @@
         <v>32</v>
       </c>
       <c r="D122" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>33</v>
@@ -6255,7 +6255,7 @@
         <v>32</v>
       </c>
       <c r="D123" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>33</v>
@@ -6272,7 +6272,7 @@
         <v>32</v>
       </c>
       <c r="D124" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>33</v>
@@ -6289,7 +6289,7 @@
         <v>32</v>
       </c>
       <c r="D125" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>33</v>
@@ -6306,7 +6306,7 @@
         <v>32</v>
       </c>
       <c r="D126" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>33</v>
@@ -6323,7 +6323,7 @@
         <v>32</v>
       </c>
       <c r="D127" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>33</v>
@@ -6340,7 +6340,7 @@
         <v>32</v>
       </c>
       <c r="D128" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>33</v>
@@ -6357,7 +6357,7 @@
         <v>32</v>
       </c>
       <c r="D129" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>33</v>
@@ -6374,7 +6374,7 @@
         <v>32</v>
       </c>
       <c r="D130" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>33</v>
@@ -6391,7 +6391,7 @@
         <v>32</v>
       </c>
       <c r="D131" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>33</v>
@@ -6408,7 +6408,7 @@
         <v>32</v>
       </c>
       <c r="D132" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>33</v>
@@ -6425,7 +6425,7 @@
         <v>32</v>
       </c>
       <c r="D133" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>33</v>
@@ -6442,7 +6442,7 @@
         <v>32</v>
       </c>
       <c r="D134" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>33</v>
@@ -6459,7 +6459,7 @@
         <v>32</v>
       </c>
       <c r="D135" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>33</v>
@@ -6476,7 +6476,7 @@
         <v>32</v>
       </c>
       <c r="D136" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>33</v>
@@ -6493,7 +6493,7 @@
         <v>32</v>
       </c>
       <c r="D137" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>33</v>
@@ -6510,7 +6510,7 @@
         <v>32</v>
       </c>
       <c r="D138" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>33</v>
@@ -6527,7 +6527,7 @@
         <v>32</v>
       </c>
       <c r="D139" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>33</v>
@@ -6544,7 +6544,7 @@
         <v>32</v>
       </c>
       <c r="D140" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>33</v>
@@ -6561,7 +6561,7 @@
         <v>32</v>
       </c>
       <c r="D141" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>33</v>
@@ -6578,7 +6578,7 @@
         <v>32</v>
       </c>
       <c r="D142" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>33</v>
@@ -6595,7 +6595,7 @@
         <v>32</v>
       </c>
       <c r="D143" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>33</v>
@@ -6612,7 +6612,7 @@
         <v>32</v>
       </c>
       <c r="D144" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>33</v>
@@ -6629,7 +6629,7 @@
         <v>32</v>
       </c>
       <c r="D145" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>33</v>
@@ -6646,7 +6646,7 @@
         <v>32</v>
       </c>
       <c r="D146" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>33</v>
@@ -6663,7 +6663,7 @@
         <v>32</v>
       </c>
       <c r="D147" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>33</v>
@@ -6680,7 +6680,7 @@
         <v>32</v>
       </c>
       <c r="D148" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>33</v>
@@ -6697,7 +6697,7 @@
         <v>32</v>
       </c>
       <c r="D149" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>33</v>
@@ -6714,7 +6714,7 @@
         <v>32</v>
       </c>
       <c r="D150" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>33</v>
@@ -6731,7 +6731,7 @@
         <v>32</v>
       </c>
       <c r="D151" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>33</v>
@@ -6748,7 +6748,7 @@
         <v>32</v>
       </c>
       <c r="D152" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>33</v>
@@ -6765,7 +6765,7 @@
         <v>32</v>
       </c>
       <c r="D153" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>33</v>
@@ -6782,7 +6782,7 @@
         <v>32</v>
       </c>
       <c r="D154" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>33</v>
@@ -6799,7 +6799,7 @@
         <v>32</v>
       </c>
       <c r="D155" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>33</v>
@@ -6816,7 +6816,7 @@
         <v>32</v>
       </c>
       <c r="D156" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>33</v>
@@ -6833,7 +6833,7 @@
         <v>32</v>
       </c>
       <c r="D157" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>33</v>
@@ -6850,7 +6850,7 @@
         <v>32</v>
       </c>
       <c r="D158" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>33</v>
@@ -6867,7 +6867,7 @@
         <v>32</v>
       </c>
       <c r="D159" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>33</v>
@@ -6884,7 +6884,7 @@
         <v>32</v>
       </c>
       <c r="D160" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>33</v>
@@ -6901,7 +6901,7 @@
         <v>32</v>
       </c>
       <c r="D161" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>33</v>
@@ -6918,7 +6918,7 @@
         <v>32</v>
       </c>
       <c r="D162" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>33</v>
@@ -6935,7 +6935,7 @@
         <v>32</v>
       </c>
       <c r="D163" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>33</v>
@@ -6952,7 +6952,7 @@
         <v>32</v>
       </c>
       <c r="D164" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>33</v>
@@ -6969,7 +6969,7 @@
         <v>32</v>
       </c>
       <c r="D165" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>33</v>
@@ -6986,7 +6986,7 @@
         <v>32</v>
       </c>
       <c r="D166" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>33</v>
@@ -7003,7 +7003,7 @@
         <v>32</v>
       </c>
       <c r="D167" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>33</v>
@@ -7020,7 +7020,7 @@
         <v>32</v>
       </c>
       <c r="D168" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>33</v>
@@ -7037,7 +7037,7 @@
         <v>32</v>
       </c>
       <c r="D169" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>33</v>
@@ -7054,7 +7054,7 @@
         <v>32</v>
       </c>
       <c r="D170" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>33</v>
@@ -7071,7 +7071,7 @@
         <v>32</v>
       </c>
       <c r="D171" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>33</v>
@@ -7088,7 +7088,7 @@
         <v>32</v>
       </c>
       <c r="D172" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>33</v>
@@ -7105,7 +7105,7 @@
         <v>32</v>
       </c>
       <c r="D173" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>33</v>
@@ -7139,7 +7139,7 @@
         <v>32</v>
       </c>
       <c r="D175" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>33</v>
@@ -7156,7 +7156,7 @@
         <v>32</v>
       </c>
       <c r="D176" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>33</v>
@@ -7190,7 +7190,7 @@
         <v>32</v>
       </c>
       <c r="D178" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>33</v>
@@ -7207,7 +7207,7 @@
         <v>32</v>
       </c>
       <c r="D179" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>33</v>
@@ -7224,7 +7224,7 @@
         <v>32</v>
       </c>
       <c r="D180" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>33</v>
@@ -7241,7 +7241,7 @@
         <v>32</v>
       </c>
       <c r="D181" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>33</v>
@@ -7258,7 +7258,7 @@
         <v>32</v>
       </c>
       <c r="D182" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>33</v>
@@ -7275,7 +7275,7 @@
         <v>32</v>
       </c>
       <c r="D183" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>33</v>
@@ -7292,7 +7292,7 @@
         <v>32</v>
       </c>
       <c r="D184" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>33</v>
@@ -7309,7 +7309,7 @@
         <v>32</v>
       </c>
       <c r="D185" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>33</v>
@@ -7326,7 +7326,7 @@
         <v>32</v>
       </c>
       <c r="D186" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>33</v>
@@ -7343,7 +7343,7 @@
         <v>32</v>
       </c>
       <c r="D187" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>33</v>
@@ -7360,7 +7360,7 @@
         <v>32</v>
       </c>
       <c r="D188" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>33</v>
@@ -7377,7 +7377,7 @@
         <v>32</v>
       </c>
       <c r="D189" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>33</v>
@@ -7394,7 +7394,7 @@
         <v>32</v>
       </c>
       <c r="D190" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>33</v>
@@ -7411,7 +7411,7 @@
         <v>32</v>
       </c>
       <c r="D191" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>33</v>
@@ -7428,7 +7428,7 @@
         <v>32</v>
       </c>
       <c r="D192" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>33</v>
@@ -7445,7 +7445,7 @@
         <v>32</v>
       </c>
       <c r="D193" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>33</v>
@@ -7462,7 +7462,7 @@
         <v>32</v>
       </c>
       <c r="D194" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>33</v>
@@ -7479,7 +7479,7 @@
         <v>32</v>
       </c>
       <c r="D195" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>33</v>
@@ -7496,7 +7496,7 @@
         <v>32</v>
       </c>
       <c r="D196" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>33</v>
@@ -7513,7 +7513,7 @@
         <v>32</v>
       </c>
       <c r="D197" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>33</v>
@@ -7530,7 +7530,7 @@
         <v>32</v>
       </c>
       <c r="D198" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>33</v>
@@ -7547,7 +7547,7 @@
         <v>32</v>
       </c>
       <c r="D199" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>33</v>
@@ -7564,7 +7564,7 @@
         <v>32</v>
       </c>
       <c r="D200" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>33</v>
@@ -7598,7 +7598,7 @@
         <v>32</v>
       </c>
       <c r="D202" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>33</v>
@@ -7615,7 +7615,7 @@
         <v>32</v>
       </c>
       <c r="D203" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>33</v>
@@ -7632,7 +7632,7 @@
         <v>32</v>
       </c>
       <c r="D204" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>33</v>
@@ -7649,7 +7649,7 @@
         <v>32</v>
       </c>
       <c r="D205" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>33</v>
@@ -7666,7 +7666,7 @@
         <v>32</v>
       </c>
       <c r="D206" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>33</v>
@@ -7683,7 +7683,7 @@
         <v>32</v>
       </c>
       <c r="D207" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>33</v>
@@ -7700,7 +7700,7 @@
         <v>32</v>
       </c>
       <c r="D208" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>33</v>
@@ -7717,7 +7717,7 @@
         <v>32</v>
       </c>
       <c r="D209" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>33</v>
@@ -7734,7 +7734,7 @@
         <v>32</v>
       </c>
       <c r="D210" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>33</v>
@@ -7751,7 +7751,7 @@
         <v>32</v>
       </c>
       <c r="D211" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>33</v>
@@ -7768,7 +7768,7 @@
         <v>32</v>
       </c>
       <c r="D212" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>33</v>
@@ -7785,7 +7785,7 @@
         <v>32</v>
       </c>
       <c r="D213" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>33</v>
@@ -7802,7 +7802,7 @@
         <v>32</v>
       </c>
       <c r="D214" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>33</v>
@@ -7819,7 +7819,7 @@
         <v>32</v>
       </c>
       <c r="D215" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>33</v>
@@ -7836,7 +7836,7 @@
         <v>32</v>
       </c>
       <c r="D216" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>33</v>
@@ -7853,7 +7853,7 @@
         <v>32</v>
       </c>
       <c r="D217" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>33</v>
@@ -7870,7 +7870,7 @@
         <v>32</v>
       </c>
       <c r="D218" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>33</v>
@@ -7887,7 +7887,7 @@
         <v>32</v>
       </c>
       <c r="D219" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>33</v>
@@ -7904,7 +7904,7 @@
         <v>32</v>
       </c>
       <c r="D220" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>33</v>
@@ -7921,7 +7921,7 @@
         <v>32</v>
       </c>
       <c r="D221" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>33</v>
@@ -7938,7 +7938,7 @@
         <v>32</v>
       </c>
       <c r="D222" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>33</v>
@@ -7955,7 +7955,7 @@
         <v>32</v>
       </c>
       <c r="D223" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>33</v>
@@ -7972,7 +7972,7 @@
         <v>32</v>
       </c>
       <c r="D224" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>33</v>
@@ -7989,7 +7989,7 @@
         <v>32</v>
       </c>
       <c r="D225" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>33</v>
@@ -8006,7 +8006,7 @@
         <v>32</v>
       </c>
       <c r="D226" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>33</v>
@@ -8023,7 +8023,7 @@
         <v>32</v>
       </c>
       <c r="D227" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>33</v>
@@ -8040,7 +8040,7 @@
         <v>32</v>
       </c>
       <c r="D228" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>33</v>
@@ -8057,7 +8057,7 @@
         <v>32</v>
       </c>
       <c r="D229" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>33</v>
@@ -8074,7 +8074,7 @@
         <v>32</v>
       </c>
       <c r="D230" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>33</v>
@@ -8091,7 +8091,7 @@
         <v>32</v>
       </c>
       <c r="D231" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>33</v>
@@ -8108,7 +8108,7 @@
         <v>32</v>
       </c>
       <c r="D232" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>33</v>
@@ -8125,7 +8125,7 @@
         <v>32</v>
       </c>
       <c r="D233" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>33</v>
@@ -8142,7 +8142,7 @@
         <v>32</v>
       </c>
       <c r="D234" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>33</v>
@@ -8159,7 +8159,7 @@
         <v>32</v>
       </c>
       <c r="D235" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>33</v>
@@ -8176,7 +8176,7 @@
         <v>32</v>
       </c>
       <c r="D236" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>33</v>
@@ -8193,7 +8193,7 @@
         <v>32</v>
       </c>
       <c r="D237" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>33</v>
@@ -8210,7 +8210,7 @@
         <v>32</v>
       </c>
       <c r="D238" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>33</v>
@@ -8227,7 +8227,7 @@
         <v>32</v>
       </c>
       <c r="D239" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>33</v>
@@ -8244,7 +8244,7 @@
         <v>32</v>
       </c>
       <c r="D240" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>33</v>
@@ -8261,7 +8261,7 @@
         <v>32</v>
       </c>
       <c r="D241" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>33</v>
@@ -8278,7 +8278,7 @@
         <v>32</v>
       </c>
       <c r="D242" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>33</v>
@@ -8295,7 +8295,7 @@
         <v>32</v>
       </c>
       <c r="D243" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>33</v>
@@ -8329,7 +8329,7 @@
         <v>32</v>
       </c>
       <c r="D245" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>33</v>
@@ -8346,7 +8346,7 @@
         <v>32</v>
       </c>
       <c r="D246" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>33</v>
@@ -8363,7 +8363,7 @@
         <v>32</v>
       </c>
       <c r="D247" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>33</v>
@@ -8380,7 +8380,7 @@
         <v>32</v>
       </c>
       <c r="D248" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>33</v>
@@ -8397,7 +8397,7 @@
         <v>32</v>
       </c>
       <c r="D249" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>33</v>
@@ -8414,7 +8414,7 @@
         <v>32</v>
       </c>
       <c r="D250" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>33</v>
@@ -8431,7 +8431,7 @@
         <v>32</v>
       </c>
       <c r="D251" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>33</v>
@@ -8448,7 +8448,7 @@
         <v>32</v>
       </c>
       <c r="D252" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>33</v>
@@ -8465,7 +8465,7 @@
         <v>32</v>
       </c>
       <c r="D253" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>33</v>
@@ -8482,7 +8482,7 @@
         <v>32</v>
       </c>
       <c r="D254" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>33</v>
@@ -8499,7 +8499,7 @@
         <v>32</v>
       </c>
       <c r="D255" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>33</v>
@@ -8516,7 +8516,7 @@
         <v>32</v>
       </c>
       <c r="D256" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>33</v>
@@ -8533,7 +8533,7 @@
         <v>32</v>
       </c>
       <c r="D257" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>33</v>
@@ -8550,7 +8550,7 @@
         <v>32</v>
       </c>
       <c r="D258" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>33</v>
@@ -8567,7 +8567,7 @@
         <v>32</v>
       </c>
       <c r="D259" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>33</v>
@@ -8584,7 +8584,7 @@
         <v>32</v>
       </c>
       <c r="D260" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>33</v>
@@ -8601,7 +8601,7 @@
         <v>32</v>
       </c>
       <c r="D261" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>33</v>
@@ -8618,7 +8618,7 @@
         <v>32</v>
       </c>
       <c r="D262" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>33</v>
@@ -8652,7 +8652,7 @@
         <v>32</v>
       </c>
       <c r="D264" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>33</v>
@@ -8669,7 +8669,7 @@
         <v>32</v>
       </c>
       <c r="D265" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>33</v>
@@ -8686,7 +8686,7 @@
         <v>32</v>
       </c>
       <c r="D266" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>33</v>
@@ -8703,7 +8703,7 @@
         <v>32</v>
       </c>
       <c r="D267" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>33</v>
@@ -8720,7 +8720,7 @@
         <v>32</v>
       </c>
       <c r="D268" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>33</v>
@@ -8737,7 +8737,7 @@
         <v>32</v>
       </c>
       <c r="D269" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>33</v>
@@ -8754,7 +8754,7 @@
         <v>32</v>
       </c>
       <c r="D270" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>33</v>
@@ -8788,7 +8788,7 @@
         <v>32</v>
       </c>
       <c r="D272" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>33</v>
@@ -8805,7 +8805,7 @@
         <v>32</v>
       </c>
       <c r="D273" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>33</v>
@@ -8822,7 +8822,7 @@
         <v>32</v>
       </c>
       <c r="D274" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>33</v>
@@ -8839,7 +8839,7 @@
         <v>32</v>
       </c>
       <c r="D275" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>33</v>
@@ -8873,7 +8873,7 @@
         <v>32</v>
       </c>
       <c r="D277" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>33</v>
@@ -8890,7 +8890,7 @@
         <v>32</v>
       </c>
       <c r="D278" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>33</v>
@@ -8907,7 +8907,7 @@
         <v>32</v>
       </c>
       <c r="D279" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>33</v>
@@ -8924,7 +8924,7 @@
         <v>32</v>
       </c>
       <c r="D280" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>33</v>
@@ -8941,7 +8941,7 @@
         <v>32</v>
       </c>
       <c r="D281" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>33</v>
@@ -8958,7 +8958,7 @@
         <v>32</v>
       </c>
       <c r="D282" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>33</v>
@@ -8975,7 +8975,7 @@
         <v>32</v>
       </c>
       <c r="D283" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>33</v>
@@ -8992,7 +8992,7 @@
         <v>32</v>
       </c>
       <c r="D284" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>33</v>
@@ -9009,7 +9009,7 @@
         <v>32</v>
       </c>
       <c r="D285" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>33</v>
@@ -9026,7 +9026,7 @@
         <v>32</v>
       </c>
       <c r="D286" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>33</v>
@@ -9043,7 +9043,7 @@
         <v>32</v>
       </c>
       <c r="D287" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>33</v>
@@ -9060,7 +9060,7 @@
         <v>32</v>
       </c>
       <c r="D288" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>33</v>
@@ -9077,7 +9077,7 @@
         <v>32</v>
       </c>
       <c r="D289" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>33</v>
@@ -9094,7 +9094,7 @@
         <v>32</v>
       </c>
       <c r="D290" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>33</v>
@@ -9111,7 +9111,7 @@
         <v>32</v>
       </c>
       <c r="D291" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>33</v>
@@ -9128,7 +9128,7 @@
         <v>32</v>
       </c>
       <c r="D292" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>33</v>
@@ -9145,7 +9145,7 @@
         <v>32</v>
       </c>
       <c r="D293" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>33</v>
@@ -9162,7 +9162,7 @@
         <v>32</v>
       </c>
       <c r="D294" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>33</v>
@@ -9179,7 +9179,7 @@
         <v>32</v>
       </c>
       <c r="D295" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>33</v>
@@ -9196,7 +9196,7 @@
         <v>32</v>
       </c>
       <c r="D296" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>33</v>
@@ -9213,7 +9213,7 @@
         <v>32</v>
       </c>
       <c r="D297" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>33</v>
@@ -9230,7 +9230,7 @@
         <v>32</v>
       </c>
       <c r="D298" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>33</v>
@@ -9247,7 +9247,7 @@
         <v>32</v>
       </c>
       <c r="D299" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>33</v>
@@ -9264,7 +9264,7 @@
         <v>32</v>
       </c>
       <c r="D300" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>33</v>
@@ -9281,7 +9281,7 @@
         <v>32</v>
       </c>
       <c r="D301" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>33</v>
@@ -9298,7 +9298,7 @@
         <v>32</v>
       </c>
       <c r="D302" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>33</v>
@@ -9315,7 +9315,7 @@
         <v>32</v>
       </c>
       <c r="D303" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>33</v>
@@ -9332,7 +9332,7 @@
         <v>32</v>
       </c>
       <c r="D304" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>33</v>
@@ -9349,7 +9349,7 @@
         <v>32</v>
       </c>
       <c r="D305" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>33</v>
@@ -9366,7 +9366,7 @@
         <v>32</v>
       </c>
       <c r="D306" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>33</v>
@@ -9383,7 +9383,7 @@
         <v>32</v>
       </c>
       <c r="D307" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>33</v>
@@ -9400,7 +9400,7 @@
         <v>32</v>
       </c>
       <c r="D308" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>33</v>
@@ -9417,7 +9417,7 @@
         <v>32</v>
       </c>
       <c r="D309" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>33</v>
@@ -9434,7 +9434,7 @@
         <v>32</v>
       </c>
       <c r="D310" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>33</v>
@@ -9468,7 +9468,7 @@
         <v>32</v>
       </c>
       <c r="D312" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>33</v>
@@ -9485,7 +9485,7 @@
         <v>32</v>
       </c>
       <c r="D313" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>33</v>
@@ -9502,7 +9502,7 @@
         <v>32</v>
       </c>
       <c r="D314" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>33</v>
@@ -9519,7 +9519,7 @@
         <v>32</v>
       </c>
       <c r="D315" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>33</v>
@@ -9536,7 +9536,7 @@
         <v>32</v>
       </c>
       <c r="D316" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>33</v>
@@ -9553,7 +9553,7 @@
         <v>32</v>
       </c>
       <c r="D317" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>33</v>
@@ -9570,7 +9570,7 @@
         <v>32</v>
       </c>
       <c r="D318" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>33</v>
@@ -9604,7 +9604,7 @@
         <v>32</v>
       </c>
       <c r="D320" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>33</v>
@@ -9621,7 +9621,7 @@
         <v>32</v>
       </c>
       <c r="D321" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>33</v>
@@ -9638,7 +9638,7 @@
         <v>32</v>
       </c>
       <c r="D322" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>33</v>
@@ -9655,7 +9655,7 @@
         <v>32</v>
       </c>
       <c r="D323" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>33</v>
@@ -9672,7 +9672,7 @@
         <v>32</v>
       </c>
       <c r="D324" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>33</v>
@@ -9689,7 +9689,7 @@
         <v>32</v>
       </c>
       <c r="D325" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>33</v>
@@ -9706,7 +9706,7 @@
         <v>32</v>
       </c>
       <c r="D326" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>33</v>
@@ -9723,7 +9723,7 @@
         <v>32</v>
       </c>
       <c r="D327" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>33</v>
@@ -9740,7 +9740,7 @@
         <v>32</v>
       </c>
       <c r="D328" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>33</v>
@@ -9757,7 +9757,7 @@
         <v>32</v>
       </c>
       <c r="D329" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>33</v>
@@ -9774,7 +9774,7 @@
         <v>32</v>
       </c>
       <c r="D330" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>33</v>
@@ -9791,7 +9791,7 @@
         <v>32</v>
       </c>
       <c r="D331" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>33</v>
@@ -9808,7 +9808,7 @@
         <v>32</v>
       </c>
       <c r="D332" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>33</v>
@@ -9825,7 +9825,7 @@
         <v>32</v>
       </c>
       <c r="D333" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>33</v>
@@ -9842,7 +9842,7 @@
         <v>32</v>
       </c>
       <c r="D334" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>33</v>
@@ -9859,7 +9859,7 @@
         <v>32</v>
       </c>
       <c r="D335" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>33</v>
@@ -9876,7 +9876,7 @@
         <v>32</v>
       </c>
       <c r="D336" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>33</v>
@@ -9893,7 +9893,7 @@
         <v>32</v>
       </c>
       <c r="D337" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>33</v>
@@ -9910,7 +9910,7 @@
         <v>32</v>
       </c>
       <c r="D338" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>33</v>
@@ -9927,7 +9927,7 @@
         <v>32</v>
       </c>
       <c r="D339" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>33</v>
@@ -9944,7 +9944,7 @@
         <v>32</v>
       </c>
       <c r="D340" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>33</v>
@@ -9961,7 +9961,7 @@
         <v>32</v>
       </c>
       <c r="D341" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>33</v>
@@ -9978,7 +9978,7 @@
         <v>32</v>
       </c>
       <c r="D342" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>33</v>
@@ -9995,7 +9995,7 @@
         <v>32</v>
       </c>
       <c r="D343" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>33</v>
@@ -10012,7 +10012,7 @@
         <v>32</v>
       </c>
       <c r="D344" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>33</v>
@@ -10029,7 +10029,7 @@
         <v>32</v>
       </c>
       <c r="D345" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>33</v>
@@ -10046,7 +10046,7 @@
         <v>32</v>
       </c>
       <c r="D346" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>33</v>
@@ -10063,7 +10063,7 @@
         <v>32</v>
       </c>
       <c r="D347" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>33</v>
@@ -10080,7 +10080,7 @@
         <v>32</v>
       </c>
       <c r="D348" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>33</v>
@@ -10097,7 +10097,7 @@
         <v>32</v>
       </c>
       <c r="D349" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>33</v>
@@ -10114,7 +10114,7 @@
         <v>32</v>
       </c>
       <c r="D350" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>33</v>
@@ -10131,7 +10131,7 @@
         <v>32</v>
       </c>
       <c r="D351" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>33</v>
@@ -10148,7 +10148,7 @@
         <v>32</v>
       </c>
       <c r="D352" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>33</v>
@@ -10165,7 +10165,7 @@
         <v>32</v>
       </c>
       <c r="D353" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>33</v>
@@ -10182,7 +10182,7 @@
         <v>32</v>
       </c>
       <c r="D354" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>33</v>
@@ -10199,7 +10199,7 @@
         <v>32</v>
       </c>
       <c r="D355" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>33</v>
@@ -10216,7 +10216,7 @@
         <v>32</v>
       </c>
       <c r="D356" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>33</v>
@@ -10233,7 +10233,7 @@
         <v>32</v>
       </c>
       <c r="D357" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>33</v>
@@ -10250,7 +10250,7 @@
         <v>32</v>
       </c>
       <c r="D358" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>33</v>
@@ -10267,7 +10267,7 @@
         <v>32</v>
       </c>
       <c r="D359" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>33</v>
@@ -10284,7 +10284,7 @@
         <v>32</v>
       </c>
       <c r="D360" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>33</v>
@@ -10301,7 +10301,7 @@
         <v>32</v>
       </c>
       <c r="D361" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>33</v>
@@ -10335,7 +10335,7 @@
         <v>32</v>
       </c>
       <c r="D363" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>33</v>
@@ -10352,7 +10352,7 @@
         <v>32</v>
       </c>
       <c r="D364" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>33</v>
@@ -10369,7 +10369,7 @@
         <v>32</v>
       </c>
       <c r="D365" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>33</v>
@@ -10386,7 +10386,7 @@
         <v>32</v>
       </c>
       <c r="D366" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>33</v>
@@ -10403,7 +10403,7 @@
         <v>32</v>
       </c>
       <c r="D367" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>33</v>
@@ -10420,7 +10420,7 @@
         <v>32</v>
       </c>
       <c r="D368" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>33</v>
@@ -10437,7 +10437,7 @@
         <v>32</v>
       </c>
       <c r="D369" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>33</v>
@@ -10454,7 +10454,7 @@
         <v>32</v>
       </c>
       <c r="D370" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>33</v>
@@ -10471,7 +10471,7 @@
         <v>32</v>
       </c>
       <c r="D371" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>33</v>
@@ -10488,7 +10488,7 @@
         <v>32</v>
       </c>
       <c r="D372" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>33</v>
@@ -10505,7 +10505,7 @@
         <v>32</v>
       </c>
       <c r="D373" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>33</v>
@@ -10522,7 +10522,7 @@
         <v>32</v>
       </c>
       <c r="D374" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>33</v>
@@ -10539,7 +10539,7 @@
         <v>32</v>
       </c>
       <c r="D375" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>33</v>
@@ -10556,7 +10556,7 @@
         <v>32</v>
       </c>
       <c r="D376" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>33</v>
@@ -10573,7 +10573,7 @@
         <v>32</v>
       </c>
       <c r="D377" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>33</v>
@@ -10590,7 +10590,7 @@
         <v>32</v>
       </c>
       <c r="D378" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>33</v>
@@ -10607,7 +10607,7 @@
         <v>32</v>
       </c>
       <c r="D379" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>33</v>
@@ -10624,7 +10624,7 @@
         <v>32</v>
       </c>
       <c r="D380" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>33</v>
@@ -10641,7 +10641,7 @@
         <v>32</v>
       </c>
       <c r="D381" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>33</v>
@@ -10658,7 +10658,7 @@
         <v>32</v>
       </c>
       <c r="D382" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>33</v>
@@ -10675,7 +10675,7 @@
         <v>32</v>
       </c>
       <c r="D383" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>33</v>
@@ -10692,7 +10692,7 @@
         <v>32</v>
       </c>
       <c r="D384" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>33</v>
@@ -10709,7 +10709,7 @@
         <v>32</v>
       </c>
       <c r="D385" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>33</v>
@@ -10726,7 +10726,7 @@
         <v>32</v>
       </c>
       <c r="D386" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>33</v>
@@ -10743,7 +10743,7 @@
         <v>32</v>
       </c>
       <c r="D387" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E387" s="2" t="s">
         <v>33</v>
@@ -10760,7 +10760,7 @@
         <v>32</v>
       </c>
       <c r="D388" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>33</v>
@@ -10794,7 +10794,7 @@
         <v>32</v>
       </c>
       <c r="D390" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>33</v>
@@ -10811,7 +10811,7 @@
         <v>32</v>
       </c>
       <c r="D391" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>33</v>
@@ -10828,7 +10828,7 @@
         <v>32</v>
       </c>
       <c r="D392" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>33</v>
@@ -10845,7 +10845,7 @@
         <v>32</v>
       </c>
       <c r="D393" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>33</v>
@@ -10862,7 +10862,7 @@
         <v>32</v>
       </c>
       <c r="D394" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>33</v>
@@ -10879,7 +10879,7 @@
         <v>32</v>
       </c>
       <c r="D395" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>33</v>
@@ -10896,7 +10896,7 @@
         <v>32</v>
       </c>
       <c r="D396" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>33</v>
@@ -10913,7 +10913,7 @@
         <v>32</v>
       </c>
       <c r="D397" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>33</v>
@@ -10930,7 +10930,7 @@
         <v>32</v>
       </c>
       <c r="D398" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>33</v>
@@ -10947,7 +10947,7 @@
         <v>32</v>
       </c>
       <c r="D399" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>33</v>
@@ -10964,7 +10964,7 @@
         <v>32</v>
       </c>
       <c r="D400" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>33</v>
@@ -10981,7 +10981,7 @@
         <v>32</v>
       </c>
       <c r="D401" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>33</v>
@@ -10998,7 +10998,7 @@
         <v>32</v>
       </c>
       <c r="D402" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>33</v>
@@ -11015,7 +11015,7 @@
         <v>32</v>
       </c>
       <c r="D403" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>33</v>
@@ -11032,7 +11032,7 @@
         <v>32</v>
       </c>
       <c r="D404" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>33</v>
@@ -11049,7 +11049,7 @@
         <v>32</v>
       </c>
       <c r="D405" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>33</v>
@@ -11066,7 +11066,7 @@
         <v>32</v>
       </c>
       <c r="D406" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>33</v>
@@ -11083,7 +11083,7 @@
         <v>32</v>
       </c>
       <c r="D407" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>33</v>
@@ -11100,7 +11100,7 @@
         <v>32</v>
       </c>
       <c r="D408" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>33</v>
@@ -11134,7 +11134,7 @@
         <v>32</v>
       </c>
       <c r="D410" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>33</v>
@@ -11168,7 +11168,7 @@
         <v>32</v>
       </c>
       <c r="D412" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>33</v>
@@ -11185,7 +11185,7 @@
         <v>32</v>
       </c>
       <c r="D413" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>33</v>
@@ -11219,7 +11219,7 @@
         <v>32</v>
       </c>
       <c r="D415" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>33</v>
@@ -11236,7 +11236,7 @@
         <v>32</v>
       </c>
       <c r="D416" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>33</v>
@@ -11253,7 +11253,7 @@
         <v>32</v>
       </c>
       <c r="D417" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>33</v>
@@ -11270,7 +11270,7 @@
         <v>32</v>
       </c>
       <c r="D418" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>33</v>
@@ -11287,7 +11287,7 @@
         <v>32</v>
       </c>
       <c r="D419" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>33</v>
@@ -11304,7 +11304,7 @@
         <v>32</v>
       </c>
       <c r="D420" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>33</v>
@@ -11321,7 +11321,7 @@
         <v>32</v>
       </c>
       <c r="D421" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>33</v>
@@ -11355,7 +11355,7 @@
         <v>32</v>
       </c>
       <c r="D423" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>33</v>
@@ -11372,7 +11372,7 @@
         <v>32</v>
       </c>
       <c r="D424" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>33</v>
@@ -11389,7 +11389,7 @@
         <v>32</v>
       </c>
       <c r="D425" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>33</v>
@@ -11406,7 +11406,7 @@
         <v>32</v>
       </c>
       <c r="D426" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>33</v>
@@ -11423,7 +11423,7 @@
         <v>32</v>
       </c>
       <c r="D427" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>33</v>
@@ -11440,7 +11440,7 @@
         <v>32</v>
       </c>
       <c r="D428" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>33</v>
@@ -11457,7 +11457,7 @@
         <v>32</v>
       </c>
       <c r="D429" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>33</v>
@@ -11474,7 +11474,7 @@
         <v>32</v>
       </c>
       <c r="D430" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>33</v>
@@ -11491,7 +11491,7 @@
         <v>32</v>
       </c>
       <c r="D431" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>33</v>
@@ -11508,7 +11508,7 @@
         <v>32</v>
       </c>
       <c r="D432" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>33</v>
@@ -11525,7 +11525,7 @@
         <v>32</v>
       </c>
       <c r="D433" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>33</v>
@@ -11542,7 +11542,7 @@
         <v>32</v>
       </c>
       <c r="D434" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>33</v>
@@ -11559,7 +11559,7 @@
         <v>32</v>
       </c>
       <c r="D435" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>33</v>
@@ -11576,7 +11576,7 @@
         <v>32</v>
       </c>
       <c r="D436" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>33</v>
@@ -11593,7 +11593,7 @@
         <v>32</v>
       </c>
       <c r="D437" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>33</v>
@@ -11610,7 +11610,7 @@
         <v>32</v>
       </c>
       <c r="D438" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>33</v>
@@ -11644,7 +11644,7 @@
         <v>32</v>
       </c>
       <c r="D440" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>33</v>
@@ -11661,7 +11661,7 @@
         <v>32</v>
       </c>
       <c r="D441" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>33</v>
@@ -11678,7 +11678,7 @@
         <v>32</v>
       </c>
       <c r="D442" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>33</v>
@@ -11695,7 +11695,7 @@
         <v>32</v>
       </c>
       <c r="D443" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>33</v>
@@ -11712,7 +11712,7 @@
         <v>32</v>
       </c>
       <c r="D444" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>33</v>
@@ -11729,7 +11729,7 @@
         <v>32</v>
       </c>
       <c r="D445" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>33</v>
@@ -11746,7 +11746,7 @@
         <v>32</v>
       </c>
       <c r="D446" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>33</v>
@@ -11763,7 +11763,7 @@
         <v>32</v>
       </c>
       <c r="D447" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>33</v>
@@ -11780,7 +11780,7 @@
         <v>32</v>
       </c>
       <c r="D448" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>33</v>
@@ -11797,7 +11797,7 @@
         <v>32</v>
       </c>
       <c r="D449" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>33</v>
@@ -11814,7 +11814,7 @@
         <v>32</v>
       </c>
       <c r="D450" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>33</v>
@@ -11831,7 +11831,7 @@
         <v>32</v>
       </c>
       <c r="D451" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>33</v>
@@ -11848,7 +11848,7 @@
         <v>32</v>
       </c>
       <c r="D452" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>33</v>
@@ -11865,7 +11865,7 @@
         <v>32</v>
       </c>
       <c r="D453" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>33</v>
@@ -11882,7 +11882,7 @@
         <v>32</v>
       </c>
       <c r="D454" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>33</v>
@@ -11899,7 +11899,7 @@
         <v>32</v>
       </c>
       <c r="D455" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>33</v>
@@ -11916,7 +11916,7 @@
         <v>32</v>
       </c>
       <c r="D456" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>33</v>
@@ -11933,7 +11933,7 @@
         <v>32</v>
       </c>
       <c r="D457" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>33</v>
@@ -11950,7 +11950,7 @@
         <v>32</v>
       </c>
       <c r="D458" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>33</v>
@@ -11967,7 +11967,7 @@
         <v>32</v>
       </c>
       <c r="D459" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>33</v>
@@ -11984,7 +11984,7 @@
         <v>32</v>
       </c>
       <c r="D460" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>33</v>
@@ -12001,7 +12001,7 @@
         <v>32</v>
       </c>
       <c r="D461" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>33</v>
@@ -12018,7 +12018,7 @@
         <v>32</v>
       </c>
       <c r="D462" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>33</v>
@@ -12035,7 +12035,7 @@
         <v>32</v>
       </c>
       <c r="D463" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>33</v>
@@ -12052,7 +12052,7 @@
         <v>32</v>
       </c>
       <c r="D464" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>33</v>
@@ -12086,7 +12086,7 @@
         <v>32</v>
       </c>
       <c r="D466" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>33</v>
@@ -12103,7 +12103,7 @@
         <v>32</v>
       </c>
       <c r="D467" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>33</v>
@@ -12120,7 +12120,7 @@
         <v>32</v>
       </c>
       <c r="D468" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>33</v>
@@ -12137,7 +12137,7 @@
         <v>32</v>
       </c>
       <c r="D469" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>33</v>
@@ -12154,7 +12154,7 @@
         <v>32</v>
       </c>
       <c r="D470" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E470" s="2" t="s">
         <v>33</v>
@@ -12171,7 +12171,7 @@
         <v>32</v>
       </c>
       <c r="D471" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>33</v>
@@ -12188,7 +12188,7 @@
         <v>32</v>
       </c>
       <c r="D472" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>33</v>
@@ -12205,7 +12205,7 @@
         <v>32</v>
       </c>
       <c r="D473" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>33</v>
@@ -12222,7 +12222,7 @@
         <v>32</v>
       </c>
       <c r="D474" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>33</v>
@@ -12239,7 +12239,7 @@
         <v>32</v>
       </c>
       <c r="D475" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>33</v>
@@ -12256,7 +12256,7 @@
         <v>32</v>
       </c>
       <c r="D476" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>33</v>
@@ -12273,7 +12273,7 @@
         <v>32</v>
       </c>
       <c r="D477" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>33</v>
@@ -12290,7 +12290,7 @@
         <v>32</v>
       </c>
       <c r="D478" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>33</v>
@@ -12307,7 +12307,7 @@
         <v>32</v>
       </c>
       <c r="D479" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>33</v>
@@ -12324,7 +12324,7 @@
         <v>32</v>
       </c>
       <c r="D480" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>33</v>
@@ -12341,7 +12341,7 @@
         <v>32</v>
       </c>
       <c r="D481" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>33</v>
@@ -12358,7 +12358,7 @@
         <v>32</v>
       </c>
       <c r="D482" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>33</v>
@@ -12375,7 +12375,7 @@
         <v>32</v>
       </c>
       <c r="D483" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>33</v>
@@ -12392,7 +12392,7 @@
         <v>32</v>
       </c>
       <c r="D484" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>33</v>
@@ -12409,7 +12409,7 @@
         <v>32</v>
       </c>
       <c r="D485" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>33</v>
@@ -12426,7 +12426,7 @@
         <v>32</v>
       </c>
       <c r="D486" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>33</v>
@@ -12443,7 +12443,7 @@
         <v>32</v>
       </c>
       <c r="D487" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>33</v>
@@ -12460,7 +12460,7 @@
         <v>32</v>
       </c>
       <c r="D488" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>33</v>
@@ -12477,7 +12477,7 @@
         <v>32</v>
       </c>
       <c r="D489" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>33</v>
@@ -12494,7 +12494,7 @@
         <v>32</v>
       </c>
       <c r="D490" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>33</v>
@@ -12511,7 +12511,7 @@
         <v>32</v>
       </c>
       <c r="D491" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>33</v>
@@ -12528,7 +12528,7 @@
         <v>32</v>
       </c>
       <c r="D492" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>33</v>
@@ -12545,7 +12545,7 @@
         <v>32</v>
       </c>
       <c r="D493" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>33</v>
@@ -12562,7 +12562,7 @@
         <v>32</v>
       </c>
       <c r="D494" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>33</v>
@@ -12579,7 +12579,7 @@
         <v>32</v>
       </c>
       <c r="D495" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>33</v>
@@ -12596,7 +12596,7 @@
         <v>32</v>
       </c>
       <c r="D496" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>33</v>
@@ -12613,7 +12613,7 @@
         <v>32</v>
       </c>
       <c r="D497" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>33</v>
@@ -12630,7 +12630,7 @@
         <v>32</v>
       </c>
       <c r="D498" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>33</v>
@@ -12647,7 +12647,7 @@
         <v>32</v>
       </c>
       <c r="D499" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>33</v>
@@ -12664,7 +12664,7 @@
         <v>32</v>
       </c>
       <c r="D500" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>33</v>
@@ -12681,7 +12681,7 @@
         <v>32</v>
       </c>
       <c r="D501" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>33</v>
@@ -12698,7 +12698,7 @@
         <v>32</v>
       </c>
       <c r="D502" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>33</v>
@@ -12715,7 +12715,7 @@
         <v>32</v>
       </c>
       <c r="D503" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>33</v>
@@ -12732,7 +12732,7 @@
         <v>32</v>
       </c>
       <c r="D504" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>33</v>
@@ -12749,7 +12749,7 @@
         <v>32</v>
       </c>
       <c r="D505" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E505" s="2" t="s">
         <v>33</v>
@@ -12766,7 +12766,7 @@
         <v>32</v>
       </c>
       <c r="D506" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>33</v>
@@ -12783,7 +12783,7 @@
         <v>32</v>
       </c>
       <c r="D507" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>33</v>
@@ -12800,7 +12800,7 @@
         <v>32</v>
       </c>
       <c r="D508" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>33</v>
@@ -12817,7 +12817,7 @@
         <v>32</v>
       </c>
       <c r="D509" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E509" s="2" t="s">
         <v>33</v>
@@ -12834,7 +12834,7 @@
         <v>32</v>
       </c>
       <c r="D510" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E510" s="2" t="s">
         <v>33</v>
@@ -12851,7 +12851,7 @@
         <v>32</v>
       </c>
       <c r="D511" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E511" s="2" t="s">
         <v>33</v>
@@ -12868,7 +12868,7 @@
         <v>32</v>
       </c>
       <c r="D512" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>33</v>
@@ -12885,7 +12885,7 @@
         <v>32</v>
       </c>
       <c r="D513" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>33</v>
@@ -12902,7 +12902,7 @@
         <v>32</v>
       </c>
       <c r="D514" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>33</v>
@@ -12919,7 +12919,7 @@
         <v>32</v>
       </c>
       <c r="D515" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E515" s="2" t="s">
         <v>33</v>
@@ -12936,7 +12936,7 @@
         <v>32</v>
       </c>
       <c r="D516" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E516" s="2" t="s">
         <v>33</v>
@@ -12953,7 +12953,7 @@
         <v>32</v>
       </c>
       <c r="D517" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>33</v>
@@ -12987,7 +12987,7 @@
         <v>32</v>
       </c>
       <c r="D519" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>33</v>
@@ -13004,7 +13004,7 @@
         <v>32</v>
       </c>
       <c r="D520" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E520" s="2" t="s">
         <v>33</v>
@@ -13021,7 +13021,7 @@
         <v>32</v>
       </c>
       <c r="D521" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>33</v>
@@ -13038,7 +13038,7 @@
         <v>32</v>
       </c>
       <c r="D522" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>33</v>
@@ -13055,7 +13055,7 @@
         <v>32</v>
       </c>
       <c r="D523" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>33</v>
@@ -13072,7 +13072,7 @@
         <v>32</v>
       </c>
       <c r="D524" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>33</v>
@@ -13089,7 +13089,7 @@
         <v>32</v>
       </c>
       <c r="D525" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>33</v>
@@ -13106,7 +13106,7 @@
         <v>32</v>
       </c>
       <c r="D526" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>33</v>
@@ -13123,7 +13123,7 @@
         <v>32</v>
       </c>
       <c r="D527" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>33</v>
@@ -13140,7 +13140,7 @@
         <v>32</v>
       </c>
       <c r="D528" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E528" s="2" t="s">
         <v>33</v>
@@ -13157,7 +13157,7 @@
         <v>32</v>
       </c>
       <c r="D529" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E529" s="2" t="s">
         <v>33</v>
@@ -13174,7 +13174,7 @@
         <v>32</v>
       </c>
       <c r="D530" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E530" s="2" t="s">
         <v>33</v>
@@ -13191,7 +13191,7 @@
         <v>32</v>
       </c>
       <c r="D531" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>33</v>
@@ -13208,7 +13208,7 @@
         <v>32</v>
       </c>
       <c r="D532" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E532" s="2" t="s">
         <v>33</v>
@@ -13225,7 +13225,7 @@
         <v>32</v>
       </c>
       <c r="D533" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E533" s="2" t="s">
         <v>33</v>
@@ -13242,7 +13242,7 @@
         <v>32</v>
       </c>
       <c r="D534" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E534" s="2" t="s">
         <v>33</v>
@@ -13259,7 +13259,7 @@
         <v>32</v>
       </c>
       <c r="D535" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E535" s="2" t="s">
         <v>33</v>
@@ -13276,7 +13276,7 @@
         <v>32</v>
       </c>
       <c r="D536" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E536" s="2" t="s">
         <v>33</v>
@@ -13310,7 +13310,7 @@
         <v>32</v>
       </c>
       <c r="D538" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>33</v>
@@ -13327,7 +13327,7 @@
         <v>32</v>
       </c>
       <c r="D539" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>33</v>
@@ -13344,7 +13344,7 @@
         <v>32</v>
       </c>
       <c r="D540" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>33</v>
@@ -13361,7 +13361,7 @@
         <v>32</v>
       </c>
       <c r="D541" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>33</v>
@@ -13378,7 +13378,7 @@
         <v>32</v>
       </c>
       <c r="D542" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>33</v>
@@ -13395,7 +13395,7 @@
         <v>32</v>
       </c>
       <c r="D543" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E543" s="2" t="s">
         <v>33</v>
@@ -13412,7 +13412,7 @@
         <v>32</v>
       </c>
       <c r="D544" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>33</v>
@@ -13429,7 +13429,7 @@
         <v>32</v>
       </c>
       <c r="D545" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E545" s="2" t="s">
         <v>33</v>
@@ -13446,7 +13446,7 @@
         <v>32</v>
       </c>
       <c r="D546" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E546" s="2" t="s">
         <v>33</v>
@@ -13463,7 +13463,7 @@
         <v>32</v>
       </c>
       <c r="D547" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E547" s="2" t="s">
         <v>33</v>
@@ -13480,7 +13480,7 @@
         <v>32</v>
       </c>
       <c r="D548" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E548" s="2" t="s">
         <v>33</v>
@@ -13497,7 +13497,7 @@
         <v>32</v>
       </c>
       <c r="D549" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E549" s="2" t="s">
         <v>33</v>
@@ -13514,7 +13514,7 @@
         <v>32</v>
       </c>
       <c r="D550" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>33</v>
@@ -13531,7 +13531,7 @@
         <v>32</v>
       </c>
       <c r="D551" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E551" s="2" t="s">
         <v>33</v>
@@ -13548,7 +13548,7 @@
         <v>32</v>
       </c>
       <c r="D552" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E552" s="2" t="s">
         <v>33</v>
@@ -13565,7 +13565,7 @@
         <v>32</v>
       </c>
       <c r="D553" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>33</v>
@@ -13582,7 +13582,7 @@
         <v>32</v>
       </c>
       <c r="D554" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>33</v>
@@ -13599,7 +13599,7 @@
         <v>32</v>
       </c>
       <c r="D555" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>33</v>
@@ -13616,7 +13616,7 @@
         <v>32</v>
       </c>
       <c r="D556" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>33</v>
@@ -13650,7 +13650,7 @@
         <v>32</v>
       </c>
       <c r="D558" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E558" s="2" t="s">
         <v>33</v>
@@ -13667,7 +13667,7 @@
         <v>32</v>
       </c>
       <c r="D559" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>33</v>
@@ -13701,7 +13701,7 @@
         <v>32</v>
       </c>
       <c r="D561" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>33</v>
@@ -13718,7 +13718,7 @@
         <v>32</v>
       </c>
       <c r="D562" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E562" s="2" t="s">
         <v>33</v>
@@ -13735,7 +13735,7 @@
         <v>32</v>
       </c>
       <c r="D563" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>33</v>
@@ -13752,7 +13752,7 @@
         <v>32</v>
       </c>
       <c r="D564" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E564" s="2" t="s">
         <v>33</v>
@@ -13769,7 +13769,7 @@
         <v>32</v>
       </c>
       <c r="D565" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E565" s="2" t="s">
         <v>33</v>
@@ -13786,7 +13786,7 @@
         <v>32</v>
       </c>
       <c r="D566" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>33</v>
@@ -13803,7 +13803,7 @@
         <v>32</v>
       </c>
       <c r="D567" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>33</v>
@@ -13820,7 +13820,7 @@
         <v>32</v>
       </c>
       <c r="D568" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E568" s="2" t="s">
         <v>33</v>
@@ -13837,7 +13837,7 @@
         <v>32</v>
       </c>
       <c r="D569" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E569" s="2" t="s">
         <v>33</v>
@@ -13854,7 +13854,7 @@
         <v>32</v>
       </c>
       <c r="D570" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E570" s="2" t="s">
         <v>33</v>
@@ -13871,7 +13871,7 @@
         <v>32</v>
       </c>
       <c r="D571" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E571" s="2" t="s">
         <v>33</v>
@@ -13905,7 +13905,7 @@
         <v>32</v>
       </c>
       <c r="D573" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E573" s="2" t="s">
         <v>33</v>
@@ -13922,7 +13922,7 @@
         <v>32</v>
       </c>
       <c r="D574" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E574" s="2" t="s">
         <v>33</v>
@@ -13939,7 +13939,7 @@
         <v>32</v>
       </c>
       <c r="D575" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>33</v>
@@ -13956,7 +13956,7 @@
         <v>32</v>
       </c>
       <c r="D576" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E576" s="2" t="s">
         <v>33</v>
@@ -13973,7 +13973,7 @@
         <v>32</v>
       </c>
       <c r="D577" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>33</v>
@@ -14007,7 +14007,7 @@
         <v>32</v>
       </c>
       <c r="D579" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E579" s="2" t="s">
         <v>33</v>
@@ -14024,7 +14024,7 @@
         <v>32</v>
       </c>
       <c r="D580" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E580" s="2" t="s">
         <v>33</v>
@@ -14041,7 +14041,7 @@
         <v>32</v>
       </c>
       <c r="D581" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>33</v>
@@ -14058,7 +14058,7 @@
         <v>32</v>
       </c>
       <c r="D582" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E582" s="2" t="s">
         <v>33</v>
@@ -14075,7 +14075,7 @@
         <v>32</v>
       </c>
       <c r="D583" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>33</v>
@@ -14092,7 +14092,7 @@
         <v>32</v>
       </c>
       <c r="D584" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>33</v>
@@ -14109,7 +14109,7 @@
         <v>32</v>
       </c>
       <c r="D585" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E585" s="2" t="s">
         <v>33</v>
@@ -14143,7 +14143,7 @@
         <v>32</v>
       </c>
       <c r="D587" s="2">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E587" s="2" t="s">
         <v>33</v>
@@ -14160,7 +14160,7 @@
         <v>32</v>
       </c>
       <c r="D588" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E588" s="2" t="s">
         <v>33</v>
@@ -14177,7 +14177,7 @@
         <v>32</v>
       </c>
       <c r="D589" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E589" s="2" t="s">
         <v>33</v>
@@ -14194,7 +14194,7 @@
         <v>32</v>
       </c>
       <c r="D590" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E590" s="2" t="s">
         <v>33</v>
@@ -14211,7 +14211,7 @@
         <v>32</v>
       </c>
       <c r="D591" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E591" s="2" t="s">
         <v>33</v>
@@ -14228,7 +14228,7 @@
         <v>32</v>
       </c>
       <c r="D592" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E592" s="2" t="s">
         <v>33</v>
@@ -14245,7 +14245,7 @@
         <v>32</v>
       </c>
       <c r="D593" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>33</v>
@@ -14262,7 +14262,7 @@
         <v>32</v>
       </c>
       <c r="D594" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E594" s="2" t="s">
         <v>33</v>
@@ -14279,7 +14279,7 @@
         <v>32</v>
       </c>
       <c r="D595" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E595" s="2" t="s">
         <v>33</v>
@@ -14296,7 +14296,7 @@
         <v>32</v>
       </c>
       <c r="D596" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E596" s="2" t="s">
         <v>33</v>
@@ -14313,7 +14313,7 @@
         <v>32</v>
       </c>
       <c r="D597" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E597" s="2" t="s">
         <v>33</v>
@@ -14330,7 +14330,7 @@
         <v>32</v>
       </c>
       <c r="D598" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E598" s="2" t="s">
         <v>33</v>
@@ -14347,7 +14347,7 @@
         <v>32</v>
       </c>
       <c r="D599" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E599" s="2" t="s">
         <v>33</v>
@@ -14364,7 +14364,7 @@
         <v>32</v>
       </c>
       <c r="D600" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E600" s="2" t="s">
         <v>33</v>
@@ -14381,7 +14381,7 @@
         <v>32</v>
       </c>
       <c r="D601" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E601" s="2" t="s">
         <v>33</v>
@@ -14398,7 +14398,7 @@
         <v>32</v>
       </c>
       <c r="D602" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>33</v>
@@ -14415,7 +14415,7 @@
         <v>32</v>
       </c>
       <c r="D603" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E603" s="2" t="s">
         <v>33</v>
@@ -14432,7 +14432,7 @@
         <v>32</v>
       </c>
       <c r="D604" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E604" s="2" t="s">
         <v>33</v>
@@ -14449,7 +14449,7 @@
         <v>32</v>
       </c>
       <c r="D605" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E605" s="2" t="s">
         <v>33</v>
@@ -14466,7 +14466,7 @@
         <v>32</v>
       </c>
       <c r="D606" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>33</v>
@@ -14483,7 +14483,7 @@
         <v>32</v>
       </c>
       <c r="D607" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>33</v>
@@ -14500,7 +14500,7 @@
         <v>32</v>
       </c>
       <c r="D608" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E608" s="2" t="s">
         <v>33</v>
@@ -14534,7 +14534,7 @@
         <v>32</v>
       </c>
       <c r="D610" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>33</v>
@@ -14551,7 +14551,7 @@
         <v>32</v>
       </c>
       <c r="D611" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E611" s="2" t="s">
         <v>33</v>
@@ -14585,7 +14585,7 @@
         <v>32</v>
       </c>
       <c r="D613" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E613" s="2" t="s">
         <v>33</v>
@@ -14602,7 +14602,7 @@
         <v>32</v>
       </c>
       <c r="D614" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E614" s="2" t="s">
         <v>33</v>
@@ -14619,7 +14619,7 @@
         <v>32</v>
       </c>
       <c r="D615" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E615" s="2" t="s">
         <v>33</v>
@@ -14636,7 +14636,7 @@
         <v>32</v>
       </c>
       <c r="D616" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E616" s="2" t="s">
         <v>33</v>
@@ -14653,7 +14653,7 @@
         <v>32</v>
       </c>
       <c r="D617" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E617" s="2" t="s">
         <v>33</v>
@@ -14670,7 +14670,7 @@
         <v>32</v>
       </c>
       <c r="D618" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E618" s="2" t="s">
         <v>33</v>
@@ -14687,7 +14687,7 @@
         <v>32</v>
       </c>
       <c r="D619" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E619" s="2" t="s">
         <v>33</v>
@@ -14704,7 +14704,7 @@
         <v>32</v>
       </c>
       <c r="D620" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E620" s="2" t="s">
         <v>33</v>
@@ -14721,7 +14721,7 @@
         <v>32</v>
       </c>
       <c r="D621" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E621" s="2" t="s">
         <v>33</v>
@@ -14738,7 +14738,7 @@
         <v>32</v>
       </c>
       <c r="D622" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E622" s="2" t="s">
         <v>33</v>
@@ -14755,7 +14755,7 @@
         <v>32</v>
       </c>
       <c r="D623" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E623" s="2" t="s">
         <v>33</v>
@@ -14772,7 +14772,7 @@
         <v>32</v>
       </c>
       <c r="D624" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E624" s="2" t="s">
         <v>33</v>
@@ -14789,7 +14789,7 @@
         <v>32</v>
       </c>
       <c r="D625" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E625" s="2" t="s">
         <v>33</v>
@@ -14806,7 +14806,7 @@
         <v>32</v>
       </c>
       <c r="D626" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E626" s="2" t="s">
         <v>33</v>
@@ -14823,7 +14823,7 @@
         <v>32</v>
       </c>
       <c r="D627" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E627" s="2" t="s">
         <v>33</v>
@@ -14840,7 +14840,7 @@
         <v>32</v>
       </c>
       <c r="D628" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E628" s="2" t="s">
         <v>33</v>
@@ -14857,7 +14857,7 @@
         <v>32</v>
       </c>
       <c r="D629" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E629" s="2" t="s">
         <v>33</v>
@@ -14874,7 +14874,7 @@
         <v>32</v>
       </c>
       <c r="D630" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E630" s="2" t="s">
         <v>33</v>
@@ -14891,7 +14891,7 @@
         <v>32</v>
       </c>
       <c r="D631" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E631" s="2" t="s">
         <v>33</v>
@@ -14908,7 +14908,7 @@
         <v>32</v>
       </c>
       <c r="D632" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E632" s="2" t="s">
         <v>33</v>
@@ -14925,7 +14925,7 @@
         <v>32</v>
       </c>
       <c r="D633" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E633" s="2" t="s">
         <v>33</v>
@@ -14959,7 +14959,7 @@
         <v>32</v>
       </c>
       <c r="D635" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E635" s="2" t="s">
         <v>33</v>
@@ -14976,7 +14976,7 @@
         <v>32</v>
       </c>
       <c r="D636" s="2">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E636" s="2" t="s">
         <v>33</v>
@@ -14993,7 +14993,7 @@
         <v>32</v>
       </c>
       <c r="D637" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E637" s="2" t="s">
         <v>33</v>
@@ -15010,7 +15010,7 @@
         <v>32</v>
       </c>
       <c r="D638" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E638" s="2" t="s">
         <v>33</v>
@@ -15027,7 +15027,7 @@
         <v>32</v>
       </c>
       <c r="D639" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E639" s="2" t="s">
         <v>33</v>
@@ -15061,7 +15061,7 @@
         <v>32</v>
       </c>
       <c r="D641" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>33</v>
@@ -15095,7 +15095,7 @@
         <v>32</v>
       </c>
       <c r="D643" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E643" s="2" t="s">
         <v>33</v>
@@ -15112,7 +15112,7 @@
         <v>32</v>
       </c>
       <c r="D644" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E644" s="2" t="s">
         <v>33</v>
@@ -15146,7 +15146,7 @@
         <v>32</v>
       </c>
       <c r="D646" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E646" s="2" t="s">
         <v>33</v>
@@ -15163,7 +15163,7 @@
         <v>32</v>
       </c>
       <c r="D647" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E647" s="2" t="s">
         <v>33</v>
@@ -15180,7 +15180,7 @@
         <v>32</v>
       </c>
       <c r="D648" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E648" s="2" t="s">
         <v>33</v>
@@ -15197,7 +15197,7 @@
         <v>32</v>
       </c>
       <c r="D649" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E649" s="2" t="s">
         <v>33</v>
@@ -15214,7 +15214,7 @@
         <v>32</v>
       </c>
       <c r="D650" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E650" s="2" t="s">
         <v>33</v>
@@ -15231,7 +15231,7 @@
         <v>32</v>
       </c>
       <c r="D651" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E651" s="2" t="s">
         <v>33</v>
@@ -15248,7 +15248,7 @@
         <v>32</v>
       </c>
       <c r="D652" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E652" s="2" t="s">
         <v>33</v>
@@ -15265,7 +15265,7 @@
         <v>32</v>
       </c>
       <c r="D653" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E653" s="2" t="s">
         <v>33</v>
@@ -15282,7 +15282,7 @@
         <v>32</v>
       </c>
       <c r="D654" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E654" s="2" t="s">
         <v>33</v>
@@ -15299,7 +15299,7 @@
         <v>32</v>
       </c>
       <c r="D655" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E655" s="2" t="s">
         <v>33</v>
@@ -15316,7 +15316,7 @@
         <v>32</v>
       </c>
       <c r="D656" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E656" s="2" t="s">
         <v>33</v>
@@ -15333,7 +15333,7 @@
         <v>32</v>
       </c>
       <c r="D657" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E657" s="2" t="s">
         <v>33</v>
@@ -15350,7 +15350,7 @@
         <v>32</v>
       </c>
       <c r="D658" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E658" s="2" t="s">
         <v>33</v>
@@ -15367,7 +15367,7 @@
         <v>32</v>
       </c>
       <c r="D659" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E659" s="2" t="s">
         <v>33</v>
@@ -15384,7 +15384,7 @@
         <v>32</v>
       </c>
       <c r="D660" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E660" s="2" t="s">
         <v>33</v>
@@ -15418,7 +15418,7 @@
         <v>32</v>
       </c>
       <c r="D662" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E662" s="2" t="s">
         <v>33</v>
@@ -15435,7 +15435,7 @@
         <v>32</v>
       </c>
       <c r="D663" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E663" s="2" t="s">
         <v>33</v>
@@ -15452,7 +15452,7 @@
         <v>32</v>
       </c>
       <c r="D664" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E664" s="2" t="s">
         <v>33</v>
@@ -15469,7 +15469,7 @@
         <v>32</v>
       </c>
       <c r="D665" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E665" s="2" t="s">
         <v>33</v>
@@ -15486,7 +15486,7 @@
         <v>32</v>
       </c>
       <c r="D666" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E666" s="2" t="s">
         <v>33</v>
@@ -15503,7 +15503,7 @@
         <v>32</v>
       </c>
       <c r="D667" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E667" s="2" t="s">
         <v>33</v>
@@ -15537,7 +15537,7 @@
         <v>32</v>
       </c>
       <c r="D669" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E669" s="2" t="s">
         <v>33</v>
@@ -15554,7 +15554,7 @@
         <v>32</v>
       </c>
       <c r="D670" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E670" s="2" t="s">
         <v>33</v>
@@ -15571,7 +15571,7 @@
         <v>32</v>
       </c>
       <c r="D671" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E671" s="2" t="s">
         <v>33</v>
@@ -15588,7 +15588,7 @@
         <v>32</v>
       </c>
       <c r="D672" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E672" s="2" t="s">
         <v>33</v>
@@ -15605,7 +15605,7 @@
         <v>32</v>
       </c>
       <c r="D673" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E673" s="2" t="s">
         <v>33</v>
@@ -15622,7 +15622,7 @@
         <v>32</v>
       </c>
       <c r="D674" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E674" s="2" t="s">
         <v>33</v>
@@ -15656,7 +15656,7 @@
         <v>32</v>
       </c>
       <c r="D676" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E676" s="2" t="s">
         <v>33</v>
@@ -15673,7 +15673,7 @@
         <v>32</v>
       </c>
       <c r="D677" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E677" s="2" t="s">
         <v>33</v>
@@ -15690,7 +15690,7 @@
         <v>32</v>
       </c>
       <c r="D678" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E678" s="2" t="s">
         <v>33</v>
@@ -15707,7 +15707,7 @@
         <v>32</v>
       </c>
       <c r="D679" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E679" s="2" t="s">
         <v>33</v>
@@ -15724,7 +15724,7 @@
         <v>32</v>
       </c>
       <c r="D680" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E680" s="2" t="s">
         <v>33</v>
@@ -15741,7 +15741,7 @@
         <v>32</v>
       </c>
       <c r="D681" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E681" s="2" t="s">
         <v>33</v>
@@ -15758,7 +15758,7 @@
         <v>32</v>
       </c>
       <c r="D682" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E682" s="2" t="s">
         <v>33</v>
@@ -15775,7 +15775,7 @@
         <v>32</v>
       </c>
       <c r="D683" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E683" s="2" t="s">
         <v>33</v>
@@ -15792,7 +15792,7 @@
         <v>32</v>
       </c>
       <c r="D684" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E684" s="2" t="s">
         <v>33</v>
@@ -15826,7 +15826,7 @@
         <v>32</v>
       </c>
       <c r="D686" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E686" s="2" t="s">
         <v>33</v>
@@ -15843,7 +15843,7 @@
         <v>32</v>
       </c>
       <c r="D687" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E687" s="2" t="s">
         <v>33</v>
@@ -15860,7 +15860,7 @@
         <v>32</v>
       </c>
       <c r="D688" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E688" s="2" t="s">
         <v>33</v>
@@ -15877,7 +15877,7 @@
         <v>32</v>
       </c>
       <c r="D689" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E689" s="2" t="s">
         <v>33</v>
@@ -15894,7 +15894,7 @@
         <v>32</v>
       </c>
       <c r="D690" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E690" s="2" t="s">
         <v>33</v>
@@ -15911,7 +15911,7 @@
         <v>32</v>
       </c>
       <c r="D691" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E691" s="2" t="s">
         <v>33</v>
@@ -15945,7 +15945,7 @@
         <v>32</v>
       </c>
       <c r="D693" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E693" s="2" t="s">
         <v>33</v>
@@ -15962,7 +15962,7 @@
         <v>32</v>
       </c>
       <c r="D694" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E694" s="2" t="s">
         <v>33</v>
@@ -15979,7 +15979,7 @@
         <v>32</v>
       </c>
       <c r="D695" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E695" s="2" t="s">
         <v>33</v>
@@ -15996,7 +15996,7 @@
         <v>32</v>
       </c>
       <c r="D696" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E696" s="2" t="s">
         <v>33</v>
@@ -16013,7 +16013,7 @@
         <v>32</v>
       </c>
       <c r="D697" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E697" s="2" t="s">
         <v>33</v>
@@ -16030,7 +16030,7 @@
         <v>32</v>
       </c>
       <c r="D698" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E698" s="2" t="s">
         <v>33</v>
@@ -16047,7 +16047,7 @@
         <v>32</v>
       </c>
       <c r="D699" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E699" s="2" t="s">
         <v>33</v>
@@ -16064,7 +16064,7 @@
         <v>32</v>
       </c>
       <c r="D700" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E700" s="2" t="s">
         <v>33</v>
@@ -16081,7 +16081,7 @@
         <v>32</v>
       </c>
       <c r="D701" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E701" s="2" t="s">
         <v>33</v>
@@ -16098,7 +16098,7 @@
         <v>32</v>
       </c>
       <c r="D702" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E702" s="2" t="s">
         <v>33</v>
@@ -16115,7 +16115,7 @@
         <v>32</v>
       </c>
       <c r="D703" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E703" s="2" t="s">
         <v>33</v>
@@ -16132,7 +16132,7 @@
         <v>32</v>
       </c>
       <c r="D704" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E704" s="2" t="s">
         <v>33</v>
@@ -16149,7 +16149,7 @@
         <v>32</v>
       </c>
       <c r="D705" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E705" s="2" t="s">
         <v>33</v>
@@ -16166,7 +16166,7 @@
         <v>32</v>
       </c>
       <c r="D706" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E706" s="2" t="s">
         <v>33</v>
@@ -16183,7 +16183,7 @@
         <v>32</v>
       </c>
       <c r="D707" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E707" s="2" t="s">
         <v>33</v>
@@ -16217,7 +16217,7 @@
         <v>32</v>
       </c>
       <c r="D709" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E709" s="2" t="s">
         <v>33</v>
@@ -16234,7 +16234,7 @@
         <v>32</v>
       </c>
       <c r="D710" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E710" s="2" t="s">
         <v>33</v>
@@ -16251,7 +16251,7 @@
         <v>32</v>
       </c>
       <c r="D711" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E711" s="2" t="s">
         <v>33</v>
@@ -16268,7 +16268,7 @@
         <v>32</v>
       </c>
       <c r="D712" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E712" s="2" t="s">
         <v>33</v>
@@ -16285,7 +16285,7 @@
         <v>32</v>
       </c>
       <c r="D713" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E713" s="2" t="s">
         <v>33</v>
@@ -16302,7 +16302,7 @@
         <v>32</v>
       </c>
       <c r="D714" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E714" s="2" t="s">
         <v>33</v>
@@ -16319,7 +16319,7 @@
         <v>32</v>
       </c>
       <c r="D715" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E715" s="2" t="s">
         <v>33</v>
@@ -16336,7 +16336,7 @@
         <v>32</v>
       </c>
       <c r="D716" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E716" s="2" t="s">
         <v>33</v>
@@ -16370,7 +16370,7 @@
         <v>32</v>
       </c>
       <c r="D718" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E718" s="2" t="s">
         <v>33</v>
@@ -16387,7 +16387,7 @@
         <v>32</v>
       </c>
       <c r="D719" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E719" s="2" t="s">
         <v>33</v>
@@ -16404,7 +16404,7 @@
         <v>32</v>
       </c>
       <c r="D720" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E720" s="2" t="s">
         <v>33</v>
@@ -16421,7 +16421,7 @@
         <v>32</v>
       </c>
       <c r="D721" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E721" s="2" t="s">
         <v>33</v>
@@ -16455,7 +16455,7 @@
         <v>32</v>
       </c>
       <c r="D723" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E723" s="2" t="s">
         <v>33</v>
@@ -16472,7 +16472,7 @@
         <v>32</v>
       </c>
       <c r="D724" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E724" s="2" t="s">
         <v>33</v>
@@ -16489,7 +16489,7 @@
         <v>32</v>
       </c>
       <c r="D725" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E725" s="2" t="s">
         <v>33</v>
@@ -16506,7 +16506,7 @@
         <v>32</v>
       </c>
       <c r="D726" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E726" s="2" t="s">
         <v>33</v>
@@ -16523,7 +16523,7 @@
         <v>32</v>
       </c>
       <c r="D727" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E727" s="2" t="s">
         <v>33</v>
@@ -16540,7 +16540,7 @@
         <v>32</v>
       </c>
       <c r="D728" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E728" s="2" t="s">
         <v>33</v>
@@ -16557,7 +16557,7 @@
         <v>32</v>
       </c>
       <c r="D729" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E729" s="2" t="s">
         <v>33</v>
@@ -16574,7 +16574,7 @@
         <v>32</v>
       </c>
       <c r="D730" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E730" s="2" t="s">
         <v>33</v>
@@ -16591,7 +16591,7 @@
         <v>32</v>
       </c>
       <c r="D731" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E731" s="2" t="s">
         <v>33</v>
@@ -16608,7 +16608,7 @@
         <v>32</v>
       </c>
       <c r="D732" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E732" s="2" t="s">
         <v>33</v>
@@ -16642,7 +16642,7 @@
         <v>32</v>
       </c>
       <c r="D734" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E734" s="2" t="s">
         <v>33</v>
@@ -16659,7 +16659,7 @@
         <v>32</v>
       </c>
       <c r="D735" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E735" s="2" t="s">
         <v>33</v>
@@ -16676,7 +16676,7 @@
         <v>32</v>
       </c>
       <c r="D736" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E736" s="2" t="s">
         <v>33</v>
@@ -16693,7 +16693,7 @@
         <v>32</v>
       </c>
       <c r="D737" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E737" s="2" t="s">
         <v>33</v>
@@ -16710,7 +16710,7 @@
         <v>32</v>
       </c>
       <c r="D738" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E738" s="2" t="s">
         <v>33</v>
@@ -16727,7 +16727,7 @@
         <v>32</v>
       </c>
       <c r="D739" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E739" s="2" t="s">
         <v>33</v>
@@ -16744,7 +16744,7 @@
         <v>32</v>
       </c>
       <c r="D740" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E740" s="2" t="s">
         <v>33</v>
@@ -16761,7 +16761,7 @@
         <v>32</v>
       </c>
       <c r="D741" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E741" s="2" t="s">
         <v>33</v>
@@ -16778,7 +16778,7 @@
         <v>32</v>
       </c>
       <c r="D742" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E742" s="2" t="s">
         <v>33</v>
@@ -16795,7 +16795,7 @@
         <v>32</v>
       </c>
       <c r="D743" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E743" s="2" t="s">
         <v>33</v>
@@ -16812,7 +16812,7 @@
         <v>32</v>
       </c>
       <c r="D744" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E744" s="2" t="s">
         <v>33</v>
@@ -16846,7 +16846,7 @@
         <v>32</v>
       </c>
       <c r="D746" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E746" s="2" t="s">
         <v>33</v>
@@ -16863,7 +16863,7 @@
         <v>32</v>
       </c>
       <c r="D747" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E747" s="2" t="s">
         <v>33</v>
@@ -16880,7 +16880,7 @@
         <v>32</v>
       </c>
       <c r="D748" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E748" s="2" t="s">
         <v>33</v>
@@ -16897,7 +16897,7 @@
         <v>32</v>
       </c>
       <c r="D749" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E749" s="2" t="s">
         <v>33</v>
@@ -16914,7 +16914,7 @@
         <v>32</v>
       </c>
       <c r="D750" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E750" s="2" t="s">
         <v>33</v>
@@ -16931,7 +16931,7 @@
         <v>32</v>
       </c>
       <c r="D751" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E751" s="2" t="s">
         <v>33</v>
@@ -16948,7 +16948,7 @@
         <v>32</v>
       </c>
       <c r="D752" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E752" s="2" t="s">
         <v>33</v>
@@ -16965,7 +16965,7 @@
         <v>32</v>
       </c>
       <c r="D753" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E753" s="2" t="s">
         <v>33</v>
@@ -16982,7 +16982,7 @@
         <v>32</v>
       </c>
       <c r="D754" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E754" s="2" t="s">
         <v>33</v>
@@ -16999,7 +16999,7 @@
         <v>32</v>
       </c>
       <c r="D755" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E755" s="2" t="s">
         <v>33</v>
@@ -17016,7 +17016,7 @@
         <v>32</v>
       </c>
       <c r="D756" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E756" s="2" t="s">
         <v>33</v>
@@ -17033,7 +17033,7 @@
         <v>32</v>
       </c>
       <c r="D757" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E757" s="2" t="s">
         <v>33</v>
@@ -17067,7 +17067,7 @@
         <v>32</v>
       </c>
       <c r="D759" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E759" s="2" t="s">
         <v>33</v>
@@ -17101,7 +17101,7 @@
         <v>32</v>
       </c>
       <c r="D761" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E761" s="2" t="s">
         <v>33</v>
@@ -17118,7 +17118,7 @@
         <v>32</v>
       </c>
       <c r="D762" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E762" s="2" t="s">
         <v>33</v>
@@ -17135,7 +17135,7 @@
         <v>32</v>
       </c>
       <c r="D763" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E763" s="2" t="s">
         <v>33</v>
@@ -17169,7 +17169,7 @@
         <v>32</v>
       </c>
       <c r="D765" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E765" s="2" t="s">
         <v>33</v>
@@ -17186,7 +17186,7 @@
         <v>32</v>
       </c>
       <c r="D766" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E766" s="2" t="s">
         <v>33</v>
@@ -17203,7 +17203,7 @@
         <v>32</v>
       </c>
       <c r="D767" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E767" s="2" t="s">
         <v>33</v>
@@ -17220,7 +17220,7 @@
         <v>32</v>
       </c>
       <c r="D768" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E768" s="2" t="s">
         <v>33</v>
@@ -17237,7 +17237,7 @@
         <v>32</v>
       </c>
       <c r="D769" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E769" s="2" t="s">
         <v>33</v>
@@ -17254,7 +17254,7 @@
         <v>32</v>
       </c>
       <c r="D770" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E770" s="2" t="s">
         <v>33</v>
@@ -17271,7 +17271,7 @@
         <v>32</v>
       </c>
       <c r="D771" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E771" s="2" t="s">
         <v>33</v>
@@ -17288,7 +17288,7 @@
         <v>32</v>
       </c>
       <c r="D772" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E772" s="2" t="s">
         <v>33</v>
@@ -17305,7 +17305,7 @@
         <v>32</v>
       </c>
       <c r="D773" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E773" s="2" t="s">
         <v>33</v>
@@ -17322,7 +17322,7 @@
         <v>32</v>
       </c>
       <c r="D774" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E774" s="2" t="s">
         <v>33</v>
@@ -17339,7 +17339,7 @@
         <v>32</v>
       </c>
       <c r="D775" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E775" s="2" t="s">
         <v>33</v>
@@ -17356,7 +17356,7 @@
         <v>32</v>
       </c>
       <c r="D776" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E776" s="2" t="s">
         <v>33</v>
@@ -17373,7 +17373,7 @@
         <v>32</v>
       </c>
       <c r="D777" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E777" s="2" t="s">
         <v>33</v>
@@ -17390,7 +17390,7 @@
         <v>32</v>
       </c>
       <c r="D778" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E778" s="2" t="s">
         <v>33</v>
@@ -17407,7 +17407,7 @@
         <v>32</v>
       </c>
       <c r="D779" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E779" s="2" t="s">
         <v>33</v>
@@ -17424,7 +17424,7 @@
         <v>32</v>
       </c>
       <c r="D780" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E780" s="2" t="s">
         <v>33</v>
@@ -17441,7 +17441,7 @@
         <v>32</v>
       </c>
       <c r="D781" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E781" s="2" t="s">
         <v>33</v>
@@ -17458,7 +17458,7 @@
         <v>32</v>
       </c>
       <c r="D782" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E782" s="2" t="s">
         <v>33</v>
@@ -17475,7 +17475,7 @@
         <v>32</v>
       </c>
       <c r="D783" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E783" s="2" t="s">
         <v>33</v>
@@ -17492,7 +17492,7 @@
         <v>32</v>
       </c>
       <c r="D784" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E784" s="2" t="s">
         <v>33</v>
@@ -17509,7 +17509,7 @@
         <v>32</v>
       </c>
       <c r="D785" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E785" s="2" t="s">
         <v>33</v>
@@ -17526,7 +17526,7 @@
         <v>32</v>
       </c>
       <c r="D786" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E786" s="2" t="s">
         <v>33</v>
@@ -17543,7 +17543,7 @@
         <v>32</v>
       </c>
       <c r="D787" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E787" s="2" t="s">
         <v>33</v>
@@ -17560,7 +17560,7 @@
         <v>32</v>
       </c>
       <c r="D788" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E788" s="2" t="s">
         <v>33</v>
@@ -17577,7 +17577,7 @@
         <v>32</v>
       </c>
       <c r="D789" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E789" s="2" t="s">
         <v>33</v>
@@ -17594,7 +17594,7 @@
         <v>32</v>
       </c>
       <c r="D790" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E790" s="2" t="s">
         <v>33</v>
@@ -17611,7 +17611,7 @@
         <v>32</v>
       </c>
       <c r="D791" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E791" s="2" t="s">
         <v>33</v>
@@ -17628,7 +17628,7 @@
         <v>32</v>
       </c>
       <c r="D792" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E792" s="2" t="s">
         <v>33</v>
@@ -17645,7 +17645,7 @@
         <v>32</v>
       </c>
       <c r="D793" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="E793" s="2" t="s">
         <v>33</v>
@@ -17662,7 +17662,7 @@
         <v>32</v>
       </c>
       <c r="D794" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E794" s="2" t="s">
         <v>33</v>
@@ -17679,7 +17679,7 @@
         <v>32</v>
       </c>
       <c r="D795" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E795" s="2" t="s">
         <v>33</v>
@@ -17696,7 +17696,7 @@
         <v>32</v>
       </c>
       <c r="D796" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E796" s="2" t="s">
         <v>33</v>
@@ -17713,7 +17713,7 @@
         <v>32</v>
       </c>
       <c r="D797" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E797" s="2" t="s">
         <v>33</v>
@@ -17730,7 +17730,7 @@
         <v>32</v>
       </c>
       <c r="D798" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E798" s="2" t="s">
         <v>33</v>
@@ -17747,7 +17747,7 @@
         <v>32</v>
       </c>
       <c r="D799" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E799" s="2" t="s">
         <v>33</v>
@@ -17764,7 +17764,7 @@
         <v>32</v>
       </c>
       <c r="D800" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E800" s="2" t="s">
         <v>33</v>
@@ -17781,7 +17781,7 @@
         <v>32</v>
       </c>
       <c r="D801" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E801" s="2" t="s">
         <v>33</v>
@@ -17815,7 +17815,7 @@
         <v>32</v>
       </c>
       <c r="D803" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E803" s="2" t="s">
         <v>33</v>
@@ -17832,7 +17832,7 @@
         <v>32</v>
       </c>
       <c r="D804" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E804" s="2" t="s">
         <v>33</v>
@@ -17849,7 +17849,7 @@
         <v>32</v>
       </c>
       <c r="D805" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E805" s="2" t="s">
         <v>33</v>
@@ -17866,7 +17866,7 @@
         <v>32</v>
       </c>
       <c r="D806" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E806" s="2" t="s">
         <v>33</v>
@@ -17883,7 +17883,7 @@
         <v>32</v>
       </c>
       <c r="D807" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E807" s="2" t="s">
         <v>33</v>
@@ -17900,7 +17900,7 @@
         <v>32</v>
       </c>
       <c r="D808" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E808" s="2" t="s">
         <v>33</v>
@@ -17917,7 +17917,7 @@
         <v>32</v>
       </c>
       <c r="D809" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E809" s="2" t="s">
         <v>33</v>
@@ -17934,7 +17934,7 @@
         <v>32</v>
       </c>
       <c r="D810" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E810" s="2" t="s">
         <v>33</v>
@@ -17951,7 +17951,7 @@
         <v>32</v>
       </c>
       <c r="D811" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E811" s="2" t="s">
         <v>33</v>
@@ -17968,7 +17968,7 @@
         <v>32</v>
       </c>
       <c r="D812" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E812" s="2" t="s">
         <v>33</v>
@@ -17985,7 +17985,7 @@
         <v>32</v>
       </c>
       <c r="D813" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E813" s="2" t="s">
         <v>33</v>
@@ -18002,7 +18002,7 @@
         <v>32</v>
       </c>
       <c r="D814" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E814" s="2" t="s">
         <v>33</v>
@@ -18019,7 +18019,7 @@
         <v>32</v>
       </c>
       <c r="D815" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E815" s="2" t="s">
         <v>33</v>
@@ -18036,7 +18036,7 @@
         <v>32</v>
       </c>
       <c r="D816" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E816" s="2" t="s">
         <v>33</v>
@@ -18070,7 +18070,7 @@
         <v>32</v>
       </c>
       <c r="D818" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E818" s="2" t="s">
         <v>33</v>
@@ -18087,7 +18087,7 @@
         <v>32</v>
       </c>
       <c r="D819" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E819" s="2" t="s">
         <v>33</v>
@@ -18104,7 +18104,7 @@
         <v>32</v>
       </c>
       <c r="D820" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E820" s="2" t="s">
         <v>33</v>
@@ -18121,7 +18121,7 @@
         <v>32</v>
       </c>
       <c r="D821" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E821" s="2" t="s">
         <v>33</v>
@@ -18138,7 +18138,7 @@
         <v>32</v>
       </c>
       <c r="D822" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E822" s="2" t="s">
         <v>33</v>
@@ -18155,7 +18155,7 @@
         <v>32</v>
       </c>
       <c r="D823" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E823" s="2" t="s">
         <v>33</v>
@@ -18172,7 +18172,7 @@
         <v>32</v>
       </c>
       <c r="D824" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E824" s="2" t="s">
         <v>33</v>
@@ -18189,7 +18189,7 @@
         <v>32</v>
       </c>
       <c r="D825" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E825" s="2" t="s">
         <v>33</v>
@@ -18206,7 +18206,7 @@
         <v>32</v>
       </c>
       <c r="D826" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E826" s="2" t="s">
         <v>33</v>
@@ -18223,7 +18223,7 @@
         <v>32</v>
       </c>
       <c r="D827" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E827" s="2" t="s">
         <v>33</v>
@@ -18240,7 +18240,7 @@
         <v>32</v>
       </c>
       <c r="D828" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E828" s="2" t="s">
         <v>33</v>
@@ -18257,7 +18257,7 @@
         <v>32</v>
       </c>
       <c r="D829" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E829" s="2" t="s">
         <v>33</v>
@@ -18274,7 +18274,7 @@
         <v>32</v>
       </c>
       <c r="D830" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E830" s="2" t="s">
         <v>33</v>
@@ -18291,7 +18291,7 @@
         <v>32</v>
       </c>
       <c r="D831" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E831" s="2" t="s">
         <v>33</v>
@@ -18325,7 +18325,7 @@
         <v>32</v>
       </c>
       <c r="D833" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E833" s="2" t="s">
         <v>33</v>
@@ -18342,7 +18342,7 @@
         <v>32</v>
       </c>
       <c r="D834" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E834" s="2" t="s">
         <v>33</v>
@@ -18359,7 +18359,7 @@
         <v>32</v>
       </c>
       <c r="D835" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E835" s="2" t="s">
         <v>33</v>
@@ -18376,7 +18376,7 @@
         <v>32</v>
       </c>
       <c r="D836" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E836" s="2" t="s">
         <v>33</v>
@@ -18393,7 +18393,7 @@
         <v>32</v>
       </c>
       <c r="D837" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E837" s="2" t="s">
         <v>33</v>
@@ -18410,7 +18410,7 @@
         <v>32</v>
       </c>
       <c r="D838" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E838" s="2" t="s">
         <v>33</v>
@@ -18427,7 +18427,7 @@
         <v>32</v>
       </c>
       <c r="D839" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E839" s="2" t="s">
         <v>33</v>
@@ -18444,7 +18444,7 @@
         <v>32</v>
       </c>
       <c r="D840" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E840" s="2" t="s">
         <v>33</v>
@@ -18461,7 +18461,7 @@
         <v>32</v>
       </c>
       <c r="D841" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E841" s="2" t="s">
         <v>33</v>
@@ -18478,7 +18478,7 @@
         <v>32</v>
       </c>
       <c r="D842" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E842" s="2" t="s">
         <v>33</v>
@@ -18495,7 +18495,7 @@
         <v>32</v>
       </c>
       <c r="D843" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E843" s="2" t="s">
         <v>33</v>
@@ -18512,7 +18512,7 @@
         <v>32</v>
       </c>
       <c r="D844" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E844" s="2" t="s">
         <v>33</v>
@@ -18529,7 +18529,7 @@
         <v>32</v>
       </c>
       <c r="D845" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E845" s="2" t="s">
         <v>33</v>
@@ -18546,7 +18546,7 @@
         <v>32</v>
       </c>
       <c r="D846" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E846" s="2" t="s">
         <v>33</v>
@@ -18563,7 +18563,7 @@
         <v>32</v>
       </c>
       <c r="D847" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E847" s="2" t="s">
         <v>33</v>
@@ -18580,7 +18580,7 @@
         <v>32</v>
       </c>
       <c r="D848" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E848" s="2" t="s">
         <v>33</v>
@@ -18597,7 +18597,7 @@
         <v>32</v>
       </c>
       <c r="D849" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E849" s="2" t="s">
         <v>33</v>
@@ -18614,7 +18614,7 @@
         <v>32</v>
       </c>
       <c r="D850" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E850" s="2" t="s">
         <v>33</v>
@@ -18631,7 +18631,7 @@
         <v>32</v>
       </c>
       <c r="D851" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E851" s="2" t="s">
         <v>33</v>
@@ -18648,7 +18648,7 @@
         <v>32</v>
       </c>
       <c r="D852" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E852" s="2" t="s">
         <v>33</v>
@@ -18665,7 +18665,7 @@
         <v>32</v>
       </c>
       <c r="D853" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E853" s="2" t="s">
         <v>33</v>
@@ -18682,7 +18682,7 @@
         <v>32</v>
       </c>
       <c r="D854" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E854" s="2" t="s">
         <v>33</v>
@@ -18699,7 +18699,7 @@
         <v>32</v>
       </c>
       <c r="D855" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E855" s="2" t="s">
         <v>33</v>
@@ -18733,7 +18733,7 @@
         <v>32</v>
       </c>
       <c r="D857" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E857" s="2" t="s">
         <v>33</v>
@@ -18750,7 +18750,7 @@
         <v>32</v>
       </c>
       <c r="D858" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E858" s="2" t="s">
         <v>33</v>
@@ -18767,7 +18767,7 @@
         <v>32</v>
       </c>
       <c r="D859" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E859" s="2" t="s">
         <v>33</v>
@@ -18784,7 +18784,7 @@
         <v>32</v>
       </c>
       <c r="D860" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E860" s="2" t="s">
         <v>33</v>
@@ -18801,7 +18801,7 @@
         <v>32</v>
       </c>
       <c r="D861" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E861" s="2" t="s">
         <v>33</v>
@@ -18818,7 +18818,7 @@
         <v>32</v>
       </c>
       <c r="D862" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E862" s="2" t="s">
         <v>33</v>
@@ -18835,7 +18835,7 @@
         <v>32</v>
       </c>
       <c r="D863" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E863" s="2" t="s">
         <v>33</v>
@@ -18852,7 +18852,7 @@
         <v>32</v>
       </c>
       <c r="D864" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E864" s="2" t="s">
         <v>33</v>
@@ -18869,7 +18869,7 @@
         <v>32</v>
       </c>
       <c r="D865" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E865" s="2" t="s">
         <v>33</v>
@@ -18886,7 +18886,7 @@
         <v>32</v>
       </c>
       <c r="D866" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E866" s="2" t="s">
         <v>33</v>
@@ -18903,7 +18903,7 @@
         <v>32</v>
       </c>
       <c r="D867" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E867" s="2" t="s">
         <v>33</v>
@@ -18920,7 +18920,7 @@
         <v>32</v>
       </c>
       <c r="D868" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E868" s="2" t="s">
         <v>33</v>
@@ -18937,7 +18937,7 @@
         <v>32</v>
       </c>
       <c r="D869" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E869" s="2" t="s">
         <v>33</v>
@@ -18954,7 +18954,7 @@
         <v>32</v>
       </c>
       <c r="D870" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E870" s="2" t="s">
         <v>33</v>
@@ -18971,7 +18971,7 @@
         <v>32</v>
       </c>
       <c r="D871" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E871" s="2" t="s">
         <v>33</v>
@@ -19005,7 +19005,7 @@
         <v>32</v>
       </c>
       <c r="D873" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E873" s="2" t="s">
         <v>33</v>
@@ -19022,7 +19022,7 @@
         <v>32</v>
       </c>
       <c r="D874" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E874" s="2" t="s">
         <v>33</v>
@@ -19039,7 +19039,7 @@
         <v>32</v>
       </c>
       <c r="D875" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E875" s="2" t="s">
         <v>33</v>
@@ -19056,7 +19056,7 @@
         <v>32</v>
       </c>
       <c r="D876" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E876" s="2" t="s">
         <v>33</v>
@@ -19073,7 +19073,7 @@
         <v>32</v>
       </c>
       <c r="D877" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E877" s="2" t="s">
         <v>33</v>
@@ -19090,7 +19090,7 @@
         <v>32</v>
       </c>
       <c r="D878" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E878" s="2" t="s">
         <v>33</v>
@@ -19107,7 +19107,7 @@
         <v>32</v>
       </c>
       <c r="D879" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E879" s="2" t="s">
         <v>33</v>
@@ -19124,7 +19124,7 @@
         <v>32</v>
       </c>
       <c r="D880" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E880" s="2" t="s">
         <v>33</v>
@@ -19141,7 +19141,7 @@
         <v>32</v>
       </c>
       <c r="D881" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E881" s="2" t="s">
         <v>33</v>
@@ -19158,7 +19158,7 @@
         <v>32</v>
       </c>
       <c r="D882" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E882" s="2" t="s">
         <v>33</v>
@@ -19192,7 +19192,7 @@
         <v>32</v>
       </c>
       <c r="D884" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E884" s="2" t="s">
         <v>33</v>
@@ -19209,7 +19209,7 @@
         <v>32</v>
       </c>
       <c r="D885" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E885" s="2" t="s">
         <v>33</v>
@@ -19226,7 +19226,7 @@
         <v>32</v>
       </c>
       <c r="D886" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E886" s="2" t="s">
         <v>33</v>
@@ -19243,7 +19243,7 @@
         <v>32</v>
       </c>
       <c r="D887" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E887" s="2" t="s">
         <v>33</v>
@@ -19260,7 +19260,7 @@
         <v>32</v>
       </c>
       <c r="D888" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E888" s="2" t="s">
         <v>33</v>
@@ -19277,7 +19277,7 @@
         <v>32</v>
       </c>
       <c r="D889" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E889" s="2" t="s">
         <v>33</v>
@@ -19294,7 +19294,7 @@
         <v>32</v>
       </c>
       <c r="D890" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E890" s="2" t="s">
         <v>33</v>
@@ -19311,7 +19311,7 @@
         <v>32</v>
       </c>
       <c r="D891" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E891" s="2" t="s">
         <v>33</v>
@@ -19328,7 +19328,7 @@
         <v>32</v>
       </c>
       <c r="D892" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E892" s="2" t="s">
         <v>33</v>
@@ -19345,7 +19345,7 @@
         <v>32</v>
       </c>
       <c r="D893" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E893" s="2" t="s">
         <v>33</v>
@@ -19362,7 +19362,7 @@
         <v>32</v>
       </c>
       <c r="D894" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E894" s="2" t="s">
         <v>33</v>
@@ -19379,7 +19379,7 @@
         <v>32</v>
       </c>
       <c r="D895" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E895" s="2" t="s">
         <v>33</v>
@@ -19396,7 +19396,7 @@
         <v>32</v>
       </c>
       <c r="D896" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E896" s="2" t="s">
         <v>33</v>
@@ -19413,7 +19413,7 @@
         <v>32</v>
       </c>
       <c r="D897" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E897" s="2" t="s">
         <v>33</v>
@@ -19430,7 +19430,7 @@
         <v>32</v>
       </c>
       <c r="D898" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E898" s="2" t="s">
         <v>33</v>
@@ -19447,7 +19447,7 @@
         <v>32</v>
       </c>
       <c r="D899" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E899" s="2" t="s">
         <v>33</v>
@@ -19464,7 +19464,7 @@
         <v>32</v>
       </c>
       <c r="D900" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E900" s="2" t="s">
         <v>33</v>
@@ -19481,7 +19481,7 @@
         <v>32</v>
       </c>
       <c r="D901" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E901" s="2" t="s">
         <v>33</v>
@@ -19498,7 +19498,7 @@
         <v>32</v>
       </c>
       <c r="D902" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E902" s="2" t="s">
         <v>33</v>
@@ -19515,7 +19515,7 @@
         <v>32</v>
       </c>
       <c r="D903" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E903" s="2" t="s">
         <v>33</v>
@@ -19532,7 +19532,7 @@
         <v>32</v>
       </c>
       <c r="D904" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E904" s="2" t="s">
         <v>33</v>
@@ -19549,7 +19549,7 @@
         <v>32</v>
       </c>
       <c r="D905" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E905" s="2" t="s">
         <v>33</v>
@@ -19566,7 +19566,7 @@
         <v>32</v>
       </c>
       <c r="D906" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E906" s="2" t="s">
         <v>33</v>
@@ -19583,7 +19583,7 @@
         <v>32</v>
       </c>
       <c r="D907" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E907" s="2" t="s">
         <v>33</v>
@@ -19600,7 +19600,7 @@
         <v>32</v>
       </c>
       <c r="D908" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E908" s="2" t="s">
         <v>33</v>
@@ -19617,7 +19617,7 @@
         <v>32</v>
       </c>
       <c r="D909" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E909" s="2" t="s">
         <v>33</v>
@@ -19651,7 +19651,7 @@
         <v>32</v>
       </c>
       <c r="D911" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E911" s="2" t="s">
         <v>33</v>
@@ -19668,7 +19668,7 @@
         <v>32</v>
       </c>
       <c r="D912" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E912" s="2" t="s">
         <v>33</v>
@@ -19685,7 +19685,7 @@
         <v>32</v>
       </c>
       <c r="D913" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E913" s="2" t="s">
         <v>33</v>
@@ -19702,7 +19702,7 @@
         <v>32</v>
       </c>
       <c r="D914" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E914" s="2" t="s">
         <v>33</v>
@@ -19719,7 +19719,7 @@
         <v>32</v>
       </c>
       <c r="D915" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E915" s="2" t="s">
         <v>33</v>
@@ -19736,7 +19736,7 @@
         <v>32</v>
       </c>
       <c r="D916" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E916" s="2" t="s">
         <v>33</v>
@@ -19753,7 +19753,7 @@
         <v>32</v>
       </c>
       <c r="D917" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E917" s="2" t="s">
         <v>33</v>
@@ -19770,7 +19770,7 @@
         <v>32</v>
       </c>
       <c r="D918" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E918" s="2" t="s">
         <v>33</v>
@@ -19787,7 +19787,7 @@
         <v>32</v>
       </c>
       <c r="D919" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E919" s="2" t="s">
         <v>33</v>
@@ -19804,7 +19804,7 @@
         <v>32</v>
       </c>
       <c r="D920" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E920" s="2" t="s">
         <v>33</v>
@@ -19821,7 +19821,7 @@
         <v>32</v>
       </c>
       <c r="D921" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E921" s="2" t="s">
         <v>33</v>
@@ -19838,7 +19838,7 @@
         <v>32</v>
       </c>
       <c r="D922" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E922" s="2" t="s">
         <v>33</v>
@@ -19855,7 +19855,7 @@
         <v>32</v>
       </c>
       <c r="D923" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E923" s="2" t="s">
         <v>33</v>
@@ -19872,7 +19872,7 @@
         <v>32</v>
       </c>
       <c r="D924" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E924" s="2" t="s">
         <v>33</v>
@@ -19889,7 +19889,7 @@
         <v>32</v>
       </c>
       <c r="D925" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E925" s="2" t="s">
         <v>33</v>
@@ -19906,7 +19906,7 @@
         <v>32</v>
       </c>
       <c r="D926" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E926" s="2" t="s">
         <v>33</v>
@@ -19940,7 +19940,7 @@
         <v>32</v>
       </c>
       <c r="D928" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E928" s="2" t="s">
         <v>33</v>
@@ -19957,7 +19957,7 @@
         <v>32</v>
       </c>
       <c r="D929" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E929" s="2" t="s">
         <v>33</v>
@@ -19974,7 +19974,7 @@
         <v>32</v>
       </c>
       <c r="D930" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E930" s="2" t="s">
         <v>33</v>
@@ -19991,7 +19991,7 @@
         <v>32</v>
       </c>
       <c r="D931" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E931" s="2" t="s">
         <v>33</v>
@@ -20008,7 +20008,7 @@
         <v>32</v>
       </c>
       <c r="D932" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E932" s="2" t="s">
         <v>33</v>
@@ -20025,7 +20025,7 @@
         <v>32</v>
       </c>
       <c r="D933" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E933" s="2" t="s">
         <v>33</v>
@@ -20042,7 +20042,7 @@
         <v>32</v>
       </c>
       <c r="D934" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E934" s="2" t="s">
         <v>33</v>
@@ -20059,7 +20059,7 @@
         <v>32</v>
       </c>
       <c r="D935" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E935" s="2" t="s">
         <v>33</v>
@@ -20076,7 +20076,7 @@
         <v>32</v>
       </c>
       <c r="D936" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E936" s="2" t="s">
         <v>33</v>
@@ -20093,7 +20093,7 @@
         <v>32</v>
       </c>
       <c r="D937" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E937" s="2" t="s">
         <v>33</v>
@@ -20110,7 +20110,7 @@
         <v>32</v>
       </c>
       <c r="D938" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E938" s="2" t="s">
         <v>33</v>
@@ -20127,7 +20127,7 @@
         <v>32</v>
       </c>
       <c r="D939" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E939" s="2" t="s">
         <v>33</v>
@@ -20144,7 +20144,7 @@
         <v>32</v>
       </c>
       <c r="D940" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E940" s="2" t="s">
         <v>33</v>
@@ -20161,7 +20161,7 @@
         <v>32</v>
       </c>
       <c r="D941" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E941" s="2" t="s">
         <v>33</v>
@@ -20178,7 +20178,7 @@
         <v>32</v>
       </c>
       <c r="D942" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E942" s="2" t="s">
         <v>33</v>
@@ -20195,7 +20195,7 @@
         <v>32</v>
       </c>
       <c r="D943" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E943" s="2" t="s">
         <v>33</v>
@@ -20212,7 +20212,7 @@
         <v>32</v>
       </c>
       <c r="D944" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E944" s="2" t="s">
         <v>33</v>
@@ -20229,7 +20229,7 @@
         <v>32</v>
       </c>
       <c r="D945" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E945" s="2" t="s">
         <v>33</v>
@@ -20246,7 +20246,7 @@
         <v>32</v>
       </c>
       <c r="D946" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E946" s="2" t="s">
         <v>33</v>
@@ -20263,7 +20263,7 @@
         <v>32</v>
       </c>
       <c r="D947" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E947" s="2" t="s">
         <v>33</v>
@@ -20280,7 +20280,7 @@
         <v>32</v>
       </c>
       <c r="D948" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E948" s="2" t="s">
         <v>33</v>
@@ -20297,7 +20297,7 @@
         <v>32</v>
       </c>
       <c r="D949" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E949" s="2" t="s">
         <v>33</v>
@@ -20314,7 +20314,7 @@
         <v>32</v>
       </c>
       <c r="D950" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E950" s="2" t="s">
         <v>33</v>
@@ -20348,7 +20348,7 @@
         <v>32</v>
       </c>
       <c r="D952" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E952" s="2" t="s">
         <v>33</v>
@@ -20365,7 +20365,7 @@
         <v>32</v>
       </c>
       <c r="D953" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E953" s="2" t="s">
         <v>33</v>
@@ -20382,7 +20382,7 @@
         <v>32</v>
       </c>
       <c r="D954" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E954" s="2" t="s">
         <v>33</v>
@@ -20399,7 +20399,7 @@
         <v>32</v>
       </c>
       <c r="D955" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E955" s="2" t="s">
         <v>33</v>
@@ -20416,7 +20416,7 @@
         <v>32</v>
       </c>
       <c r="D956" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E956" s="2" t="s">
         <v>33</v>
@@ -20433,7 +20433,7 @@
         <v>32</v>
       </c>
       <c r="D957" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E957" s="2" t="s">
         <v>33</v>
@@ -20450,7 +20450,7 @@
         <v>32</v>
       </c>
       <c r="D958" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E958" s="2" t="s">
         <v>33</v>
@@ -20467,7 +20467,7 @@
         <v>32</v>
       </c>
       <c r="D959" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E959" s="2" t="s">
         <v>33</v>
@@ -20484,7 +20484,7 @@
         <v>32</v>
       </c>
       <c r="D960" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E960" s="2" t="s">
         <v>33</v>
@@ -20501,7 +20501,7 @@
         <v>32</v>
       </c>
       <c r="D961" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E961" s="2" t="s">
         <v>33</v>
@@ -20518,7 +20518,7 @@
         <v>32</v>
       </c>
       <c r="D962" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E962" s="2" t="s">
         <v>33</v>
@@ -20535,7 +20535,7 @@
         <v>32</v>
       </c>
       <c r="D963" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E963" s="2" t="s">
         <v>33</v>
@@ -20552,7 +20552,7 @@
         <v>32</v>
       </c>
       <c r="D964" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E964" s="2" t="s">
         <v>33</v>
@@ -20569,7 +20569,7 @@
         <v>32</v>
       </c>
       <c r="D965" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E965" s="2" t="s">
         <v>33</v>
@@ -20603,7 +20603,7 @@
         <v>32</v>
       </c>
       <c r="D967" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E967" s="2" t="s">
         <v>33</v>
@@ -20620,7 +20620,7 @@
         <v>32</v>
       </c>
       <c r="D968" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E968" s="2" t="s">
         <v>33</v>
@@ -20637,7 +20637,7 @@
         <v>32</v>
       </c>
       <c r="D969" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E969" s="2" t="s">
         <v>33</v>
@@ -20654,7 +20654,7 @@
         <v>32</v>
       </c>
       <c r="D970" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E970" s="2" t="s">
         <v>33</v>
@@ -20671,7 +20671,7 @@
         <v>32</v>
       </c>
       <c r="D971" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E971" s="2" t="s">
         <v>33</v>
@@ -20705,7 +20705,7 @@
         <v>32</v>
       </c>
       <c r="D973" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E973" s="2" t="s">
         <v>33</v>
@@ -20722,7 +20722,7 @@
         <v>32</v>
       </c>
       <c r="D974" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E974" s="2" t="s">
         <v>33</v>
@@ -20739,7 +20739,7 @@
         <v>32</v>
       </c>
       <c r="D975" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E975" s="2" t="s">
         <v>33</v>
@@ -20756,7 +20756,7 @@
         <v>32</v>
       </c>
       <c r="D976" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E976" s="2" t="s">
         <v>33</v>
@@ -20773,7 +20773,7 @@
         <v>32</v>
       </c>
       <c r="D977" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E977" s="2" t="s">
         <v>33</v>
@@ -20790,7 +20790,7 @@
         <v>32</v>
       </c>
       <c r="D978" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E978" s="2" t="s">
         <v>33</v>
@@ -20807,7 +20807,7 @@
         <v>32</v>
       </c>
       <c r="D979" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E979" s="2" t="s">
         <v>33</v>
@@ -20824,7 +20824,7 @@
         <v>32</v>
       </c>
       <c r="D980" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E980" s="2" t="s">
         <v>33</v>
@@ -20841,7 +20841,7 @@
         <v>32</v>
       </c>
       <c r="D981" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>33</v>
@@ -20858,7 +20858,7 @@
         <v>32</v>
       </c>
       <c r="D982" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E982" s="2" t="s">
         <v>33</v>
@@ -20875,7 +20875,7 @@
         <v>32</v>
       </c>
       <c r="D983" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E983" s="2" t="s">
         <v>33</v>
@@ -20892,7 +20892,7 @@
         <v>32</v>
       </c>
       <c r="D984" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E984" s="2" t="s">
         <v>33</v>
@@ -20909,7 +20909,7 @@
         <v>32</v>
       </c>
       <c r="D985" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E985" s="2" t="s">
         <v>33</v>
@@ -20943,7 +20943,7 @@
         <v>32</v>
       </c>
       <c r="D987" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E987" s="2" t="s">
         <v>33</v>
@@ -20977,7 +20977,7 @@
         <v>32</v>
       </c>
       <c r="D989" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E989" s="2" t="s">
         <v>33</v>
@@ -20994,7 +20994,7 @@
         <v>32</v>
       </c>
       <c r="D990" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E990" s="2" t="s">
         <v>33</v>
@@ -21011,7 +21011,7 @@
         <v>32</v>
       </c>
       <c r="D991" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E991" s="2" t="s">
         <v>33</v>
@@ -21028,7 +21028,7 @@
         <v>32</v>
       </c>
       <c r="D992" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E992" s="2" t="s">
         <v>33</v>
@@ -21045,7 +21045,7 @@
         <v>32</v>
       </c>
       <c r="D993" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E993" s="2" t="s">
         <v>33</v>
@@ -21062,7 +21062,7 @@
         <v>32</v>
       </c>
       <c r="D994" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E994" s="2" t="s">
         <v>33</v>
@@ -21079,7 +21079,7 @@
         <v>32</v>
       </c>
       <c r="D995" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E995" s="2" t="s">
         <v>33</v>
@@ -21096,7 +21096,7 @@
         <v>32</v>
       </c>
       <c r="D996" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E996" s="2" t="s">
         <v>33</v>
@@ -21113,7 +21113,7 @@
         <v>32</v>
       </c>
       <c r="D997" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E997" s="2" t="s">
         <v>33</v>
@@ -21130,7 +21130,7 @@
         <v>32</v>
       </c>
       <c r="D998" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E998" s="2" t="s">
         <v>33</v>
@@ -21147,7 +21147,7 @@
         <v>32</v>
       </c>
       <c r="D999" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E999" s="2" t="s">
         <v>33</v>
@@ -21164,7 +21164,7 @@
         <v>32</v>
       </c>
       <c r="D1000" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1000" s="2" t="s">
         <v>33</v>
@@ -21198,7 +21198,7 @@
         <v>32</v>
       </c>
       <c r="D1002" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1002" s="2" t="s">
         <v>33</v>
@@ -21215,7 +21215,7 @@
         <v>32</v>
       </c>
       <c r="D1003" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E1003" s="2" t="s">
         <v>33</v>
@@ -21232,7 +21232,7 @@
         <v>32</v>
       </c>
       <c r="D1004" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E1004" s="2" t="s">
         <v>33</v>
@@ -21249,7 +21249,7 @@
         <v>32</v>
       </c>
       <c r="D1005" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1005" s="2" t="s">
         <v>33</v>
@@ -21266,7 +21266,7 @@
         <v>32</v>
       </c>
       <c r="D1006" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1006" s="2" t="s">
         <v>33</v>
@@ -21283,7 +21283,7 @@
         <v>32</v>
       </c>
       <c r="D1007" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1007" s="2" t="s">
         <v>33</v>
@@ -21317,7 +21317,7 @@
         <v>32</v>
       </c>
       <c r="D1009" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E1009" s="2" t="s">
         <v>33</v>
@@ -21334,7 +21334,7 @@
         <v>32</v>
       </c>
       <c r="D1010" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E1010" s="2" t="s">
         <v>33</v>
@@ -21351,7 +21351,7 @@
         <v>32</v>
       </c>
       <c r="D1011" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E1011" s="2" t="s">
         <v>33</v>
@@ -21368,7 +21368,7 @@
         <v>32</v>
       </c>
       <c r="D1012" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1012" s="2" t="s">
         <v>33</v>
@@ -21385,7 +21385,7 @@
         <v>32</v>
       </c>
       <c r="D1013" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E1013" s="2" t="s">
         <v>33</v>
@@ -21402,7 +21402,7 @@
         <v>32</v>
       </c>
       <c r="D1014" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1014" s="2" t="s">
         <v>33</v>
@@ -21419,7 +21419,7 @@
         <v>32</v>
       </c>
       <c r="D1015" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E1015" s="2" t="s">
         <v>33</v>
@@ -21436,7 +21436,7 @@
         <v>32</v>
       </c>
       <c r="D1016" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>33</v>
@@ -21453,7 +21453,7 @@
         <v>32</v>
       </c>
       <c r="D1017" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E1017" s="2" t="s">
         <v>33</v>
@@ -21470,7 +21470,7 @@
         <v>32</v>
       </c>
       <c r="D1018" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1018" s="2" t="s">
         <v>33</v>
@@ -21487,7 +21487,7 @@
         <v>32</v>
       </c>
       <c r="D1019" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1019" s="2" t="s">
         <v>33</v>
@@ -21504,7 +21504,7 @@
         <v>32</v>
       </c>
       <c r="D1020" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1020" s="2" t="s">
         <v>33</v>
@@ -21521,7 +21521,7 @@
         <v>32</v>
       </c>
       <c r="D1021" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1021" s="2" t="s">
         <v>33</v>
@@ -21538,7 +21538,7 @@
         <v>32</v>
       </c>
       <c r="D1022" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1022" s="2" t="s">
         <v>33</v>
@@ -21555,7 +21555,7 @@
         <v>32</v>
       </c>
       <c r="D1023" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1023" s="2" t="s">
         <v>33</v>
@@ -21572,7 +21572,7 @@
         <v>32</v>
       </c>
       <c r="D1024" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1024" s="2" t="s">
         <v>33</v>
@@ -21589,7 +21589,7 @@
         <v>32</v>
       </c>
       <c r="D1025" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E1025" s="2" t="s">
         <v>33</v>
@@ -21606,7 +21606,7 @@
         <v>32</v>
       </c>
       <c r="D1026" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E1026" s="2" t="s">
         <v>33</v>
@@ -21623,7 +21623,7 @@
         <v>32</v>
       </c>
       <c r="D1027" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E1027" s="2" t="s">
         <v>33</v>
@@ -21640,7 +21640,7 @@
         <v>32</v>
       </c>
       <c r="D1028" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1028" s="2" t="s">
         <v>33</v>
@@ -21657,7 +21657,7 @@
         <v>32</v>
       </c>
       <c r="D1029" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E1029" s="2" t="s">
         <v>33</v>
@@ -21674,7 +21674,7 @@
         <v>32</v>
       </c>
       <c r="D1030" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1030" s="2" t="s">
         <v>33</v>
@@ -21691,7 +21691,7 @@
         <v>32</v>
       </c>
       <c r="D1031" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E1031" s="2" t="s">
         <v>33</v>
@@ -21725,7 +21725,7 @@
         <v>32</v>
       </c>
       <c r="D1033" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1033" s="2" t="s">
         <v>33</v>
@@ -21742,7 +21742,7 @@
         <v>32</v>
       </c>
       <c r="D1034" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E1034" s="2" t="s">
         <v>33</v>
@@ -21759,7 +21759,7 @@
         <v>32</v>
       </c>
       <c r="D1035" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1035" s="2" t="s">
         <v>33</v>
@@ -21776,7 +21776,7 @@
         <v>32</v>
       </c>
       <c r="D1036" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E1036" s="2" t="s">
         <v>33</v>
@@ -21793,7 +21793,7 @@
         <v>32</v>
       </c>
       <c r="D1037" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1037" s="2" t="s">
         <v>33</v>
@@ -21810,7 +21810,7 @@
         <v>32</v>
       </c>
       <c r="D1038" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E1038" s="2" t="s">
         <v>33</v>
@@ -21827,7 +21827,7 @@
         <v>32</v>
       </c>
       <c r="D1039" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1039" s="2" t="s">
         <v>33</v>
@@ -21844,7 +21844,7 @@
         <v>32</v>
       </c>
       <c r="D1040" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1040" s="2" t="s">
         <v>33</v>
@@ -21861,7 +21861,7 @@
         <v>32</v>
       </c>
       <c r="D1041" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E1041" s="2" t="s">
         <v>33</v>
@@ -21878,7 +21878,7 @@
         <v>32</v>
       </c>
       <c r="D1042" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E1042" s="2" t="s">
         <v>33</v>
@@ -21912,7 +21912,7 @@
         <v>32</v>
       </c>
       <c r="D1044" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E1044" s="2" t="s">
         <v>33</v>
@@ -21929,7 +21929,7 @@
         <v>32</v>
       </c>
       <c r="D1045" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1045" s="2" t="s">
         <v>33</v>
@@ -21946,7 +21946,7 @@
         <v>32</v>
       </c>
       <c r="D1046" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1046" s="2" t="s">
         <v>33</v>
@@ -21963,7 +21963,7 @@
         <v>32</v>
       </c>
       <c r="D1047" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1047" s="2" t="s">
         <v>33</v>
@@ -21980,7 +21980,7 @@
         <v>32</v>
       </c>
       <c r="D1048" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E1048" s="2" t="s">
         <v>33</v>
@@ -21997,7 +21997,7 @@
         <v>32</v>
       </c>
       <c r="D1049" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E1049" s="2" t="s">
         <v>33</v>
@@ -22014,7 +22014,7 @@
         <v>32</v>
       </c>
       <c r="D1050" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1050" s="2" t="s">
         <v>33</v>
@@ -22031,7 +22031,7 @@
         <v>32</v>
       </c>
       <c r="D1051" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E1051" s="2" t="s">
         <v>33</v>
@@ -22048,7 +22048,7 @@
         <v>32</v>
       </c>
       <c r="D1052" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1052" s="2" t="s">
         <v>33</v>
@@ -22065,7 +22065,7 @@
         <v>32</v>
       </c>
       <c r="D1053" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E1053" s="2" t="s">
         <v>33</v>
@@ -22082,7 +22082,7 @@
         <v>32</v>
       </c>
       <c r="D1054" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1054" s="2" t="s">
         <v>33</v>
@@ -22099,7 +22099,7 @@
         <v>32</v>
       </c>
       <c r="D1055" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1055" s="2" t="s">
         <v>33</v>
@@ -22116,7 +22116,7 @@
         <v>32</v>
       </c>
       <c r="D1056" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E1056" s="2" t="s">
         <v>33</v>
@@ -22133,7 +22133,7 @@
         <v>32</v>
       </c>
       <c r="D1057" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E1057" s="2" t="s">
         <v>33</v>
@@ -22150,7 +22150,7 @@
         <v>32</v>
       </c>
       <c r="D1058" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1058" s="2" t="s">
         <v>33</v>
@@ -22184,7 +22184,7 @@
         <v>32</v>
       </c>
       <c r="D1060" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E1060" s="2" t="s">
         <v>33</v>
@@ -22201,7 +22201,7 @@
         <v>32</v>
       </c>
       <c r="D1061" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1061" s="2" t="s">
         <v>33</v>
@@ -22218,7 +22218,7 @@
         <v>32</v>
       </c>
       <c r="D1062" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1062" s="2" t="s">
         <v>33</v>
@@ -22235,7 +22235,7 @@
         <v>32</v>
       </c>
       <c r="D1063" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E1063" s="2" t="s">
         <v>33</v>
@@ -22252,7 +22252,7 @@
         <v>32</v>
       </c>
       <c r="D1064" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E1064" s="2" t="s">
         <v>33</v>
@@ -22269,7 +22269,7 @@
         <v>32</v>
       </c>
       <c r="D1065" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1065" s="2" t="s">
         <v>33</v>
@@ -22286,7 +22286,7 @@
         <v>32</v>
       </c>
       <c r="D1066" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1066" s="2" t="s">
         <v>33</v>
@@ -22303,7 +22303,7 @@
         <v>32</v>
       </c>
       <c r="D1067" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E1067" s="2" t="s">
         <v>33</v>
@@ -22337,7 +22337,7 @@
         <v>32</v>
       </c>
       <c r="D1069" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1069" s="2" t="s">
         <v>33</v>
@@ -22354,7 +22354,7 @@
         <v>32</v>
       </c>
       <c r="D1070" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1070" s="2" t="s">
         <v>33</v>
@@ -22371,7 +22371,7 @@
         <v>32</v>
       </c>
       <c r="D1071" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1071" s="2" t="s">
         <v>33</v>
@@ -22388,7 +22388,7 @@
         <v>32</v>
       </c>
       <c r="D1072" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E1072" s="2" t="s">
         <v>33</v>
@@ -22405,7 +22405,7 @@
         <v>32</v>
       </c>
       <c r="D1073" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E1073" s="2" t="s">
         <v>33</v>
@@ -22422,7 +22422,7 @@
         <v>32</v>
       </c>
       <c r="D1074" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E1074" s="2" t="s">
         <v>33</v>
@@ -22456,7 +22456,7 @@
         <v>32</v>
       </c>
       <c r="D1076" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E1076" s="2" t="s">
         <v>33</v>
@@ -22473,7 +22473,7 @@
         <v>32</v>
       </c>
       <c r="D1077" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E1077" s="2" t="s">
         <v>33</v>
@@ -22490,7 +22490,7 @@
         <v>32</v>
       </c>
       <c r="D1078" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E1078" s="2" t="s">
         <v>33</v>
@@ -22507,7 +22507,7 @@
         <v>32</v>
       </c>
       <c r="D1079" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E1079" s="2" t="s">
         <v>33</v>
@@ -22524,7 +22524,7 @@
         <v>32</v>
       </c>
       <c r="D1080" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1080" s="2" t="s">
         <v>33</v>
@@ -22541,7 +22541,7 @@
         <v>32</v>
       </c>
       <c r="D1081" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E1081" s="2" t="s">
         <v>33</v>
@@ -22558,7 +22558,7 @@
         <v>32</v>
       </c>
       <c r="D1082" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E1082" s="2" t="s">
         <v>33</v>
@@ -22592,7 +22592,7 @@
         <v>32</v>
       </c>
       <c r="D1084" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E1084" s="2" t="s">
         <v>33</v>
@@ -22609,7 +22609,7 @@
         <v>32</v>
       </c>
       <c r="D1085" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E1085" s="2" t="s">
         <v>33</v>
@@ -22626,7 +22626,7 @@
         <v>32</v>
       </c>
       <c r="D1086" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E1086" s="2" t="s">
         <v>33</v>
@@ -22643,7 +22643,7 @@
         <v>32</v>
       </c>
       <c r="D1087" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E1087" s="2" t="s">
         <v>33</v>
@@ -22660,7 +22660,7 @@
         <v>32</v>
       </c>
       <c r="D1088" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E1088" s="2" t="s">
         <v>33</v>
@@ -22677,7 +22677,7 @@
         <v>32</v>
       </c>
       <c r="D1089" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1089" s="2" t="s">
         <v>33</v>
@@ -22694,7 +22694,7 @@
         <v>32</v>
       </c>
       <c r="D1090" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E1090" s="2" t="s">
         <v>33</v>
@@ -22711,7 +22711,7 @@
         <v>32</v>
       </c>
       <c r="D1091" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E1091" s="2" t="s">
         <v>33</v>
@@ -22728,7 +22728,7 @@
         <v>32</v>
       </c>
       <c r="D1092" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1092" s="2" t="s">
         <v>33</v>
@@ -22745,7 +22745,7 @@
         <v>32</v>
       </c>
       <c r="D1093" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E1093" s="2" t="s">
         <v>33</v>
@@ -22762,7 +22762,7 @@
         <v>32</v>
       </c>
       <c r="D1094" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E1094" s="2" t="s">
         <v>33</v>
@@ -22779,7 +22779,7 @@
         <v>32</v>
       </c>
       <c r="D1095" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E1095" s="2" t="s">
         <v>33</v>
@@ -22796,7 +22796,7 @@
         <v>32</v>
       </c>
       <c r="D1096" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1096" s="2" t="s">
         <v>33</v>
@@ -22813,7 +22813,7 @@
         <v>32</v>
       </c>
       <c r="D1097" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E1097" s="2" t="s">
         <v>33</v>
@@ -22847,7 +22847,7 @@
         <v>32</v>
       </c>
       <c r="D1099" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1099" s="2" t="s">
         <v>33</v>
@@ -22864,7 +22864,7 @@
         <v>32</v>
       </c>
       <c r="D1100" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E1100" s="2" t="s">
         <v>33</v>
@@ -22881,7 +22881,7 @@
         <v>32</v>
       </c>
       <c r="D1101" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E1101" s="2" t="s">
         <v>33</v>
@@ -22898,7 +22898,7 @@
         <v>32</v>
       </c>
       <c r="D1102" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1102" s="2" t="s">
         <v>33</v>
@@ -22915,7 +22915,7 @@
         <v>32</v>
       </c>
       <c r="D1103" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E1103" s="2" t="s">
         <v>33</v>
@@ -22949,7 +22949,7 @@
         <v>32</v>
       </c>
       <c r="D1105" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1105" s="2" t="s">
         <v>33</v>
@@ -22966,7 +22966,7 @@
         <v>32</v>
       </c>
       <c r="D1106" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1106" s="2" t="s">
         <v>33</v>
@@ -22983,7 +22983,7 @@
         <v>32</v>
       </c>
       <c r="D1107" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E1107" s="2" t="s">
         <v>33</v>
@@ -23000,7 +23000,7 @@
         <v>32</v>
       </c>
       <c r="D1108" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E1108" s="2" t="s">
         <v>33</v>
@@ -23017,7 +23017,7 @@
         <v>32</v>
       </c>
       <c r="D1109" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1109" s="2" t="s">
         <v>33</v>
@@ -23034,7 +23034,7 @@
         <v>32</v>
       </c>
       <c r="D1110" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E1110" s="2" t="s">
         <v>33</v>
@@ -23051,7 +23051,7 @@
         <v>32</v>
       </c>
       <c r="D1111" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E1111" s="2" t="s">
         <v>33</v>
@@ -23068,7 +23068,7 @@
         <v>32</v>
       </c>
       <c r="D1112" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E1112" s="2" t="s">
         <v>33</v>

--- a/reports/appium/appium-test-results.xlsx
+++ b/reports/appium/appium-test-results.xlsx
@@ -30,7 +30,7 @@
     <t>Execution Date</t>
   </si>
   <si>
-    <t>7/27/2026, 8:28:29 AM</t>
+    <t>7/27/2026, 8:31:55 AM</t>
   </si>
   <si>
     <t>Total Tests Executed</t>
@@ -3930,7 +3930,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>13878</v>
+        <v>14026</v>
       </c>
     </row>
   </sheetData>
@@ -4198,7 +4198,7 @@
         <v>32</v>
       </c>
       <c r="D2" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>33</v>
@@ -4215,7 +4215,7 @@
         <v>32</v>
       </c>
       <c r="D3" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>33</v>
@@ -4232,7 +4232,7 @@
         <v>32</v>
       </c>
       <c r="D4" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>33</v>
@@ -4249,7 +4249,7 @@
         <v>32</v>
       </c>
       <c r="D5" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>33</v>
@@ -4266,7 +4266,7 @@
         <v>32</v>
       </c>
       <c r="D6" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>33</v>
@@ -4283,7 +4283,7 @@
         <v>32</v>
       </c>
       <c r="D7" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>33</v>
@@ -4300,7 +4300,7 @@
         <v>32</v>
       </c>
       <c r="D8" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
@@ -4317,7 +4317,7 @@
         <v>32</v>
       </c>
       <c r="D9" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>33</v>
@@ -4334,7 +4334,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>33</v>
@@ -4351,7 +4351,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -4368,7 +4368,7 @@
         <v>32</v>
       </c>
       <c r="D12" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>33</v>
@@ -4385,7 +4385,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>33</v>
@@ -4402,7 +4402,7 @@
         <v>32</v>
       </c>
       <c r="D14" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>33</v>
@@ -4436,7 +4436,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>33</v>
@@ -4453,7 +4453,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>33</v>
@@ -4470,7 +4470,7 @@
         <v>32</v>
       </c>
       <c r="D18" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>33</v>
@@ -4487,7 +4487,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>33</v>
@@ -4504,7 +4504,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>33</v>
@@ -4521,7 +4521,7 @@
         <v>32</v>
       </c>
       <c r="D21" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>33</v>
@@ -4538,7 +4538,7 @@
         <v>32</v>
       </c>
       <c r="D22" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>33</v>
@@ -4555,7 +4555,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>33</v>
@@ -4572,7 +4572,7 @@
         <v>32</v>
       </c>
       <c r="D24" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>33</v>
@@ -4589,7 +4589,7 @@
         <v>32</v>
       </c>
       <c r="D25" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>33</v>
@@ -4606,7 +4606,7 @@
         <v>32</v>
       </c>
       <c r="D26" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>33</v>
@@ -4623,7 +4623,7 @@
         <v>32</v>
       </c>
       <c r="D27" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>33</v>
@@ -4640,7 +4640,7 @@
         <v>32</v>
       </c>
       <c r="D28" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>33</v>
@@ -4657,7 +4657,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>33</v>
@@ -4674,7 +4674,7 @@
         <v>32</v>
       </c>
       <c r="D30" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>33</v>
@@ -4691,7 +4691,7 @@
         <v>32</v>
       </c>
       <c r="D31" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>33</v>
@@ -4708,7 +4708,7 @@
         <v>32</v>
       </c>
       <c r="D32" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>33</v>
@@ -4725,7 +4725,7 @@
         <v>32</v>
       </c>
       <c r="D33" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>33</v>
@@ -4742,7 +4742,7 @@
         <v>32</v>
       </c>
       <c r="D34" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>33</v>
@@ -4776,7 +4776,7 @@
         <v>32</v>
       </c>
       <c r="D36" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>33</v>
@@ -4793,7 +4793,7 @@
         <v>32</v>
       </c>
       <c r="D37" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>33</v>
@@ -4810,7 +4810,7 @@
         <v>32</v>
       </c>
       <c r="D38" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>33</v>
@@ -4827,7 +4827,7 @@
         <v>32</v>
       </c>
       <c r="D39" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>33</v>
@@ -4844,7 +4844,7 @@
         <v>32</v>
       </c>
       <c r="D40" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>33</v>
@@ -4861,7 +4861,7 @@
         <v>32</v>
       </c>
       <c r="D41" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>33</v>
@@ -4878,7 +4878,7 @@
         <v>32</v>
       </c>
       <c r="D42" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>33</v>
@@ -4895,7 +4895,7 @@
         <v>32</v>
       </c>
       <c r="D43" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>33</v>
@@ -4912,7 +4912,7 @@
         <v>32</v>
       </c>
       <c r="D44" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>33</v>
@@ -4929,7 +4929,7 @@
         <v>32</v>
       </c>
       <c r="D45" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>33</v>
@@ -4946,7 +4946,7 @@
         <v>32</v>
       </c>
       <c r="D46" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>33</v>
@@ -4963,7 +4963,7 @@
         <v>32</v>
       </c>
       <c r="D47" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>33</v>
@@ -4980,7 +4980,7 @@
         <v>32</v>
       </c>
       <c r="D48" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>33</v>
@@ -4997,7 +4997,7 @@
         <v>32</v>
       </c>
       <c r="D49" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>33</v>
@@ -5014,7 +5014,7 @@
         <v>32</v>
       </c>
       <c r="D50" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>33</v>
@@ -5031,7 +5031,7 @@
         <v>32</v>
       </c>
       <c r="D51" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>33</v>
@@ -5048,7 +5048,7 @@
         <v>32</v>
       </c>
       <c r="D52" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>33</v>
@@ -5065,7 +5065,7 @@
         <v>32</v>
       </c>
       <c r="D53" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>33</v>
@@ -5082,7 +5082,7 @@
         <v>32</v>
       </c>
       <c r="D54" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>33</v>
@@ -5099,7 +5099,7 @@
         <v>32</v>
       </c>
       <c r="D55" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>33</v>
@@ -5133,7 +5133,7 @@
         <v>32</v>
       </c>
       <c r="D57" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>33</v>
@@ -5167,7 +5167,7 @@
         <v>32</v>
       </c>
       <c r="D59" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>33</v>
@@ -5184,7 +5184,7 @@
         <v>32</v>
       </c>
       <c r="D60" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>33</v>
@@ -5201,7 +5201,7 @@
         <v>32</v>
       </c>
       <c r="D61" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>33</v>
@@ -5218,7 +5218,7 @@
         <v>32</v>
       </c>
       <c r="D62" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>33</v>
@@ -5235,7 +5235,7 @@
         <v>32</v>
       </c>
       <c r="D63" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>33</v>
@@ -5252,7 +5252,7 @@
         <v>32</v>
       </c>
       <c r="D64" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>33</v>
@@ -5269,7 +5269,7 @@
         <v>32</v>
       </c>
       <c r="D65" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>33</v>
@@ -5286,7 +5286,7 @@
         <v>32</v>
       </c>
       <c r="D66" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>33</v>
@@ -5303,7 +5303,7 @@
         <v>32</v>
       </c>
       <c r="D67" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>33</v>
@@ -5320,7 +5320,7 @@
         <v>32</v>
       </c>
       <c r="D68" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>33</v>
@@ -5354,7 +5354,7 @@
         <v>32</v>
       </c>
       <c r="D70" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>33</v>
@@ -5371,7 +5371,7 @@
         <v>32</v>
       </c>
       <c r="D71" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>33</v>
@@ -5388,7 +5388,7 @@
         <v>32</v>
       </c>
       <c r="D72" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>33</v>
@@ -5422,7 +5422,7 @@
         <v>32</v>
       </c>
       <c r="D74" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>33</v>
@@ -5439,7 +5439,7 @@
         <v>32</v>
       </c>
       <c r="D75" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>33</v>
@@ -5456,7 +5456,7 @@
         <v>32</v>
       </c>
       <c r="D76" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>33</v>
@@ -5473,7 +5473,7 @@
         <v>32</v>
       </c>
       <c r="D77" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>33</v>
@@ -5490,7 +5490,7 @@
         <v>32</v>
       </c>
       <c r="D78" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>33</v>
@@ -5507,7 +5507,7 @@
         <v>32</v>
       </c>
       <c r="D79" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>33</v>
@@ -5524,7 +5524,7 @@
         <v>32</v>
       </c>
       <c r="D80" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>33</v>
@@ -5541,7 +5541,7 @@
         <v>32</v>
       </c>
       <c r="D81" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>33</v>
@@ -5558,7 +5558,7 @@
         <v>32</v>
       </c>
       <c r="D82" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>33</v>
@@ -5575,7 +5575,7 @@
         <v>32</v>
       </c>
       <c r="D83" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>33</v>
@@ -5592,7 +5592,7 @@
         <v>32</v>
       </c>
       <c r="D84" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>33</v>
@@ -5609,7 +5609,7 @@
         <v>32</v>
       </c>
       <c r="D85" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>33</v>
@@ -5626,7 +5626,7 @@
         <v>32</v>
       </c>
       <c r="D86" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>33</v>
@@ -5643,7 +5643,7 @@
         <v>32</v>
       </c>
       <c r="D87" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>33</v>
@@ -5660,7 +5660,7 @@
         <v>32</v>
       </c>
       <c r="D88" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>33</v>
@@ -5677,7 +5677,7 @@
         <v>32</v>
       </c>
       <c r="D89" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>33</v>
@@ -5694,7 +5694,7 @@
         <v>32</v>
       </c>
       <c r="D90" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>33</v>
@@ -5711,7 +5711,7 @@
         <v>32</v>
       </c>
       <c r="D91" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>33</v>
@@ -5728,7 +5728,7 @@
         <v>32</v>
       </c>
       <c r="D92" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>33</v>
@@ -5745,7 +5745,7 @@
         <v>32</v>
       </c>
       <c r="D93" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>33</v>
@@ -5762,7 +5762,7 @@
         <v>32</v>
       </c>
       <c r="D94" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>33</v>
@@ -5779,7 +5779,7 @@
         <v>32</v>
       </c>
       <c r="D95" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>33</v>
@@ -5796,7 +5796,7 @@
         <v>32</v>
       </c>
       <c r="D96" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>33</v>
@@ -5813,7 +5813,7 @@
         <v>32</v>
       </c>
       <c r="D97" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>33</v>
@@ -5830,7 +5830,7 @@
         <v>32</v>
       </c>
       <c r="D98" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>33</v>
@@ -5847,7 +5847,7 @@
         <v>32</v>
       </c>
       <c r="D99" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>33</v>
@@ -5864,7 +5864,7 @@
         <v>32</v>
       </c>
       <c r="D100" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>33</v>
@@ -5881,7 +5881,7 @@
         <v>32</v>
       </c>
       <c r="D101" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>33</v>
@@ -5898,7 +5898,7 @@
         <v>32</v>
       </c>
       <c r="D102" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>33</v>
@@ -5915,7 +5915,7 @@
         <v>32</v>
       </c>
       <c r="D103" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>33</v>
@@ -5932,7 +5932,7 @@
         <v>32</v>
       </c>
       <c r="D104" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>33</v>
@@ -5949,7 +5949,7 @@
         <v>32</v>
       </c>
       <c r="D105" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>33</v>
@@ -5966,7 +5966,7 @@
         <v>32</v>
       </c>
       <c r="D106" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>33</v>
@@ -5983,7 +5983,7 @@
         <v>32</v>
       </c>
       <c r="D107" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>33</v>
@@ -6000,7 +6000,7 @@
         <v>32</v>
       </c>
       <c r="D108" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>33</v>
@@ -6017,7 +6017,7 @@
         <v>32</v>
       </c>
       <c r="D109" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>33</v>
@@ -6034,7 +6034,7 @@
         <v>32</v>
       </c>
       <c r="D110" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>33</v>
@@ -6051,7 +6051,7 @@
         <v>32</v>
       </c>
       <c r="D111" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>33</v>
@@ -6068,7 +6068,7 @@
         <v>32</v>
       </c>
       <c r="D112" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>33</v>
@@ -6085,7 +6085,7 @@
         <v>32</v>
       </c>
       <c r="D113" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>33</v>
@@ -6102,7 +6102,7 @@
         <v>32</v>
       </c>
       <c r="D114" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>33</v>
@@ -6119,7 +6119,7 @@
         <v>32</v>
       </c>
       <c r="D115" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>33</v>
@@ -6136,7 +6136,7 @@
         <v>32</v>
       </c>
       <c r="D116" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>33</v>
@@ -6153,7 +6153,7 @@
         <v>32</v>
       </c>
       <c r="D117" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>33</v>
@@ -6170,7 +6170,7 @@
         <v>32</v>
       </c>
       <c r="D118" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>33</v>
@@ -6187,7 +6187,7 @@
         <v>32</v>
       </c>
       <c r="D119" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>33</v>
@@ -6204,7 +6204,7 @@
         <v>32</v>
       </c>
       <c r="D120" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>33</v>
@@ -6221,7 +6221,7 @@
         <v>32</v>
       </c>
       <c r="D121" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>33</v>
@@ -6238,7 +6238,7 @@
         <v>32</v>
       </c>
       <c r="D122" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>33</v>
@@ -6255,7 +6255,7 @@
         <v>32</v>
       </c>
       <c r="D123" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>33</v>
@@ -6272,7 +6272,7 @@
         <v>32</v>
       </c>
       <c r="D124" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>33</v>
@@ -6289,7 +6289,7 @@
         <v>32</v>
       </c>
       <c r="D125" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>33</v>
@@ -6306,7 +6306,7 @@
         <v>32</v>
       </c>
       <c r="D126" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>33</v>
@@ -6323,7 +6323,7 @@
         <v>32</v>
       </c>
       <c r="D127" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>33</v>
@@ -6340,7 +6340,7 @@
         <v>32</v>
       </c>
       <c r="D128" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>33</v>
@@ -6357,7 +6357,7 @@
         <v>32</v>
       </c>
       <c r="D129" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>33</v>
@@ -6374,7 +6374,7 @@
         <v>32</v>
       </c>
       <c r="D130" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>33</v>
@@ -6391,7 +6391,7 @@
         <v>32</v>
       </c>
       <c r="D131" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>33</v>
@@ -6425,7 +6425,7 @@
         <v>32</v>
       </c>
       <c r="D133" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>33</v>
@@ -6442,7 +6442,7 @@
         <v>32</v>
       </c>
       <c r="D134" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>33</v>
@@ -6459,7 +6459,7 @@
         <v>32</v>
       </c>
       <c r="D135" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>33</v>
@@ -6476,7 +6476,7 @@
         <v>32</v>
       </c>
       <c r="D136" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>33</v>
@@ -6493,7 +6493,7 @@
         <v>32</v>
       </c>
       <c r="D137" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>33</v>
@@ -6510,7 +6510,7 @@
         <v>32</v>
       </c>
       <c r="D138" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>33</v>
@@ -6527,7 +6527,7 @@
         <v>32</v>
       </c>
       <c r="D139" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>33</v>
@@ -6544,7 +6544,7 @@
         <v>32</v>
       </c>
       <c r="D140" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>33</v>
@@ -6561,7 +6561,7 @@
         <v>32</v>
       </c>
       <c r="D141" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>33</v>
@@ -6578,7 +6578,7 @@
         <v>32</v>
       </c>
       <c r="D142" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>33</v>
@@ -6595,7 +6595,7 @@
         <v>32</v>
       </c>
       <c r="D143" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>33</v>
@@ -6629,7 +6629,7 @@
         <v>32</v>
       </c>
       <c r="D145" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>33</v>
@@ -6646,7 +6646,7 @@
         <v>32</v>
       </c>
       <c r="D146" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>33</v>
@@ -6663,7 +6663,7 @@
         <v>32</v>
       </c>
       <c r="D147" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>33</v>
@@ -6680,7 +6680,7 @@
         <v>32</v>
       </c>
       <c r="D148" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>33</v>
@@ -6697,7 +6697,7 @@
         <v>32</v>
       </c>
       <c r="D149" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>33</v>
@@ -6714,7 +6714,7 @@
         <v>32</v>
       </c>
       <c r="D150" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>33</v>
@@ -6731,7 +6731,7 @@
         <v>32</v>
       </c>
       <c r="D151" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>33</v>
@@ -6748,7 +6748,7 @@
         <v>32</v>
       </c>
       <c r="D152" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>33</v>
@@ -6765,7 +6765,7 @@
         <v>32</v>
       </c>
       <c r="D153" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>33</v>
@@ -6782,7 +6782,7 @@
         <v>32</v>
       </c>
       <c r="D154" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>33</v>
@@ -6799,7 +6799,7 @@
         <v>32</v>
       </c>
       <c r="D155" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>33</v>
@@ -6816,7 +6816,7 @@
         <v>32</v>
       </c>
       <c r="D156" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>33</v>
@@ -6833,7 +6833,7 @@
         <v>32</v>
       </c>
       <c r="D157" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>33</v>
@@ -6850,7 +6850,7 @@
         <v>32</v>
       </c>
       <c r="D158" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>33</v>
@@ -6867,7 +6867,7 @@
         <v>32</v>
       </c>
       <c r="D159" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>33</v>
@@ -6884,7 +6884,7 @@
         <v>32</v>
       </c>
       <c r="D160" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>33</v>
@@ -6901,7 +6901,7 @@
         <v>32</v>
       </c>
       <c r="D161" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>33</v>
@@ -6918,7 +6918,7 @@
         <v>32</v>
       </c>
       <c r="D162" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>33</v>
@@ -6935,7 +6935,7 @@
         <v>32</v>
       </c>
       <c r="D163" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>33</v>
@@ -6952,7 +6952,7 @@
         <v>32</v>
       </c>
       <c r="D164" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>33</v>
@@ -6969,7 +6969,7 @@
         <v>32</v>
       </c>
       <c r="D165" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>33</v>
@@ -6986,7 +6986,7 @@
         <v>32</v>
       </c>
       <c r="D166" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>33</v>
@@ -7003,7 +7003,7 @@
         <v>32</v>
       </c>
       <c r="D167" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>33</v>
@@ -7020,7 +7020,7 @@
         <v>32</v>
       </c>
       <c r="D168" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>33</v>
@@ -7037,7 +7037,7 @@
         <v>32</v>
       </c>
       <c r="D169" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>33</v>
@@ -7054,7 +7054,7 @@
         <v>32</v>
       </c>
       <c r="D170" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>33</v>
@@ -7071,7 +7071,7 @@
         <v>32</v>
       </c>
       <c r="D171" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>33</v>
@@ -7088,7 +7088,7 @@
         <v>32</v>
       </c>
       <c r="D172" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>33</v>
@@ -7122,7 +7122,7 @@
         <v>32</v>
       </c>
       <c r="D174" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>33</v>
@@ -7139,7 +7139,7 @@
         <v>32</v>
       </c>
       <c r="D175" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>33</v>
@@ -7156,7 +7156,7 @@
         <v>32</v>
       </c>
       <c r="D176" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>33</v>
@@ -7173,7 +7173,7 @@
         <v>32</v>
       </c>
       <c r="D177" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>33</v>
@@ -7190,7 +7190,7 @@
         <v>32</v>
       </c>
       <c r="D178" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>33</v>
@@ -7207,7 +7207,7 @@
         <v>32</v>
       </c>
       <c r="D179" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>33</v>
@@ -7224,7 +7224,7 @@
         <v>32</v>
       </c>
       <c r="D180" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>33</v>
@@ -7258,7 +7258,7 @@
         <v>32</v>
       </c>
       <c r="D182" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>33</v>
@@ -7275,7 +7275,7 @@
         <v>32</v>
       </c>
       <c r="D183" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>33</v>
@@ -7292,7 +7292,7 @@
         <v>32</v>
       </c>
       <c r="D184" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>33</v>
@@ -7309,7 +7309,7 @@
         <v>32</v>
       </c>
       <c r="D185" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>33</v>
@@ -7326,7 +7326,7 @@
         <v>32</v>
       </c>
       <c r="D186" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>33</v>
@@ -7343,7 +7343,7 @@
         <v>32</v>
       </c>
       <c r="D187" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>33</v>
@@ -7360,7 +7360,7 @@
         <v>32</v>
       </c>
       <c r="D188" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>33</v>
@@ -7377,7 +7377,7 @@
         <v>32</v>
       </c>
       <c r="D189" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>33</v>
@@ -7394,7 +7394,7 @@
         <v>32</v>
       </c>
       <c r="D190" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>33</v>
@@ -7411,7 +7411,7 @@
         <v>32</v>
       </c>
       <c r="D191" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>33</v>
@@ -7445,7 +7445,7 @@
         <v>32</v>
       </c>
       <c r="D193" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>33</v>
@@ -7462,7 +7462,7 @@
         <v>32</v>
       </c>
       <c r="D194" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>33</v>
@@ -7479,7 +7479,7 @@
         <v>32</v>
       </c>
       <c r="D195" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>33</v>
@@ -7496,7 +7496,7 @@
         <v>32</v>
       </c>
       <c r="D196" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>33</v>
@@ -7530,7 +7530,7 @@
         <v>32</v>
       </c>
       <c r="D198" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>33</v>
@@ -7547,7 +7547,7 @@
         <v>32</v>
       </c>
       <c r="D199" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>33</v>
@@ -7564,7 +7564,7 @@
         <v>32</v>
       </c>
       <c r="D200" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>33</v>
@@ -7581,7 +7581,7 @@
         <v>32</v>
       </c>
       <c r="D201" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>33</v>
@@ -7598,7 +7598,7 @@
         <v>32</v>
       </c>
       <c r="D202" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>33</v>
@@ -7615,7 +7615,7 @@
         <v>32</v>
       </c>
       <c r="D203" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>33</v>
@@ -7649,7 +7649,7 @@
         <v>32</v>
       </c>
       <c r="D205" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>33</v>
@@ -7666,7 +7666,7 @@
         <v>32</v>
       </c>
       <c r="D206" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>33</v>
@@ -7683,7 +7683,7 @@
         <v>32</v>
       </c>
       <c r="D207" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>33</v>
@@ -7700,7 +7700,7 @@
         <v>32</v>
       </c>
       <c r="D208" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>33</v>
@@ -7717,7 +7717,7 @@
         <v>32</v>
       </c>
       <c r="D209" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>33</v>
@@ -7734,7 +7734,7 @@
         <v>32</v>
       </c>
       <c r="D210" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>33</v>
@@ -7751,7 +7751,7 @@
         <v>32</v>
       </c>
       <c r="D211" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>33</v>
@@ -7768,7 +7768,7 @@
         <v>32</v>
       </c>
       <c r="D212" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>33</v>
@@ -7785,7 +7785,7 @@
         <v>32</v>
       </c>
       <c r="D213" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>33</v>
@@ -7802,7 +7802,7 @@
         <v>32</v>
       </c>
       <c r="D214" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>33</v>
@@ -7819,7 +7819,7 @@
         <v>32</v>
       </c>
       <c r="D215" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>33</v>
@@ -7836,7 +7836,7 @@
         <v>32</v>
       </c>
       <c r="D216" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>33</v>
@@ -7853,7 +7853,7 @@
         <v>32</v>
       </c>
       <c r="D217" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>33</v>
@@ -7870,7 +7870,7 @@
         <v>32</v>
       </c>
       <c r="D218" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>33</v>
@@ -7887,7 +7887,7 @@
         <v>32</v>
       </c>
       <c r="D219" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>33</v>
@@ -7904,7 +7904,7 @@
         <v>32</v>
       </c>
       <c r="D220" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>33</v>
@@ -7921,7 +7921,7 @@
         <v>32</v>
       </c>
       <c r="D221" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>33</v>
@@ -7938,7 +7938,7 @@
         <v>32</v>
       </c>
       <c r="D222" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>33</v>
@@ -7955,7 +7955,7 @@
         <v>32</v>
       </c>
       <c r="D223" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>33</v>
@@ -7972,7 +7972,7 @@
         <v>32</v>
       </c>
       <c r="D224" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>33</v>
@@ -7989,7 +7989,7 @@
         <v>32</v>
       </c>
       <c r="D225" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>33</v>
@@ -8006,7 +8006,7 @@
         <v>32</v>
       </c>
       <c r="D226" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>33</v>
@@ -8040,7 +8040,7 @@
         <v>32</v>
       </c>
       <c r="D228" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>33</v>
@@ -8057,7 +8057,7 @@
         <v>32</v>
       </c>
       <c r="D229" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>33</v>
@@ -8074,7 +8074,7 @@
         <v>32</v>
       </c>
       <c r="D230" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>33</v>
@@ -8091,7 +8091,7 @@
         <v>32</v>
       </c>
       <c r="D231" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>33</v>
@@ -8108,7 +8108,7 @@
         <v>32</v>
       </c>
       <c r="D232" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>33</v>
@@ -8125,7 +8125,7 @@
         <v>32</v>
       </c>
       <c r="D233" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>33</v>
@@ -8142,7 +8142,7 @@
         <v>32</v>
       </c>
       <c r="D234" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>33</v>
@@ -8159,7 +8159,7 @@
         <v>32</v>
       </c>
       <c r="D235" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>33</v>
@@ -8176,7 +8176,7 @@
         <v>32</v>
       </c>
       <c r="D236" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>33</v>
@@ -8193,7 +8193,7 @@
         <v>32</v>
       </c>
       <c r="D237" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>33</v>
@@ -8227,7 +8227,7 @@
         <v>32</v>
       </c>
       <c r="D239" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>33</v>
@@ -8244,7 +8244,7 @@
         <v>32</v>
       </c>
       <c r="D240" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>33</v>
@@ -8261,7 +8261,7 @@
         <v>32</v>
       </c>
       <c r="D241" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>33</v>
@@ -8278,7 +8278,7 @@
         <v>32</v>
       </c>
       <c r="D242" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>33</v>
@@ -8295,7 +8295,7 @@
         <v>32</v>
       </c>
       <c r="D243" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>33</v>
@@ -8329,7 +8329,7 @@
         <v>32</v>
       </c>
       <c r="D245" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>33</v>
@@ -8346,7 +8346,7 @@
         <v>32</v>
       </c>
       <c r="D246" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>33</v>
@@ -8363,7 +8363,7 @@
         <v>32</v>
       </c>
       <c r="D247" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>33</v>
@@ -8397,7 +8397,7 @@
         <v>32</v>
       </c>
       <c r="D249" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>33</v>
@@ -8414,7 +8414,7 @@
         <v>32</v>
       </c>
       <c r="D250" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>33</v>
@@ -8431,7 +8431,7 @@
         <v>32</v>
       </c>
       <c r="D251" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>33</v>
@@ -8448,7 +8448,7 @@
         <v>32</v>
       </c>
       <c r="D252" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>33</v>
@@ -8465,7 +8465,7 @@
         <v>32</v>
       </c>
       <c r="D253" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>33</v>
@@ -8482,7 +8482,7 @@
         <v>32</v>
       </c>
       <c r="D254" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>33</v>
@@ -8499,7 +8499,7 @@
         <v>32</v>
       </c>
       <c r="D255" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>33</v>
@@ -8516,7 +8516,7 @@
         <v>32</v>
       </c>
       <c r="D256" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>33</v>
@@ -8533,7 +8533,7 @@
         <v>32</v>
       </c>
       <c r="D257" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>33</v>
@@ -8550,7 +8550,7 @@
         <v>32</v>
       </c>
       <c r="D258" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>33</v>
@@ -8567,7 +8567,7 @@
         <v>32</v>
       </c>
       <c r="D259" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>33</v>
@@ -8584,7 +8584,7 @@
         <v>32</v>
       </c>
       <c r="D260" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>33</v>
@@ -8601,7 +8601,7 @@
         <v>32</v>
       </c>
       <c r="D261" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>33</v>
@@ -8618,7 +8618,7 @@
         <v>32</v>
       </c>
       <c r="D262" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>33</v>
@@ -8635,7 +8635,7 @@
         <v>32</v>
       </c>
       <c r="D263" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>33</v>
@@ -8652,7 +8652,7 @@
         <v>32</v>
       </c>
       <c r="D264" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>33</v>
@@ -8669,7 +8669,7 @@
         <v>32</v>
       </c>
       <c r="D265" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>33</v>
@@ -8686,7 +8686,7 @@
         <v>32</v>
       </c>
       <c r="D266" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>33</v>
@@ -8703,7 +8703,7 @@
         <v>32</v>
       </c>
       <c r="D267" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>33</v>
@@ -8720,7 +8720,7 @@
         <v>32</v>
       </c>
       <c r="D268" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>33</v>
@@ -8737,7 +8737,7 @@
         <v>32</v>
       </c>
       <c r="D269" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>33</v>
@@ -8754,7 +8754,7 @@
         <v>32</v>
       </c>
       <c r="D270" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>33</v>
@@ -8771,7 +8771,7 @@
         <v>32</v>
       </c>
       <c r="D271" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>33</v>
@@ -8788,7 +8788,7 @@
         <v>32</v>
       </c>
       <c r="D272" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>33</v>
@@ -8805,7 +8805,7 @@
         <v>32</v>
       </c>
       <c r="D273" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>33</v>
@@ -8822,7 +8822,7 @@
         <v>32</v>
       </c>
       <c r="D274" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>33</v>
@@ -8839,7 +8839,7 @@
         <v>32</v>
       </c>
       <c r="D275" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>33</v>
@@ -8856,7 +8856,7 @@
         <v>32</v>
       </c>
       <c r="D276" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>33</v>
@@ -8873,7 +8873,7 @@
         <v>32</v>
       </c>
       <c r="D277" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>33</v>
@@ -8890,7 +8890,7 @@
         <v>32</v>
       </c>
       <c r="D278" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>33</v>
@@ -8907,7 +8907,7 @@
         <v>32</v>
       </c>
       <c r="D279" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>33</v>
@@ -8924,7 +8924,7 @@
         <v>32</v>
       </c>
       <c r="D280" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>33</v>
@@ -8941,7 +8941,7 @@
         <v>32</v>
       </c>
       <c r="D281" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>33</v>
@@ -8958,7 +8958,7 @@
         <v>32</v>
       </c>
       <c r="D282" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>33</v>
@@ -8975,7 +8975,7 @@
         <v>32</v>
       </c>
       <c r="D283" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>33</v>
@@ -8992,7 +8992,7 @@
         <v>32</v>
       </c>
       <c r="D284" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>33</v>
@@ -9009,7 +9009,7 @@
         <v>32</v>
       </c>
       <c r="D285" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>33</v>
@@ -9026,7 +9026,7 @@
         <v>32</v>
       </c>
       <c r="D286" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>33</v>
@@ -9043,7 +9043,7 @@
         <v>32</v>
       </c>
       <c r="D287" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>33</v>
@@ -9060,7 +9060,7 @@
         <v>32</v>
       </c>
       <c r="D288" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>33</v>
@@ -9077,7 +9077,7 @@
         <v>32</v>
       </c>
       <c r="D289" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>33</v>
@@ -9094,7 +9094,7 @@
         <v>32</v>
       </c>
       <c r="D290" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>33</v>
@@ -9111,7 +9111,7 @@
         <v>32</v>
       </c>
       <c r="D291" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>33</v>
@@ -9128,7 +9128,7 @@
         <v>32</v>
       </c>
       <c r="D292" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>33</v>
@@ -9145,7 +9145,7 @@
         <v>32</v>
       </c>
       <c r="D293" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>33</v>
@@ -9162,7 +9162,7 @@
         <v>32</v>
       </c>
       <c r="D294" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>33</v>
@@ -9179,7 +9179,7 @@
         <v>32</v>
       </c>
       <c r="D295" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>33</v>
@@ -9213,7 +9213,7 @@
         <v>32</v>
       </c>
       <c r="D297" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>33</v>
@@ -9230,7 +9230,7 @@
         <v>32</v>
       </c>
       <c r="D298" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>33</v>
@@ -9247,7 +9247,7 @@
         <v>32</v>
       </c>
       <c r="D299" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>33</v>
@@ -9264,7 +9264,7 @@
         <v>32</v>
       </c>
       <c r="D300" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>33</v>
@@ -9281,7 +9281,7 @@
         <v>32</v>
       </c>
       <c r="D301" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>33</v>
@@ -9298,7 +9298,7 @@
         <v>32</v>
       </c>
       <c r="D302" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>33</v>
@@ -9332,7 +9332,7 @@
         <v>32</v>
       </c>
       <c r="D304" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>33</v>
@@ -9366,7 +9366,7 @@
         <v>32</v>
       </c>
       <c r="D306" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>33</v>
@@ -9383,7 +9383,7 @@
         <v>32</v>
       </c>
       <c r="D307" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>33</v>
@@ -9400,7 +9400,7 @@
         <v>32</v>
       </c>
       <c r="D308" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>33</v>
@@ -9417,7 +9417,7 @@
         <v>32</v>
       </c>
       <c r="D309" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>33</v>
@@ -9434,7 +9434,7 @@
         <v>32</v>
       </c>
       <c r="D310" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>33</v>
@@ -9468,7 +9468,7 @@
         <v>32</v>
       </c>
       <c r="D312" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>33</v>
@@ -9502,7 +9502,7 @@
         <v>32</v>
       </c>
       <c r="D314" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>33</v>
@@ -9519,7 +9519,7 @@
         <v>32</v>
       </c>
       <c r="D315" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>33</v>
@@ -9536,7 +9536,7 @@
         <v>32</v>
       </c>
       <c r="D316" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>33</v>
@@ -9553,7 +9553,7 @@
         <v>32</v>
       </c>
       <c r="D317" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>33</v>
@@ -9570,7 +9570,7 @@
         <v>32</v>
       </c>
       <c r="D318" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>33</v>
@@ -9587,7 +9587,7 @@
         <v>32</v>
       </c>
       <c r="D319" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>33</v>
@@ -9604,7 +9604,7 @@
         <v>32</v>
       </c>
       <c r="D320" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>33</v>
@@ -9621,7 +9621,7 @@
         <v>32</v>
       </c>
       <c r="D321" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>33</v>
@@ -9638,7 +9638,7 @@
         <v>32</v>
       </c>
       <c r="D322" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>33</v>
@@ -9655,7 +9655,7 @@
         <v>32</v>
       </c>
       <c r="D323" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>33</v>
@@ -9689,7 +9689,7 @@
         <v>32</v>
       </c>
       <c r="D325" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>33</v>
@@ -9706,7 +9706,7 @@
         <v>32</v>
       </c>
       <c r="D326" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>33</v>
@@ -9723,7 +9723,7 @@
         <v>32</v>
       </c>
       <c r="D327" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>33</v>
@@ -9740,7 +9740,7 @@
         <v>32</v>
       </c>
       <c r="D328" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>33</v>
@@ -9757,7 +9757,7 @@
         <v>32</v>
       </c>
       <c r="D329" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>33</v>
@@ -9774,7 +9774,7 @@
         <v>32</v>
       </c>
       <c r="D330" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>33</v>
@@ -9791,7 +9791,7 @@
         <v>32</v>
       </c>
       <c r="D331" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>33</v>
@@ -9808,7 +9808,7 @@
         <v>32</v>
       </c>
       <c r="D332" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>33</v>
@@ -9825,7 +9825,7 @@
         <v>32</v>
       </c>
       <c r="D333" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>33</v>
@@ -9859,7 +9859,7 @@
         <v>32</v>
       </c>
       <c r="D335" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>33</v>
@@ -9876,7 +9876,7 @@
         <v>32</v>
       </c>
       <c r="D336" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>33</v>
@@ -9893,7 +9893,7 @@
         <v>32</v>
       </c>
       <c r="D337" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>33</v>
@@ -9910,7 +9910,7 @@
         <v>32</v>
       </c>
       <c r="D338" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>33</v>
@@ -9927,7 +9927,7 @@
         <v>32</v>
       </c>
       <c r="D339" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>33</v>
@@ -9944,7 +9944,7 @@
         <v>32</v>
       </c>
       <c r="D340" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>33</v>
@@ -9961,7 +9961,7 @@
         <v>32</v>
       </c>
       <c r="D341" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>33</v>
@@ -9978,7 +9978,7 @@
         <v>32</v>
       </c>
       <c r="D342" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>33</v>
@@ -9995,7 +9995,7 @@
         <v>32</v>
       </c>
       <c r="D343" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>33</v>
@@ -10012,7 +10012,7 @@
         <v>32</v>
       </c>
       <c r="D344" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>33</v>
@@ -10029,7 +10029,7 @@
         <v>32</v>
       </c>
       <c r="D345" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>33</v>
@@ -10046,7 +10046,7 @@
         <v>32</v>
       </c>
       <c r="D346" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>33</v>
@@ -10063,7 +10063,7 @@
         <v>32</v>
       </c>
       <c r="D347" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>33</v>
@@ -10080,7 +10080,7 @@
         <v>32</v>
       </c>
       <c r="D348" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>33</v>
@@ -10097,7 +10097,7 @@
         <v>32</v>
       </c>
       <c r="D349" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>33</v>
@@ -10114,7 +10114,7 @@
         <v>32</v>
       </c>
       <c r="D350" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>33</v>
@@ -10131,7 +10131,7 @@
         <v>32</v>
       </c>
       <c r="D351" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>33</v>
@@ -10148,7 +10148,7 @@
         <v>32</v>
       </c>
       <c r="D352" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>33</v>
@@ -10165,7 +10165,7 @@
         <v>32</v>
       </c>
       <c r="D353" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>33</v>
@@ -10182,7 +10182,7 @@
         <v>32</v>
       </c>
       <c r="D354" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>33</v>
@@ -10199,7 +10199,7 @@
         <v>32</v>
       </c>
       <c r="D355" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>33</v>
@@ -10216,7 +10216,7 @@
         <v>32</v>
       </c>
       <c r="D356" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>33</v>
@@ -10233,7 +10233,7 @@
         <v>32</v>
       </c>
       <c r="D357" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>33</v>
@@ -10267,7 +10267,7 @@
         <v>32</v>
       </c>
       <c r="D359" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>33</v>
@@ -10284,7 +10284,7 @@
         <v>32</v>
       </c>
       <c r="D360" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>33</v>
@@ -10301,7 +10301,7 @@
         <v>32</v>
       </c>
       <c r="D361" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>33</v>
@@ -10318,7 +10318,7 @@
         <v>32</v>
       </c>
       <c r="D362" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>33</v>
@@ -10335,7 +10335,7 @@
         <v>32</v>
       </c>
       <c r="D363" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>33</v>
@@ -10352,7 +10352,7 @@
         <v>32</v>
       </c>
       <c r="D364" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>33</v>
@@ -10369,7 +10369,7 @@
         <v>32</v>
       </c>
       <c r="D365" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>33</v>
@@ -10386,7 +10386,7 @@
         <v>32</v>
       </c>
       <c r="D366" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>33</v>
@@ -10403,7 +10403,7 @@
         <v>32</v>
       </c>
       <c r="D367" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>33</v>
@@ -10420,7 +10420,7 @@
         <v>32</v>
       </c>
       <c r="D368" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>33</v>
@@ -10437,7 +10437,7 @@
         <v>32</v>
       </c>
       <c r="D369" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>33</v>
@@ -10454,7 +10454,7 @@
         <v>32</v>
       </c>
       <c r="D370" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>33</v>
@@ -10471,7 +10471,7 @@
         <v>32</v>
       </c>
       <c r="D371" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>33</v>
@@ -10488,7 +10488,7 @@
         <v>32</v>
       </c>
       <c r="D372" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>33</v>
@@ -10505,7 +10505,7 @@
         <v>32</v>
       </c>
       <c r="D373" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>33</v>
@@ -10522,7 +10522,7 @@
         <v>32</v>
       </c>
       <c r="D374" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>33</v>
@@ -10539,7 +10539,7 @@
         <v>32</v>
       </c>
       <c r="D375" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>33</v>
@@ -10556,7 +10556,7 @@
         <v>32</v>
       </c>
       <c r="D376" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>33</v>
@@ -10573,7 +10573,7 @@
         <v>32</v>
       </c>
       <c r="D377" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>33</v>
@@ -10590,7 +10590,7 @@
         <v>32</v>
       </c>
       <c r="D378" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>33</v>
@@ -10607,7 +10607,7 @@
         <v>32</v>
       </c>
       <c r="D379" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>33</v>
@@ -10624,7 +10624,7 @@
         <v>32</v>
       </c>
       <c r="D380" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>33</v>
@@ -10641,7 +10641,7 @@
         <v>32</v>
       </c>
       <c r="D381" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>33</v>
@@ -10658,7 +10658,7 @@
         <v>32</v>
       </c>
       <c r="D382" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>33</v>
@@ -10675,7 +10675,7 @@
         <v>32</v>
       </c>
       <c r="D383" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>33</v>
@@ -10692,7 +10692,7 @@
         <v>32</v>
       </c>
       <c r="D384" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>33</v>
@@ -10709,7 +10709,7 @@
         <v>32</v>
       </c>
       <c r="D385" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>33</v>
@@ -10726,7 +10726,7 @@
         <v>32</v>
       </c>
       <c r="D386" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>33</v>
@@ -10760,7 +10760,7 @@
         <v>32</v>
       </c>
       <c r="D388" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>33</v>
@@ -10777,7 +10777,7 @@
         <v>32</v>
       </c>
       <c r="D389" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>33</v>
@@ -10794,7 +10794,7 @@
         <v>32</v>
       </c>
       <c r="D390" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>33</v>
@@ -10811,7 +10811,7 @@
         <v>32</v>
       </c>
       <c r="D391" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>33</v>
@@ -10828,7 +10828,7 @@
         <v>32</v>
       </c>
       <c r="D392" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>33</v>
@@ -10845,7 +10845,7 @@
         <v>32</v>
       </c>
       <c r="D393" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>33</v>
@@ -10862,7 +10862,7 @@
         <v>32</v>
       </c>
       <c r="D394" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>33</v>
@@ -10879,7 +10879,7 @@
         <v>32</v>
       </c>
       <c r="D395" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>33</v>
@@ -10896,7 +10896,7 @@
         <v>32</v>
       </c>
       <c r="D396" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>33</v>
@@ -10930,7 +10930,7 @@
         <v>32</v>
       </c>
       <c r="D398" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>33</v>
@@ -10947,7 +10947,7 @@
         <v>32</v>
       </c>
       <c r="D399" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>33</v>
@@ -10964,7 +10964,7 @@
         <v>32</v>
       </c>
       <c r="D400" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>33</v>
@@ -10981,7 +10981,7 @@
         <v>32</v>
       </c>
       <c r="D401" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>33</v>
@@ -10998,7 +10998,7 @@
         <v>32</v>
       </c>
       <c r="D402" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>33</v>
@@ -11015,7 +11015,7 @@
         <v>32</v>
       </c>
       <c r="D403" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>33</v>
@@ -11032,7 +11032,7 @@
         <v>32</v>
       </c>
       <c r="D404" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>33</v>
@@ -11049,7 +11049,7 @@
         <v>32</v>
       </c>
       <c r="D405" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>33</v>
@@ -11066,7 +11066,7 @@
         <v>32</v>
       </c>
       <c r="D406" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>33</v>
@@ -11083,7 +11083,7 @@
         <v>32</v>
       </c>
       <c r="D407" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>33</v>
@@ -11100,7 +11100,7 @@
         <v>32</v>
       </c>
       <c r="D408" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>33</v>
@@ -11117,7 +11117,7 @@
         <v>32</v>
       </c>
       <c r="D409" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>33</v>
@@ -11134,7 +11134,7 @@
         <v>32</v>
       </c>
       <c r="D410" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>33</v>
@@ -11151,7 +11151,7 @@
         <v>32</v>
       </c>
       <c r="D411" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>33</v>
@@ -11168,7 +11168,7 @@
         <v>32</v>
       </c>
       <c r="D412" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>33</v>
@@ -11185,7 +11185,7 @@
         <v>32</v>
       </c>
       <c r="D413" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>33</v>
@@ -11202,7 +11202,7 @@
         <v>32</v>
       </c>
       <c r="D414" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>33</v>
@@ -11219,7 +11219,7 @@
         <v>32</v>
       </c>
       <c r="D415" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>33</v>
@@ -11236,7 +11236,7 @@
         <v>32</v>
       </c>
       <c r="D416" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>33</v>
@@ -11253,7 +11253,7 @@
         <v>32</v>
       </c>
       <c r="D417" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>33</v>
@@ -11270,7 +11270,7 @@
         <v>32</v>
       </c>
       <c r="D418" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>33</v>
@@ -11287,7 +11287,7 @@
         <v>32</v>
       </c>
       <c r="D419" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>33</v>
@@ -11304,7 +11304,7 @@
         <v>32</v>
       </c>
       <c r="D420" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>33</v>
@@ -11321,7 +11321,7 @@
         <v>32</v>
       </c>
       <c r="D421" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>33</v>
@@ -11338,7 +11338,7 @@
         <v>32</v>
       </c>
       <c r="D422" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>33</v>
@@ -11355,7 +11355,7 @@
         <v>32</v>
       </c>
       <c r="D423" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>33</v>
@@ -11372,7 +11372,7 @@
         <v>32</v>
       </c>
       <c r="D424" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>33</v>
@@ -11389,7 +11389,7 @@
         <v>32</v>
       </c>
       <c r="D425" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>33</v>
@@ -11406,7 +11406,7 @@
         <v>32</v>
       </c>
       <c r="D426" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>33</v>
@@ -11423,7 +11423,7 @@
         <v>32</v>
       </c>
       <c r="D427" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>33</v>
@@ -11440,7 +11440,7 @@
         <v>32</v>
       </c>
       <c r="D428" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>33</v>
@@ -11457,7 +11457,7 @@
         <v>32</v>
       </c>
       <c r="D429" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>33</v>
@@ -11474,7 +11474,7 @@
         <v>32</v>
       </c>
       <c r="D430" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>33</v>
@@ -11491,7 +11491,7 @@
         <v>32</v>
       </c>
       <c r="D431" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>33</v>
@@ -11508,7 +11508,7 @@
         <v>32</v>
       </c>
       <c r="D432" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>33</v>
@@ -11525,7 +11525,7 @@
         <v>32</v>
       </c>
       <c r="D433" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>33</v>
@@ -11542,7 +11542,7 @@
         <v>32</v>
       </c>
       <c r="D434" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>33</v>
@@ -11559,7 +11559,7 @@
         <v>32</v>
       </c>
       <c r="D435" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>33</v>
@@ -11576,7 +11576,7 @@
         <v>32</v>
       </c>
       <c r="D436" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>33</v>
@@ -11593,7 +11593,7 @@
         <v>32</v>
       </c>
       <c r="D437" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>33</v>
@@ -11610,7 +11610,7 @@
         <v>32</v>
       </c>
       <c r="D438" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>33</v>
@@ -11627,7 +11627,7 @@
         <v>32</v>
       </c>
       <c r="D439" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>33</v>
@@ -11644,7 +11644,7 @@
         <v>32</v>
       </c>
       <c r="D440" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>33</v>
@@ -11661,7 +11661,7 @@
         <v>32</v>
       </c>
       <c r="D441" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>33</v>
@@ -11678,7 +11678,7 @@
         <v>32</v>
       </c>
       <c r="D442" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>33</v>
@@ -11695,7 +11695,7 @@
         <v>32</v>
       </c>
       <c r="D443" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>33</v>
@@ -11712,7 +11712,7 @@
         <v>32</v>
       </c>
       <c r="D444" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>33</v>
@@ -11729,7 +11729,7 @@
         <v>32</v>
       </c>
       <c r="D445" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>33</v>
@@ -11746,7 +11746,7 @@
         <v>32</v>
       </c>
       <c r="D446" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>33</v>
@@ -11763,7 +11763,7 @@
         <v>32</v>
       </c>
       <c r="D447" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>33</v>
@@ -11780,7 +11780,7 @@
         <v>32</v>
       </c>
       <c r="D448" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>33</v>
@@ -11797,7 +11797,7 @@
         <v>32</v>
       </c>
       <c r="D449" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>33</v>
@@ -11814,7 +11814,7 @@
         <v>32</v>
       </c>
       <c r="D450" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>33</v>
@@ -11831,7 +11831,7 @@
         <v>32</v>
       </c>
       <c r="D451" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>33</v>
@@ -11848,7 +11848,7 @@
         <v>32</v>
       </c>
       <c r="D452" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>33</v>
@@ -11865,7 +11865,7 @@
         <v>32</v>
       </c>
       <c r="D453" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>33</v>
@@ -11882,7 +11882,7 @@
         <v>32</v>
       </c>
       <c r="D454" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>33</v>
@@ -11899,7 +11899,7 @@
         <v>32</v>
       </c>
       <c r="D455" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>33</v>
@@ -11933,7 +11933,7 @@
         <v>32</v>
       </c>
       <c r="D457" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>33</v>
@@ -11967,7 +11967,7 @@
         <v>32</v>
       </c>
       <c r="D459" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>33</v>
@@ -11984,7 +11984,7 @@
         <v>32</v>
       </c>
       <c r="D460" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>33</v>
@@ -12001,7 +12001,7 @@
         <v>32</v>
       </c>
       <c r="D461" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>33</v>
@@ -12018,7 +12018,7 @@
         <v>32</v>
       </c>
       <c r="D462" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>33</v>
@@ -12035,7 +12035,7 @@
         <v>32</v>
       </c>
       <c r="D463" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>33</v>
@@ -12052,7 +12052,7 @@
         <v>32</v>
       </c>
       <c r="D464" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>33</v>
@@ -12069,7 +12069,7 @@
         <v>32</v>
       </c>
       <c r="D465" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>33</v>
@@ -12086,7 +12086,7 @@
         <v>32</v>
       </c>
       <c r="D466" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>33</v>
@@ -12103,7 +12103,7 @@
         <v>32</v>
       </c>
       <c r="D467" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>33</v>
@@ -12120,7 +12120,7 @@
         <v>32</v>
       </c>
       <c r="D468" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>33</v>
@@ -12137,7 +12137,7 @@
         <v>32</v>
       </c>
       <c r="D469" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>33</v>
@@ -12154,7 +12154,7 @@
         <v>32</v>
       </c>
       <c r="D470" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E470" s="2" t="s">
         <v>33</v>
@@ -12171,7 +12171,7 @@
         <v>32</v>
       </c>
       <c r="D471" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>33</v>
@@ -12205,7 +12205,7 @@
         <v>32</v>
       </c>
       <c r="D473" s="2">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>33</v>
@@ -12222,7 +12222,7 @@
         <v>32</v>
       </c>
       <c r="D474" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>33</v>
@@ -12239,7 +12239,7 @@
         <v>32</v>
       </c>
       <c r="D475" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>33</v>
@@ -12256,7 +12256,7 @@
         <v>32</v>
       </c>
       <c r="D476" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>33</v>
@@ -12273,7 +12273,7 @@
         <v>32</v>
       </c>
       <c r="D477" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>33</v>
@@ -12290,7 +12290,7 @@
         <v>32</v>
       </c>
       <c r="D478" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>33</v>
@@ -12307,7 +12307,7 @@
         <v>32</v>
       </c>
       <c r="D479" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>33</v>
@@ -12324,7 +12324,7 @@
         <v>32</v>
       </c>
       <c r="D480" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>33</v>
@@ -12358,7 +12358,7 @@
         <v>32</v>
       </c>
       <c r="D482" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>33</v>
@@ -12375,7 +12375,7 @@
         <v>32</v>
       </c>
       <c r="D483" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>33</v>
@@ -12392,7 +12392,7 @@
         <v>32</v>
       </c>
       <c r="D484" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>33</v>
@@ -12409,7 +12409,7 @@
         <v>32</v>
       </c>
       <c r="D485" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>33</v>
@@ -12426,7 +12426,7 @@
         <v>32</v>
       </c>
       <c r="D486" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>33</v>
@@ -12443,7 +12443,7 @@
         <v>32</v>
       </c>
       <c r="D487" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>33</v>
@@ -12460,7 +12460,7 @@
         <v>32</v>
       </c>
       <c r="D488" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>33</v>
@@ -12477,7 +12477,7 @@
         <v>32</v>
       </c>
       <c r="D489" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>33</v>
@@ -12494,7 +12494,7 @@
         <v>32</v>
       </c>
       <c r="D490" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>33</v>
@@ -12511,7 +12511,7 @@
         <v>32</v>
       </c>
       <c r="D491" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>33</v>
@@ -12528,7 +12528,7 @@
         <v>32</v>
       </c>
       <c r="D492" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>33</v>
@@ -12545,7 +12545,7 @@
         <v>32</v>
       </c>
       <c r="D493" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>33</v>
@@ -12562,7 +12562,7 @@
         <v>32</v>
       </c>
       <c r="D494" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>33</v>
@@ -12579,7 +12579,7 @@
         <v>32</v>
       </c>
       <c r="D495" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>33</v>
@@ -12596,7 +12596,7 @@
         <v>32</v>
       </c>
       <c r="D496" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>33</v>
@@ -12613,7 +12613,7 @@
         <v>32</v>
       </c>
       <c r="D497" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>33</v>
@@ -12630,7 +12630,7 @@
         <v>32</v>
       </c>
       <c r="D498" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>33</v>
@@ -12647,7 +12647,7 @@
         <v>32</v>
       </c>
       <c r="D499" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>33</v>
@@ -12664,7 +12664,7 @@
         <v>32</v>
       </c>
       <c r="D500" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>33</v>
@@ -12681,7 +12681,7 @@
         <v>32</v>
       </c>
       <c r="D501" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>33</v>
@@ -12698,7 +12698,7 @@
         <v>32</v>
       </c>
       <c r="D502" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>33</v>
@@ -12732,7 +12732,7 @@
         <v>32</v>
       </c>
       <c r="D504" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>33</v>
@@ -12749,7 +12749,7 @@
         <v>32</v>
       </c>
       <c r="D505" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E505" s="2" t="s">
         <v>33</v>
@@ -12766,7 +12766,7 @@
         <v>32</v>
       </c>
       <c r="D506" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>33</v>
@@ -12783,7 +12783,7 @@
         <v>32</v>
       </c>
       <c r="D507" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>33</v>
@@ -12800,7 +12800,7 @@
         <v>32</v>
       </c>
       <c r="D508" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>33</v>
@@ -12834,7 +12834,7 @@
         <v>32</v>
       </c>
       <c r="D510" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E510" s="2" t="s">
         <v>33</v>
@@ -12851,7 +12851,7 @@
         <v>32</v>
       </c>
       <c r="D511" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E511" s="2" t="s">
         <v>33</v>
@@ -12868,7 +12868,7 @@
         <v>32</v>
       </c>
       <c r="D512" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>33</v>
@@ -12885,7 +12885,7 @@
         <v>32</v>
       </c>
       <c r="D513" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>33</v>
@@ -12902,7 +12902,7 @@
         <v>32</v>
       </c>
       <c r="D514" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>33</v>
@@ -12919,7 +12919,7 @@
         <v>32</v>
       </c>
       <c r="D515" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E515" s="2" t="s">
         <v>33</v>
@@ -12936,7 +12936,7 @@
         <v>32</v>
       </c>
       <c r="D516" s="2">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="E516" s="2" t="s">
         <v>33</v>
@@ -12953,7 +12953,7 @@
         <v>32</v>
       </c>
       <c r="D517" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>33</v>
@@ -12987,7 +12987,7 @@
         <v>32</v>
       </c>
       <c r="D519" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>33</v>
@@ -13004,7 +13004,7 @@
         <v>32</v>
       </c>
       <c r="D520" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E520" s="2" t="s">
         <v>33</v>
@@ -13038,7 +13038,7 @@
         <v>32</v>
       </c>
       <c r="D522" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>33</v>
@@ -13055,7 +13055,7 @@
         <v>32</v>
       </c>
       <c r="D523" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>33</v>
@@ -13072,7 +13072,7 @@
         <v>32</v>
       </c>
       <c r="D524" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>33</v>
@@ -13089,7 +13089,7 @@
         <v>32</v>
       </c>
       <c r="D525" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>33</v>
@@ -13106,7 +13106,7 @@
         <v>32</v>
       </c>
       <c r="D526" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>33</v>
@@ -13123,7 +13123,7 @@
         <v>32</v>
       </c>
       <c r="D527" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>33</v>
@@ -13140,7 +13140,7 @@
         <v>32</v>
       </c>
       <c r="D528" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E528" s="2" t="s">
         <v>33</v>
@@ -13157,7 +13157,7 @@
         <v>32</v>
       </c>
       <c r="D529" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E529" s="2" t="s">
         <v>33</v>
@@ -13191,7 +13191,7 @@
         <v>32</v>
       </c>
       <c r="D531" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>33</v>
@@ -13225,7 +13225,7 @@
         <v>32</v>
       </c>
       <c r="D533" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E533" s="2" t="s">
         <v>33</v>
@@ -13242,7 +13242,7 @@
         <v>32</v>
       </c>
       <c r="D534" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E534" s="2" t="s">
         <v>33</v>
@@ -13259,7 +13259,7 @@
         <v>32</v>
       </c>
       <c r="D535" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E535" s="2" t="s">
         <v>33</v>
@@ -13276,7 +13276,7 @@
         <v>32</v>
       </c>
       <c r="D536" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E536" s="2" t="s">
         <v>33</v>
@@ -13293,7 +13293,7 @@
         <v>32</v>
       </c>
       <c r="D537" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E537" s="2" t="s">
         <v>33</v>
@@ -13310,7 +13310,7 @@
         <v>32</v>
       </c>
       <c r="D538" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>33</v>
@@ -13327,7 +13327,7 @@
         <v>32</v>
       </c>
       <c r="D539" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>33</v>
@@ -13344,7 +13344,7 @@
         <v>32</v>
       </c>
       <c r="D540" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>33</v>
@@ -13361,7 +13361,7 @@
         <v>32</v>
       </c>
       <c r="D541" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>33</v>
@@ -13378,7 +13378,7 @@
         <v>32</v>
       </c>
       <c r="D542" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>33</v>
@@ -13395,7 +13395,7 @@
         <v>32</v>
       </c>
       <c r="D543" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E543" s="2" t="s">
         <v>33</v>
@@ -13412,7 +13412,7 @@
         <v>32</v>
       </c>
       <c r="D544" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>33</v>
@@ -13429,7 +13429,7 @@
         <v>32</v>
       </c>
       <c r="D545" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E545" s="2" t="s">
         <v>33</v>
@@ -13446,7 +13446,7 @@
         <v>32</v>
       </c>
       <c r="D546" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E546" s="2" t="s">
         <v>33</v>
@@ -13463,7 +13463,7 @@
         <v>32</v>
       </c>
       <c r="D547" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E547" s="2" t="s">
         <v>33</v>
@@ -13480,7 +13480,7 @@
         <v>32</v>
       </c>
       <c r="D548" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E548" s="2" t="s">
         <v>33</v>
@@ -13497,7 +13497,7 @@
         <v>32</v>
       </c>
       <c r="D549" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E549" s="2" t="s">
         <v>33</v>
@@ -13514,7 +13514,7 @@
         <v>32</v>
       </c>
       <c r="D550" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>33</v>
@@ -13531,7 +13531,7 @@
         <v>32</v>
       </c>
       <c r="D551" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E551" s="2" t="s">
         <v>33</v>
@@ -13548,7 +13548,7 @@
         <v>32</v>
       </c>
       <c r="D552" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E552" s="2" t="s">
         <v>33</v>
@@ -13582,7 +13582,7 @@
         <v>32</v>
       </c>
       <c r="D554" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>33</v>
@@ -13599,7 +13599,7 @@
         <v>32</v>
       </c>
       <c r="D555" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>33</v>
@@ -13616,7 +13616,7 @@
         <v>32</v>
       </c>
       <c r="D556" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>33</v>
@@ -13633,7 +13633,7 @@
         <v>32</v>
       </c>
       <c r="D557" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>33</v>
@@ -13650,7 +13650,7 @@
         <v>32</v>
       </c>
       <c r="D558" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E558" s="2" t="s">
         <v>33</v>
@@ -13667,7 +13667,7 @@
         <v>32</v>
       </c>
       <c r="D559" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>33</v>
@@ -13684,7 +13684,7 @@
         <v>32</v>
       </c>
       <c r="D560" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E560" s="2" t="s">
         <v>33</v>
@@ -13701,7 +13701,7 @@
         <v>32</v>
       </c>
       <c r="D561" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>33</v>
@@ -13718,7 +13718,7 @@
         <v>32</v>
       </c>
       <c r="D562" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E562" s="2" t="s">
         <v>33</v>
@@ -13735,7 +13735,7 @@
         <v>32</v>
       </c>
       <c r="D563" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>33</v>
@@ -13752,7 +13752,7 @@
         <v>32</v>
       </c>
       <c r="D564" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E564" s="2" t="s">
         <v>33</v>
@@ -13769,7 +13769,7 @@
         <v>32</v>
       </c>
       <c r="D565" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E565" s="2" t="s">
         <v>33</v>
@@ -13786,7 +13786,7 @@
         <v>32</v>
       </c>
       <c r="D566" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>33</v>
@@ -13803,7 +13803,7 @@
         <v>32</v>
       </c>
       <c r="D567" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>33</v>
@@ -13820,7 +13820,7 @@
         <v>32</v>
       </c>
       <c r="D568" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E568" s="2" t="s">
         <v>33</v>
@@ -13837,7 +13837,7 @@
         <v>32</v>
       </c>
       <c r="D569" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E569" s="2" t="s">
         <v>33</v>
@@ -13854,7 +13854,7 @@
         <v>32</v>
       </c>
       <c r="D570" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E570" s="2" t="s">
         <v>33</v>
@@ -13871,7 +13871,7 @@
         <v>32</v>
       </c>
       <c r="D571" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E571" s="2" t="s">
         <v>33</v>
@@ -13888,7 +13888,7 @@
         <v>32</v>
       </c>
       <c r="D572" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E572" s="2" t="s">
         <v>33</v>
@@ -13905,7 +13905,7 @@
         <v>32</v>
       </c>
       <c r="D573" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E573" s="2" t="s">
         <v>33</v>
@@ -13922,7 +13922,7 @@
         <v>32</v>
       </c>
       <c r="D574" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E574" s="2" t="s">
         <v>33</v>
@@ -13939,7 +13939,7 @@
         <v>32</v>
       </c>
       <c r="D575" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>33</v>
@@ -13956,7 +13956,7 @@
         <v>32</v>
       </c>
       <c r="D576" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E576" s="2" t="s">
         <v>33</v>
@@ -13973,7 +13973,7 @@
         <v>32</v>
       </c>
       <c r="D577" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>33</v>
@@ -13990,7 +13990,7 @@
         <v>32</v>
       </c>
       <c r="D578" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E578" s="2" t="s">
         <v>33</v>
@@ -14024,7 +14024,7 @@
         <v>32</v>
       </c>
       <c r="D580" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E580" s="2" t="s">
         <v>33</v>
@@ -14041,7 +14041,7 @@
         <v>32</v>
       </c>
       <c r="D581" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>33</v>
@@ -14058,7 +14058,7 @@
         <v>32</v>
       </c>
       <c r="D582" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E582" s="2" t="s">
         <v>33</v>
@@ -14075,7 +14075,7 @@
         <v>32</v>
       </c>
       <c r="D583" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>33</v>
@@ -14092,7 +14092,7 @@
         <v>32</v>
       </c>
       <c r="D584" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>33</v>
@@ -14109,7 +14109,7 @@
         <v>32</v>
       </c>
       <c r="D585" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E585" s="2" t="s">
         <v>33</v>
@@ -14126,7 +14126,7 @@
         <v>32</v>
       </c>
       <c r="D586" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E586" s="2" t="s">
         <v>33</v>
@@ -14143,7 +14143,7 @@
         <v>32</v>
       </c>
       <c r="D587" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E587" s="2" t="s">
         <v>33</v>
@@ -14160,7 +14160,7 @@
         <v>32</v>
       </c>
       <c r="D588" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E588" s="2" t="s">
         <v>33</v>
@@ -14194,7 +14194,7 @@
         <v>32</v>
       </c>
       <c r="D590" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E590" s="2" t="s">
         <v>33</v>
@@ -14211,7 +14211,7 @@
         <v>32</v>
       </c>
       <c r="D591" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E591" s="2" t="s">
         <v>33</v>
@@ -14228,7 +14228,7 @@
         <v>32</v>
       </c>
       <c r="D592" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E592" s="2" t="s">
         <v>33</v>
@@ -14245,7 +14245,7 @@
         <v>32</v>
       </c>
       <c r="D593" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>33</v>
@@ -14262,7 +14262,7 @@
         <v>32</v>
       </c>
       <c r="D594" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E594" s="2" t="s">
         <v>33</v>
@@ -14279,7 +14279,7 @@
         <v>32</v>
       </c>
       <c r="D595" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E595" s="2" t="s">
         <v>33</v>
@@ -14296,7 +14296,7 @@
         <v>32</v>
       </c>
       <c r="D596" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E596" s="2" t="s">
         <v>33</v>
@@ -14313,7 +14313,7 @@
         <v>32</v>
       </c>
       <c r="D597" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E597" s="2" t="s">
         <v>33</v>
@@ -14330,7 +14330,7 @@
         <v>32</v>
       </c>
       <c r="D598" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E598" s="2" t="s">
         <v>33</v>
@@ -14347,7 +14347,7 @@
         <v>32</v>
       </c>
       <c r="D599" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E599" s="2" t="s">
         <v>33</v>
@@ -14364,7 +14364,7 @@
         <v>32</v>
       </c>
       <c r="D600" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E600" s="2" t="s">
         <v>33</v>
@@ -14398,7 +14398,7 @@
         <v>32</v>
       </c>
       <c r="D602" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>33</v>
@@ -14415,7 +14415,7 @@
         <v>32</v>
       </c>
       <c r="D603" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E603" s="2" t="s">
         <v>33</v>
@@ -14432,7 +14432,7 @@
         <v>32</v>
       </c>
       <c r="D604" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E604" s="2" t="s">
         <v>33</v>
@@ -14449,7 +14449,7 @@
         <v>32</v>
       </c>
       <c r="D605" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E605" s="2" t="s">
         <v>33</v>
@@ -14466,7 +14466,7 @@
         <v>32</v>
       </c>
       <c r="D606" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>33</v>
@@ -14483,7 +14483,7 @@
         <v>32</v>
       </c>
       <c r="D607" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>33</v>
@@ -14500,7 +14500,7 @@
         <v>32</v>
       </c>
       <c r="D608" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E608" s="2" t="s">
         <v>33</v>
@@ -14517,7 +14517,7 @@
         <v>32</v>
       </c>
       <c r="D609" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E609" s="2" t="s">
         <v>33</v>
@@ -14534,7 +14534,7 @@
         <v>32</v>
       </c>
       <c r="D610" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>33</v>
@@ -14551,7 +14551,7 @@
         <v>32</v>
       </c>
       <c r="D611" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E611" s="2" t="s">
         <v>33</v>
@@ -14568,7 +14568,7 @@
         <v>32</v>
       </c>
       <c r="D612" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E612" s="2" t="s">
         <v>33</v>
@@ -14585,7 +14585,7 @@
         <v>32</v>
       </c>
       <c r="D613" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E613" s="2" t="s">
         <v>33</v>
@@ -14602,7 +14602,7 @@
         <v>32</v>
       </c>
       <c r="D614" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E614" s="2" t="s">
         <v>33</v>
@@ -14619,7 +14619,7 @@
         <v>32</v>
       </c>
       <c r="D615" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E615" s="2" t="s">
         <v>33</v>
@@ -14636,7 +14636,7 @@
         <v>32</v>
       </c>
       <c r="D616" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E616" s="2" t="s">
         <v>33</v>
@@ -14653,7 +14653,7 @@
         <v>32</v>
       </c>
       <c r="D617" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E617" s="2" t="s">
         <v>33</v>
@@ -14670,7 +14670,7 @@
         <v>32</v>
       </c>
       <c r="D618" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E618" s="2" t="s">
         <v>33</v>
@@ -14704,7 +14704,7 @@
         <v>32</v>
       </c>
       <c r="D620" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E620" s="2" t="s">
         <v>33</v>
@@ -14721,7 +14721,7 @@
         <v>32</v>
       </c>
       <c r="D621" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E621" s="2" t="s">
         <v>33</v>
@@ -14738,7 +14738,7 @@
         <v>32</v>
       </c>
       <c r="D622" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E622" s="2" t="s">
         <v>33</v>
@@ -14755,7 +14755,7 @@
         <v>32</v>
       </c>
       <c r="D623" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E623" s="2" t="s">
         <v>33</v>
@@ -14772,7 +14772,7 @@
         <v>32</v>
       </c>
       <c r="D624" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E624" s="2" t="s">
         <v>33</v>
@@ -14789,7 +14789,7 @@
         <v>32</v>
       </c>
       <c r="D625" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E625" s="2" t="s">
         <v>33</v>
@@ -14806,7 +14806,7 @@
         <v>32</v>
       </c>
       <c r="D626" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E626" s="2" t="s">
         <v>33</v>
@@ -14823,7 +14823,7 @@
         <v>32</v>
       </c>
       <c r="D627" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E627" s="2" t="s">
         <v>33</v>
@@ -14840,7 +14840,7 @@
         <v>32</v>
       </c>
       <c r="D628" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E628" s="2" t="s">
         <v>33</v>
@@ -14874,7 +14874,7 @@
         <v>32</v>
       </c>
       <c r="D630" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E630" s="2" t="s">
         <v>33</v>
@@ -14891,7 +14891,7 @@
         <v>32</v>
       </c>
       <c r="D631" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E631" s="2" t="s">
         <v>33</v>
@@ -14908,7 +14908,7 @@
         <v>32</v>
       </c>
       <c r="D632" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E632" s="2" t="s">
         <v>33</v>
@@ -14925,7 +14925,7 @@
         <v>32</v>
       </c>
       <c r="D633" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E633" s="2" t="s">
         <v>33</v>
@@ -14942,7 +14942,7 @@
         <v>32</v>
       </c>
       <c r="D634" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E634" s="2" t="s">
         <v>33</v>
@@ -14959,7 +14959,7 @@
         <v>32</v>
       </c>
       <c r="D635" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E635" s="2" t="s">
         <v>33</v>
@@ -14976,7 +14976,7 @@
         <v>32</v>
       </c>
       <c r="D636" s="2">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E636" s="2" t="s">
         <v>33</v>
@@ -14993,7 +14993,7 @@
         <v>32</v>
       </c>
       <c r="D637" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E637" s="2" t="s">
         <v>33</v>
@@ -15010,7 +15010,7 @@
         <v>32</v>
       </c>
       <c r="D638" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E638" s="2" t="s">
         <v>33</v>
@@ -15027,7 +15027,7 @@
         <v>32</v>
       </c>
       <c r="D639" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E639" s="2" t="s">
         <v>33</v>
@@ -15044,7 +15044,7 @@
         <v>32</v>
       </c>
       <c r="D640" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E640" s="2" t="s">
         <v>33</v>
@@ -15061,7 +15061,7 @@
         <v>32</v>
       </c>
       <c r="D641" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>33</v>
@@ -15078,7 +15078,7 @@
         <v>32</v>
       </c>
       <c r="D642" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E642" s="2" t="s">
         <v>33</v>
@@ -15095,7 +15095,7 @@
         <v>32</v>
       </c>
       <c r="D643" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E643" s="2" t="s">
         <v>33</v>
@@ -15112,7 +15112,7 @@
         <v>32</v>
       </c>
       <c r="D644" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E644" s="2" t="s">
         <v>33</v>
@@ -15129,7 +15129,7 @@
         <v>32</v>
       </c>
       <c r="D645" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E645" s="2" t="s">
         <v>33</v>
@@ -15146,7 +15146,7 @@
         <v>32</v>
       </c>
       <c r="D646" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E646" s="2" t="s">
         <v>33</v>
@@ -15180,7 +15180,7 @@
         <v>32</v>
       </c>
       <c r="D648" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E648" s="2" t="s">
         <v>33</v>
@@ -15197,7 +15197,7 @@
         <v>32</v>
       </c>
       <c r="D649" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E649" s="2" t="s">
         <v>33</v>
@@ -15214,7 +15214,7 @@
         <v>32</v>
       </c>
       <c r="D650" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E650" s="2" t="s">
         <v>33</v>
@@ -15231,7 +15231,7 @@
         <v>32</v>
       </c>
       <c r="D651" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E651" s="2" t="s">
         <v>33</v>
@@ -15248,7 +15248,7 @@
         <v>32</v>
       </c>
       <c r="D652" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E652" s="2" t="s">
         <v>33</v>
@@ -15265,7 +15265,7 @@
         <v>32</v>
       </c>
       <c r="D653" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E653" s="2" t="s">
         <v>33</v>
@@ -15282,7 +15282,7 @@
         <v>32</v>
       </c>
       <c r="D654" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E654" s="2" t="s">
         <v>33</v>
@@ -15299,7 +15299,7 @@
         <v>32</v>
       </c>
       <c r="D655" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E655" s="2" t="s">
         <v>33</v>
@@ -15316,7 +15316,7 @@
         <v>32</v>
       </c>
       <c r="D656" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E656" s="2" t="s">
         <v>33</v>
@@ -15333,7 +15333,7 @@
         <v>32</v>
       </c>
       <c r="D657" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E657" s="2" t="s">
         <v>33</v>
@@ -15350,7 +15350,7 @@
         <v>32</v>
       </c>
       <c r="D658" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E658" s="2" t="s">
         <v>33</v>
@@ -15367,7 +15367,7 @@
         <v>32</v>
       </c>
       <c r="D659" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E659" s="2" t="s">
         <v>33</v>
@@ -15384,7 +15384,7 @@
         <v>32</v>
       </c>
       <c r="D660" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E660" s="2" t="s">
         <v>33</v>
@@ -15401,7 +15401,7 @@
         <v>32</v>
       </c>
       <c r="D661" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E661" s="2" t="s">
         <v>33</v>
@@ -15435,7 +15435,7 @@
         <v>32</v>
       </c>
       <c r="D663" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E663" s="2" t="s">
         <v>33</v>
@@ -15452,7 +15452,7 @@
         <v>32</v>
       </c>
       <c r="D664" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E664" s="2" t="s">
         <v>33</v>
@@ -15469,7 +15469,7 @@
         <v>32</v>
       </c>
       <c r="D665" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E665" s="2" t="s">
         <v>33</v>
@@ -15486,7 +15486,7 @@
         <v>32</v>
       </c>
       <c r="D666" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E666" s="2" t="s">
         <v>33</v>
@@ -15503,7 +15503,7 @@
         <v>32</v>
       </c>
       <c r="D667" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E667" s="2" t="s">
         <v>33</v>
@@ -15520,7 +15520,7 @@
         <v>32</v>
       </c>
       <c r="D668" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E668" s="2" t="s">
         <v>33</v>
@@ -15537,7 +15537,7 @@
         <v>32</v>
       </c>
       <c r="D669" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E669" s="2" t="s">
         <v>33</v>
@@ -15554,7 +15554,7 @@
         <v>32</v>
       </c>
       <c r="D670" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E670" s="2" t="s">
         <v>33</v>
@@ -15571,7 +15571,7 @@
         <v>32</v>
       </c>
       <c r="D671" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E671" s="2" t="s">
         <v>33</v>
@@ -15588,7 +15588,7 @@
         <v>32</v>
       </c>
       <c r="D672" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E672" s="2" t="s">
         <v>33</v>
@@ -15605,7 +15605,7 @@
         <v>32</v>
       </c>
       <c r="D673" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E673" s="2" t="s">
         <v>33</v>
@@ -15639,7 +15639,7 @@
         <v>32</v>
       </c>
       <c r="D675" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E675" s="2" t="s">
         <v>33</v>
@@ -15656,7 +15656,7 @@
         <v>32</v>
       </c>
       <c r="D676" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E676" s="2" t="s">
         <v>33</v>
@@ -15673,7 +15673,7 @@
         <v>32</v>
       </c>
       <c r="D677" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E677" s="2" t="s">
         <v>33</v>
@@ -15690,7 +15690,7 @@
         <v>32</v>
       </c>
       <c r="D678" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E678" s="2" t="s">
         <v>33</v>
@@ -15707,7 +15707,7 @@
         <v>32</v>
       </c>
       <c r="D679" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E679" s="2" t="s">
         <v>33</v>
@@ -15724,7 +15724,7 @@
         <v>32</v>
       </c>
       <c r="D680" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E680" s="2" t="s">
         <v>33</v>
@@ -15741,7 +15741,7 @@
         <v>32</v>
       </c>
       <c r="D681" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E681" s="2" t="s">
         <v>33</v>
@@ -15758,7 +15758,7 @@
         <v>32</v>
       </c>
       <c r="D682" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E682" s="2" t="s">
         <v>33</v>
@@ -15792,7 +15792,7 @@
         <v>32</v>
       </c>
       <c r="D684" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E684" s="2" t="s">
         <v>33</v>
@@ -15809,7 +15809,7 @@
         <v>32</v>
       </c>
       <c r="D685" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E685" s="2" t="s">
         <v>33</v>
@@ -15843,7 +15843,7 @@
         <v>32</v>
       </c>
       <c r="D687" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E687" s="2" t="s">
         <v>33</v>
@@ -15860,7 +15860,7 @@
         <v>32</v>
       </c>
       <c r="D688" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E688" s="2" t="s">
         <v>33</v>
@@ -15877,7 +15877,7 @@
         <v>32</v>
       </c>
       <c r="D689" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E689" s="2" t="s">
         <v>33</v>
@@ -15911,7 +15911,7 @@
         <v>32</v>
       </c>
       <c r="D691" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E691" s="2" t="s">
         <v>33</v>
@@ -15928,7 +15928,7 @@
         <v>32</v>
       </c>
       <c r="D692" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E692" s="2" t="s">
         <v>33</v>
@@ -15945,7 +15945,7 @@
         <v>32</v>
       </c>
       <c r="D693" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E693" s="2" t="s">
         <v>33</v>
@@ -15962,7 +15962,7 @@
         <v>32</v>
       </c>
       <c r="D694" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E694" s="2" t="s">
         <v>33</v>
@@ -15996,7 +15996,7 @@
         <v>32</v>
       </c>
       <c r="D696" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E696" s="2" t="s">
         <v>33</v>
@@ -16013,7 +16013,7 @@
         <v>32</v>
       </c>
       <c r="D697" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E697" s="2" t="s">
         <v>33</v>
@@ -16030,7 +16030,7 @@
         <v>32</v>
       </c>
       <c r="D698" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E698" s="2" t="s">
         <v>33</v>
@@ -16047,7 +16047,7 @@
         <v>32</v>
       </c>
       <c r="D699" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E699" s="2" t="s">
         <v>33</v>
@@ -16064,7 +16064,7 @@
         <v>32</v>
       </c>
       <c r="D700" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E700" s="2" t="s">
         <v>33</v>
@@ -16081,7 +16081,7 @@
         <v>32</v>
       </c>
       <c r="D701" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E701" s="2" t="s">
         <v>33</v>
@@ -16098,7 +16098,7 @@
         <v>32</v>
       </c>
       <c r="D702" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E702" s="2" t="s">
         <v>33</v>
@@ -16115,7 +16115,7 @@
         <v>32</v>
       </c>
       <c r="D703" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E703" s="2" t="s">
         <v>33</v>
@@ -16132,7 +16132,7 @@
         <v>32</v>
       </c>
       <c r="D704" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E704" s="2" t="s">
         <v>33</v>
@@ -16149,7 +16149,7 @@
         <v>32</v>
       </c>
       <c r="D705" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E705" s="2" t="s">
         <v>33</v>
@@ -16166,7 +16166,7 @@
         <v>32</v>
       </c>
       <c r="D706" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E706" s="2" t="s">
         <v>33</v>
@@ -16183,7 +16183,7 @@
         <v>32</v>
       </c>
       <c r="D707" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E707" s="2" t="s">
         <v>33</v>
@@ -16200,7 +16200,7 @@
         <v>32</v>
       </c>
       <c r="D708" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E708" s="2" t="s">
         <v>33</v>
@@ -16217,7 +16217,7 @@
         <v>32</v>
       </c>
       <c r="D709" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E709" s="2" t="s">
         <v>33</v>
@@ -16234,7 +16234,7 @@
         <v>32</v>
       </c>
       <c r="D710" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E710" s="2" t="s">
         <v>33</v>
@@ -16268,7 +16268,7 @@
         <v>32</v>
       </c>
       <c r="D712" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E712" s="2" t="s">
         <v>33</v>
@@ -16285,7 +16285,7 @@
         <v>32</v>
       </c>
       <c r="D713" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E713" s="2" t="s">
         <v>33</v>
@@ -16302,7 +16302,7 @@
         <v>32</v>
       </c>
       <c r="D714" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E714" s="2" t="s">
         <v>33</v>
@@ -16319,7 +16319,7 @@
         <v>32</v>
       </c>
       <c r="D715" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E715" s="2" t="s">
         <v>33</v>
@@ -16336,7 +16336,7 @@
         <v>32</v>
       </c>
       <c r="D716" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E716" s="2" t="s">
         <v>33</v>
@@ -16353,7 +16353,7 @@
         <v>32</v>
       </c>
       <c r="D717" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E717" s="2" t="s">
         <v>33</v>
@@ -16370,7 +16370,7 @@
         <v>32</v>
       </c>
       <c r="D718" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E718" s="2" t="s">
         <v>33</v>
@@ -16387,7 +16387,7 @@
         <v>32</v>
       </c>
       <c r="D719" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E719" s="2" t="s">
         <v>33</v>
@@ -16404,7 +16404,7 @@
         <v>32</v>
       </c>
       <c r="D720" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E720" s="2" t="s">
         <v>33</v>
@@ -16421,7 +16421,7 @@
         <v>32</v>
       </c>
       <c r="D721" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E721" s="2" t="s">
         <v>33</v>
@@ -16438,7 +16438,7 @@
         <v>32</v>
       </c>
       <c r="D722" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E722" s="2" t="s">
         <v>33</v>
@@ -16455,7 +16455,7 @@
         <v>32</v>
       </c>
       <c r="D723" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E723" s="2" t="s">
         <v>33</v>
@@ -16472,7 +16472,7 @@
         <v>32</v>
       </c>
       <c r="D724" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E724" s="2" t="s">
         <v>33</v>
@@ -16489,7 +16489,7 @@
         <v>32</v>
       </c>
       <c r="D725" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E725" s="2" t="s">
         <v>33</v>
@@ -16506,7 +16506,7 @@
         <v>32</v>
       </c>
       <c r="D726" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E726" s="2" t="s">
         <v>33</v>
@@ -16523,7 +16523,7 @@
         <v>32</v>
       </c>
       <c r="D727" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E727" s="2" t="s">
         <v>33</v>
@@ -16540,7 +16540,7 @@
         <v>32</v>
       </c>
       <c r="D728" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E728" s="2" t="s">
         <v>33</v>
@@ -16557,7 +16557,7 @@
         <v>32</v>
       </c>
       <c r="D729" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E729" s="2" t="s">
         <v>33</v>
@@ -16574,7 +16574,7 @@
         <v>32</v>
       </c>
       <c r="D730" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E730" s="2" t="s">
         <v>33</v>
@@ -16591,7 +16591,7 @@
         <v>32</v>
       </c>
       <c r="D731" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E731" s="2" t="s">
         <v>33</v>
@@ -16625,7 +16625,7 @@
         <v>32</v>
       </c>
       <c r="D733" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E733" s="2" t="s">
         <v>33</v>
@@ -16642,7 +16642,7 @@
         <v>32</v>
       </c>
       <c r="D734" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E734" s="2" t="s">
         <v>33</v>
@@ -16659,7 +16659,7 @@
         <v>32</v>
       </c>
       <c r="D735" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E735" s="2" t="s">
         <v>33</v>
@@ -16676,7 +16676,7 @@
         <v>32</v>
       </c>
       <c r="D736" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E736" s="2" t="s">
         <v>33</v>
@@ -16710,7 +16710,7 @@
         <v>32</v>
       </c>
       <c r="D738" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E738" s="2" t="s">
         <v>33</v>
@@ -16727,7 +16727,7 @@
         <v>32</v>
       </c>
       <c r="D739" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E739" s="2" t="s">
         <v>33</v>
@@ -16744,7 +16744,7 @@
         <v>32</v>
       </c>
       <c r="D740" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E740" s="2" t="s">
         <v>33</v>
@@ -16761,7 +16761,7 @@
         <v>32</v>
       </c>
       <c r="D741" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E741" s="2" t="s">
         <v>33</v>
@@ -16778,7 +16778,7 @@
         <v>32</v>
       </c>
       <c r="D742" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E742" s="2" t="s">
         <v>33</v>
@@ -16795,7 +16795,7 @@
         <v>32</v>
       </c>
       <c r="D743" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E743" s="2" t="s">
         <v>33</v>
@@ -16812,7 +16812,7 @@
         <v>32</v>
       </c>
       <c r="D744" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E744" s="2" t="s">
         <v>33</v>
@@ -16829,7 +16829,7 @@
         <v>32</v>
       </c>
       <c r="D745" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E745" s="2" t="s">
         <v>33</v>
@@ -16846,7 +16846,7 @@
         <v>32</v>
       </c>
       <c r="D746" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E746" s="2" t="s">
         <v>33</v>
@@ -16863,7 +16863,7 @@
         <v>32</v>
       </c>
       <c r="D747" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E747" s="2" t="s">
         <v>33</v>
@@ -16880,7 +16880,7 @@
         <v>32</v>
       </c>
       <c r="D748" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E748" s="2" t="s">
         <v>33</v>
@@ -16897,7 +16897,7 @@
         <v>32</v>
       </c>
       <c r="D749" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E749" s="2" t="s">
         <v>33</v>
@@ -16914,7 +16914,7 @@
         <v>32</v>
       </c>
       <c r="D750" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E750" s="2" t="s">
         <v>33</v>
@@ -16931,7 +16931,7 @@
         <v>32</v>
       </c>
       <c r="D751" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E751" s="2" t="s">
         <v>33</v>
@@ -16948,7 +16948,7 @@
         <v>32</v>
       </c>
       <c r="D752" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E752" s="2" t="s">
         <v>33</v>
@@ -16965,7 +16965,7 @@
         <v>32</v>
       </c>
       <c r="D753" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E753" s="2" t="s">
         <v>33</v>
@@ -16982,7 +16982,7 @@
         <v>32</v>
       </c>
       <c r="D754" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E754" s="2" t="s">
         <v>33</v>
@@ -16999,7 +16999,7 @@
         <v>32</v>
       </c>
       <c r="D755" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E755" s="2" t="s">
         <v>33</v>
@@ -17016,7 +17016,7 @@
         <v>32</v>
       </c>
       <c r="D756" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E756" s="2" t="s">
         <v>33</v>
@@ -17033,7 +17033,7 @@
         <v>32</v>
       </c>
       <c r="D757" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E757" s="2" t="s">
         <v>33</v>
@@ -17050,7 +17050,7 @@
         <v>32</v>
       </c>
       <c r="D758" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E758" s="2" t="s">
         <v>33</v>
@@ -17067,7 +17067,7 @@
         <v>32</v>
       </c>
       <c r="D759" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E759" s="2" t="s">
         <v>33</v>
@@ -17084,7 +17084,7 @@
         <v>32</v>
       </c>
       <c r="D760" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E760" s="2" t="s">
         <v>33</v>
@@ -17101,7 +17101,7 @@
         <v>32</v>
       </c>
       <c r="D761" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E761" s="2" t="s">
         <v>33</v>
@@ -17118,7 +17118,7 @@
         <v>32</v>
       </c>
       <c r="D762" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E762" s="2" t="s">
         <v>33</v>
@@ -17135,7 +17135,7 @@
         <v>32</v>
       </c>
       <c r="D763" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E763" s="2" t="s">
         <v>33</v>
@@ -17152,7 +17152,7 @@
         <v>32</v>
       </c>
       <c r="D764" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E764" s="2" t="s">
         <v>33</v>
@@ -17169,7 +17169,7 @@
         <v>32</v>
       </c>
       <c r="D765" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E765" s="2" t="s">
         <v>33</v>
@@ -17203,7 +17203,7 @@
         <v>32</v>
       </c>
       <c r="D767" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E767" s="2" t="s">
         <v>33</v>
@@ -17220,7 +17220,7 @@
         <v>32</v>
       </c>
       <c r="D768" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E768" s="2" t="s">
         <v>33</v>
@@ -17237,7 +17237,7 @@
         <v>32</v>
       </c>
       <c r="D769" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E769" s="2" t="s">
         <v>33</v>
@@ -17254,7 +17254,7 @@
         <v>32</v>
       </c>
       <c r="D770" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E770" s="2" t="s">
         <v>33</v>
@@ -17271,7 +17271,7 @@
         <v>32</v>
       </c>
       <c r="D771" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E771" s="2" t="s">
         <v>33</v>
@@ -17288,7 +17288,7 @@
         <v>32</v>
       </c>
       <c r="D772" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E772" s="2" t="s">
         <v>33</v>
@@ -17305,7 +17305,7 @@
         <v>32</v>
       </c>
       <c r="D773" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E773" s="2" t="s">
         <v>33</v>
@@ -17322,7 +17322,7 @@
         <v>32</v>
       </c>
       <c r="D774" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E774" s="2" t="s">
         <v>33</v>
@@ -17339,7 +17339,7 @@
         <v>32</v>
       </c>
       <c r="D775" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E775" s="2" t="s">
         <v>33</v>
@@ -17356,7 +17356,7 @@
         <v>32</v>
       </c>
       <c r="D776" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E776" s="2" t="s">
         <v>33</v>
@@ -17373,7 +17373,7 @@
         <v>32</v>
       </c>
       <c r="D777" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E777" s="2" t="s">
         <v>33</v>
@@ -17390,7 +17390,7 @@
         <v>32</v>
       </c>
       <c r="D778" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E778" s="2" t="s">
         <v>33</v>
@@ -17407,7 +17407,7 @@
         <v>32</v>
       </c>
       <c r="D779" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E779" s="2" t="s">
         <v>33</v>
@@ -17424,7 +17424,7 @@
         <v>32</v>
       </c>
       <c r="D780" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E780" s="2" t="s">
         <v>33</v>
@@ -17441,7 +17441,7 @@
         <v>32</v>
       </c>
       <c r="D781" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E781" s="2" t="s">
         <v>33</v>
@@ -17458,7 +17458,7 @@
         <v>32</v>
       </c>
       <c r="D782" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E782" s="2" t="s">
         <v>33</v>
@@ -17475,7 +17475,7 @@
         <v>32</v>
       </c>
       <c r="D783" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E783" s="2" t="s">
         <v>33</v>
@@ -17492,7 +17492,7 @@
         <v>32</v>
       </c>
       <c r="D784" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E784" s="2" t="s">
         <v>33</v>
@@ -17509,7 +17509,7 @@
         <v>32</v>
       </c>
       <c r="D785" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E785" s="2" t="s">
         <v>33</v>
@@ -17526,7 +17526,7 @@
         <v>32</v>
       </c>
       <c r="D786" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E786" s="2" t="s">
         <v>33</v>
@@ -17543,7 +17543,7 @@
         <v>32</v>
       </c>
       <c r="D787" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E787" s="2" t="s">
         <v>33</v>
@@ -17594,7 +17594,7 @@
         <v>32</v>
       </c>
       <c r="D790" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E790" s="2" t="s">
         <v>33</v>
@@ -17611,7 +17611,7 @@
         <v>32</v>
       </c>
       <c r="D791" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E791" s="2" t="s">
         <v>33</v>
@@ -17628,7 +17628,7 @@
         <v>32</v>
       </c>
       <c r="D792" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E792" s="2" t="s">
         <v>33</v>
@@ -17645,7 +17645,7 @@
         <v>32</v>
       </c>
       <c r="D793" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E793" s="2" t="s">
         <v>33</v>
@@ -17662,7 +17662,7 @@
         <v>32</v>
       </c>
       <c r="D794" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E794" s="2" t="s">
         <v>33</v>
@@ -17679,7 +17679,7 @@
         <v>32</v>
       </c>
       <c r="D795" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E795" s="2" t="s">
         <v>33</v>
@@ -17713,7 +17713,7 @@
         <v>32</v>
       </c>
       <c r="D797" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E797" s="2" t="s">
         <v>33</v>
@@ -17730,7 +17730,7 @@
         <v>32</v>
       </c>
       <c r="D798" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E798" s="2" t="s">
         <v>33</v>
@@ -17747,7 +17747,7 @@
         <v>32</v>
       </c>
       <c r="D799" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E799" s="2" t="s">
         <v>33</v>
@@ -17764,7 +17764,7 @@
         <v>32</v>
       </c>
       <c r="D800" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E800" s="2" t="s">
         <v>33</v>
@@ -17781,7 +17781,7 @@
         <v>32</v>
       </c>
       <c r="D801" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E801" s="2" t="s">
         <v>33</v>
@@ -17798,7 +17798,7 @@
         <v>32</v>
       </c>
       <c r="D802" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E802" s="2" t="s">
         <v>33</v>
@@ -17815,7 +17815,7 @@
         <v>32</v>
       </c>
       <c r="D803" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E803" s="2" t="s">
         <v>33</v>
@@ -17849,7 +17849,7 @@
         <v>32</v>
       </c>
       <c r="D805" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E805" s="2" t="s">
         <v>33</v>
@@ -17866,7 +17866,7 @@
         <v>32</v>
       </c>
       <c r="D806" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E806" s="2" t="s">
         <v>33</v>
@@ -17900,7 +17900,7 @@
         <v>32</v>
       </c>
       <c r="D808" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E808" s="2" t="s">
         <v>33</v>
@@ -17917,7 +17917,7 @@
         <v>32</v>
       </c>
       <c r="D809" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E809" s="2" t="s">
         <v>33</v>
@@ -17934,7 +17934,7 @@
         <v>32</v>
       </c>
       <c r="D810" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E810" s="2" t="s">
         <v>33</v>
@@ -17951,7 +17951,7 @@
         <v>32</v>
       </c>
       <c r="D811" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E811" s="2" t="s">
         <v>33</v>
@@ -17968,7 +17968,7 @@
         <v>32</v>
       </c>
       <c r="D812" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E812" s="2" t="s">
         <v>33</v>
@@ -18002,7 +18002,7 @@
         <v>32</v>
       </c>
       <c r="D814" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E814" s="2" t="s">
         <v>33</v>
@@ -18036,7 +18036,7 @@
         <v>32</v>
       </c>
       <c r="D816" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E816" s="2" t="s">
         <v>33</v>
@@ -18053,7 +18053,7 @@
         <v>32</v>
       </c>
       <c r="D817" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E817" s="2" t="s">
         <v>33</v>
@@ -18070,7 +18070,7 @@
         <v>32</v>
       </c>
       <c r="D818" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E818" s="2" t="s">
         <v>33</v>
@@ -18087,7 +18087,7 @@
         <v>32</v>
       </c>
       <c r="D819" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E819" s="2" t="s">
         <v>33</v>
@@ -18104,7 +18104,7 @@
         <v>32</v>
       </c>
       <c r="D820" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E820" s="2" t="s">
         <v>33</v>
@@ -18121,7 +18121,7 @@
         <v>32</v>
       </c>
       <c r="D821" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E821" s="2" t="s">
         <v>33</v>
@@ -18138,7 +18138,7 @@
         <v>32</v>
       </c>
       <c r="D822" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E822" s="2" t="s">
         <v>33</v>
@@ -18155,7 +18155,7 @@
         <v>32</v>
       </c>
       <c r="D823" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E823" s="2" t="s">
         <v>33</v>
@@ -18172,7 +18172,7 @@
         <v>32</v>
       </c>
       <c r="D824" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E824" s="2" t="s">
         <v>33</v>
@@ -18189,7 +18189,7 @@
         <v>32</v>
       </c>
       <c r="D825" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E825" s="2" t="s">
         <v>33</v>
@@ -18206,7 +18206,7 @@
         <v>32</v>
       </c>
       <c r="D826" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E826" s="2" t="s">
         <v>33</v>
@@ -18223,7 +18223,7 @@
         <v>32</v>
       </c>
       <c r="D827" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E827" s="2" t="s">
         <v>33</v>
@@ -18240,7 +18240,7 @@
         <v>32</v>
       </c>
       <c r="D828" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E828" s="2" t="s">
         <v>33</v>
@@ -18257,7 +18257,7 @@
         <v>32</v>
       </c>
       <c r="D829" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E829" s="2" t="s">
         <v>33</v>
@@ -18274,7 +18274,7 @@
         <v>32</v>
       </c>
       <c r="D830" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E830" s="2" t="s">
         <v>33</v>
@@ -18291,7 +18291,7 @@
         <v>32</v>
       </c>
       <c r="D831" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E831" s="2" t="s">
         <v>33</v>
@@ -18308,7 +18308,7 @@
         <v>32</v>
       </c>
       <c r="D832" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E832" s="2" t="s">
         <v>33</v>
@@ -18325,7 +18325,7 @@
         <v>32</v>
       </c>
       <c r="D833" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E833" s="2" t="s">
         <v>33</v>
@@ -18342,7 +18342,7 @@
         <v>32</v>
       </c>
       <c r="D834" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E834" s="2" t="s">
         <v>33</v>
@@ -18359,7 +18359,7 @@
         <v>32</v>
       </c>
       <c r="D835" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E835" s="2" t="s">
         <v>33</v>
@@ -18376,7 +18376,7 @@
         <v>32</v>
       </c>
       <c r="D836" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E836" s="2" t="s">
         <v>33</v>
@@ -18393,7 +18393,7 @@
         <v>32</v>
       </c>
       <c r="D837" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E837" s="2" t="s">
         <v>33</v>
@@ -18410,7 +18410,7 @@
         <v>32</v>
       </c>
       <c r="D838" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E838" s="2" t="s">
         <v>33</v>
@@ -18427,7 +18427,7 @@
         <v>32</v>
       </c>
       <c r="D839" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E839" s="2" t="s">
         <v>33</v>
@@ -18444,7 +18444,7 @@
         <v>32</v>
       </c>
       <c r="D840" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E840" s="2" t="s">
         <v>33</v>
@@ -18461,7 +18461,7 @@
         <v>32</v>
       </c>
       <c r="D841" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E841" s="2" t="s">
         <v>33</v>
@@ -18478,7 +18478,7 @@
         <v>32</v>
       </c>
       <c r="D842" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E842" s="2" t="s">
         <v>33</v>
@@ -18495,7 +18495,7 @@
         <v>32</v>
       </c>
       <c r="D843" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E843" s="2" t="s">
         <v>33</v>
@@ -18512,7 +18512,7 @@
         <v>32</v>
       </c>
       <c r="D844" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E844" s="2" t="s">
         <v>33</v>
@@ -18529,7 +18529,7 @@
         <v>32</v>
       </c>
       <c r="D845" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E845" s="2" t="s">
         <v>33</v>
@@ -18546,7 +18546,7 @@
         <v>32</v>
       </c>
       <c r="D846" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E846" s="2" t="s">
         <v>33</v>
@@ -18563,7 +18563,7 @@
         <v>32</v>
       </c>
       <c r="D847" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E847" s="2" t="s">
         <v>33</v>
@@ -18580,7 +18580,7 @@
         <v>32</v>
       </c>
       <c r="D848" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E848" s="2" t="s">
         <v>33</v>
@@ -18597,7 +18597,7 @@
         <v>32</v>
       </c>
       <c r="D849" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E849" s="2" t="s">
         <v>33</v>
@@ -18614,7 +18614,7 @@
         <v>32</v>
       </c>
       <c r="D850" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E850" s="2" t="s">
         <v>33</v>
@@ -18631,7 +18631,7 @@
         <v>32</v>
       </c>
       <c r="D851" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E851" s="2" t="s">
         <v>33</v>
@@ -18648,7 +18648,7 @@
         <v>32</v>
       </c>
       <c r="D852" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E852" s="2" t="s">
         <v>33</v>
@@ -18665,7 +18665,7 @@
         <v>32</v>
       </c>
       <c r="D853" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E853" s="2" t="s">
         <v>33</v>
@@ -18682,7 +18682,7 @@
         <v>32</v>
       </c>
       <c r="D854" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E854" s="2" t="s">
         <v>33</v>
@@ -18699,7 +18699,7 @@
         <v>32</v>
       </c>
       <c r="D855" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E855" s="2" t="s">
         <v>33</v>
@@ -18716,7 +18716,7 @@
         <v>32</v>
       </c>
       <c r="D856" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E856" s="2" t="s">
         <v>33</v>
@@ -18733,7 +18733,7 @@
         <v>32</v>
       </c>
       <c r="D857" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E857" s="2" t="s">
         <v>33</v>
@@ -18750,7 +18750,7 @@
         <v>32</v>
       </c>
       <c r="D858" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E858" s="2" t="s">
         <v>33</v>
@@ -18767,7 +18767,7 @@
         <v>32</v>
       </c>
       <c r="D859" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E859" s="2" t="s">
         <v>33</v>
@@ -18784,7 +18784,7 @@
         <v>32</v>
       </c>
       <c r="D860" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E860" s="2" t="s">
         <v>33</v>
@@ -18801,7 +18801,7 @@
         <v>32</v>
       </c>
       <c r="D861" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E861" s="2" t="s">
         <v>33</v>
@@ -18818,7 +18818,7 @@
         <v>32</v>
       </c>
       <c r="D862" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E862" s="2" t="s">
         <v>33</v>
@@ -18835,7 +18835,7 @@
         <v>32</v>
       </c>
       <c r="D863" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E863" s="2" t="s">
         <v>33</v>
@@ -18852,7 +18852,7 @@
         <v>32</v>
       </c>
       <c r="D864" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E864" s="2" t="s">
         <v>33</v>
@@ -18869,7 +18869,7 @@
         <v>32</v>
       </c>
       <c r="D865" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E865" s="2" t="s">
         <v>33</v>
@@ -18886,7 +18886,7 @@
         <v>32</v>
       </c>
       <c r="D866" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E866" s="2" t="s">
         <v>33</v>
@@ -18903,7 +18903,7 @@
         <v>32</v>
       </c>
       <c r="D867" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E867" s="2" t="s">
         <v>33</v>
@@ -18920,7 +18920,7 @@
         <v>32</v>
       </c>
       <c r="D868" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E868" s="2" t="s">
         <v>33</v>
@@ -18937,7 +18937,7 @@
         <v>32</v>
       </c>
       <c r="D869" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E869" s="2" t="s">
         <v>33</v>
@@ -18971,7 +18971,7 @@
         <v>32</v>
       </c>
       <c r="D871" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E871" s="2" t="s">
         <v>33</v>
@@ -18988,7 +18988,7 @@
         <v>32</v>
       </c>
       <c r="D872" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E872" s="2" t="s">
         <v>33</v>
@@ -19005,7 +19005,7 @@
         <v>32</v>
       </c>
       <c r="D873" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E873" s="2" t="s">
         <v>33</v>
@@ -19022,7 +19022,7 @@
         <v>32</v>
       </c>
       <c r="D874" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E874" s="2" t="s">
         <v>33</v>
@@ -19039,7 +19039,7 @@
         <v>32</v>
       </c>
       <c r="D875" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E875" s="2" t="s">
         <v>33</v>
@@ -19056,7 +19056,7 @@
         <v>32</v>
       </c>
       <c r="D876" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E876" s="2" t="s">
         <v>33</v>
@@ -19073,7 +19073,7 @@
         <v>32</v>
       </c>
       <c r="D877" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E877" s="2" t="s">
         <v>33</v>
@@ -19090,7 +19090,7 @@
         <v>32</v>
       </c>
       <c r="D878" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E878" s="2" t="s">
         <v>33</v>
@@ -19124,7 +19124,7 @@
         <v>32</v>
       </c>
       <c r="D880" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E880" s="2" t="s">
         <v>33</v>
@@ -19141,7 +19141,7 @@
         <v>32</v>
       </c>
       <c r="D881" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E881" s="2" t="s">
         <v>33</v>
@@ -19158,7 +19158,7 @@
         <v>32</v>
       </c>
       <c r="D882" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E882" s="2" t="s">
         <v>33</v>
@@ -19175,7 +19175,7 @@
         <v>32</v>
       </c>
       <c r="D883" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E883" s="2" t="s">
         <v>33</v>
@@ -19192,7 +19192,7 @@
         <v>32</v>
       </c>
       <c r="D884" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E884" s="2" t="s">
         <v>33</v>
@@ -19209,7 +19209,7 @@
         <v>32</v>
       </c>
       <c r="D885" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E885" s="2" t="s">
         <v>33</v>
@@ -19226,7 +19226,7 @@
         <v>32</v>
       </c>
       <c r="D886" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E886" s="2" t="s">
         <v>33</v>
@@ -19243,7 +19243,7 @@
         <v>32</v>
       </c>
       <c r="D887" s="2">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E887" s="2" t="s">
         <v>33</v>
@@ -19260,7 +19260,7 @@
         <v>32</v>
       </c>
       <c r="D888" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E888" s="2" t="s">
         <v>33</v>
@@ -19277,7 +19277,7 @@
         <v>32</v>
       </c>
       <c r="D889" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E889" s="2" t="s">
         <v>33</v>
@@ -19294,7 +19294,7 @@
         <v>32</v>
       </c>
       <c r="D890" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E890" s="2" t="s">
         <v>33</v>
@@ -19311,7 +19311,7 @@
         <v>32</v>
       </c>
       <c r="D891" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E891" s="2" t="s">
         <v>33</v>
@@ -19328,7 +19328,7 @@
         <v>32</v>
       </c>
       <c r="D892" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E892" s="2" t="s">
         <v>33</v>
@@ -19345,7 +19345,7 @@
         <v>32</v>
       </c>
       <c r="D893" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E893" s="2" t="s">
         <v>33</v>
@@ -19362,7 +19362,7 @@
         <v>32</v>
       </c>
       <c r="D894" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E894" s="2" t="s">
         <v>33</v>
@@ -19379,7 +19379,7 @@
         <v>32</v>
       </c>
       <c r="D895" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E895" s="2" t="s">
         <v>33</v>
@@ -19396,7 +19396,7 @@
         <v>32</v>
       </c>
       <c r="D896" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E896" s="2" t="s">
         <v>33</v>
@@ -19413,7 +19413,7 @@
         <v>32</v>
       </c>
       <c r="D897" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E897" s="2" t="s">
         <v>33</v>
@@ -19430,7 +19430,7 @@
         <v>32</v>
       </c>
       <c r="D898" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E898" s="2" t="s">
         <v>33</v>
@@ -19447,7 +19447,7 @@
         <v>32</v>
       </c>
       <c r="D899" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E899" s="2" t="s">
         <v>33</v>
@@ -19464,7 +19464,7 @@
         <v>32</v>
       </c>
       <c r="D900" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E900" s="2" t="s">
         <v>33</v>
@@ -19481,7 +19481,7 @@
         <v>32</v>
       </c>
       <c r="D901" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E901" s="2" t="s">
         <v>33</v>
@@ -19498,7 +19498,7 @@
         <v>32</v>
       </c>
       <c r="D902" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E902" s="2" t="s">
         <v>33</v>
@@ -19515,7 +19515,7 @@
         <v>32</v>
       </c>
       <c r="D903" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E903" s="2" t="s">
         <v>33</v>
@@ -19532,7 +19532,7 @@
         <v>32</v>
       </c>
       <c r="D904" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E904" s="2" t="s">
         <v>33</v>
@@ -19549,7 +19549,7 @@
         <v>32</v>
       </c>
       <c r="D905" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E905" s="2" t="s">
         <v>33</v>
@@ -19566,7 +19566,7 @@
         <v>32</v>
       </c>
       <c r="D906" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E906" s="2" t="s">
         <v>33</v>
@@ -19583,7 +19583,7 @@
         <v>32</v>
       </c>
       <c r="D907" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E907" s="2" t="s">
         <v>33</v>
@@ -19600,7 +19600,7 @@
         <v>32</v>
       </c>
       <c r="D908" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E908" s="2" t="s">
         <v>33</v>
@@ -19617,7 +19617,7 @@
         <v>32</v>
       </c>
       <c r="D909" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E909" s="2" t="s">
         <v>33</v>
@@ -19634,7 +19634,7 @@
         <v>32</v>
       </c>
       <c r="D910" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E910" s="2" t="s">
         <v>33</v>
@@ -19651,7 +19651,7 @@
         <v>32</v>
       </c>
       <c r="D911" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E911" s="2" t="s">
         <v>33</v>
@@ -19668,7 +19668,7 @@
         <v>32</v>
       </c>
       <c r="D912" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E912" s="2" t="s">
         <v>33</v>
@@ -19685,7 +19685,7 @@
         <v>32</v>
       </c>
       <c r="D913" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E913" s="2" t="s">
         <v>33</v>
@@ -19702,7 +19702,7 @@
         <v>32</v>
       </c>
       <c r="D914" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E914" s="2" t="s">
         <v>33</v>
@@ -19719,7 +19719,7 @@
         <v>32</v>
       </c>
       <c r="D915" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E915" s="2" t="s">
         <v>33</v>
@@ -19736,7 +19736,7 @@
         <v>32</v>
       </c>
       <c r="D916" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E916" s="2" t="s">
         <v>33</v>
@@ -19753,7 +19753,7 @@
         <v>32</v>
       </c>
       <c r="D917" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E917" s="2" t="s">
         <v>33</v>
@@ -19770,7 +19770,7 @@
         <v>32</v>
       </c>
       <c r="D918" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E918" s="2" t="s">
         <v>33</v>
@@ -19787,7 +19787,7 @@
         <v>32</v>
       </c>
       <c r="D919" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E919" s="2" t="s">
         <v>33</v>
@@ -19804,7 +19804,7 @@
         <v>32</v>
       </c>
       <c r="D920" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E920" s="2" t="s">
         <v>33</v>
@@ -19821,7 +19821,7 @@
         <v>32</v>
       </c>
       <c r="D921" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E921" s="2" t="s">
         <v>33</v>
@@ -19838,7 +19838,7 @@
         <v>32</v>
       </c>
       <c r="D922" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E922" s="2" t="s">
         <v>33</v>
@@ -19855,7 +19855,7 @@
         <v>32</v>
       </c>
       <c r="D923" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E923" s="2" t="s">
         <v>33</v>
@@ -19872,7 +19872,7 @@
         <v>32</v>
       </c>
       <c r="D924" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E924" s="2" t="s">
         <v>33</v>
@@ -19889,7 +19889,7 @@
         <v>32</v>
       </c>
       <c r="D925" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E925" s="2" t="s">
         <v>33</v>
@@ -19906,7 +19906,7 @@
         <v>32</v>
       </c>
       <c r="D926" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E926" s="2" t="s">
         <v>33</v>
@@ -19923,7 +19923,7 @@
         <v>32</v>
       </c>
       <c r="D927" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E927" s="2" t="s">
         <v>33</v>
@@ -19940,7 +19940,7 @@
         <v>32</v>
       </c>
       <c r="D928" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E928" s="2" t="s">
         <v>33</v>
@@ -19957,7 +19957,7 @@
         <v>32</v>
       </c>
       <c r="D929" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E929" s="2" t="s">
         <v>33</v>
@@ -19991,7 +19991,7 @@
         <v>32</v>
       </c>
       <c r="D931" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E931" s="2" t="s">
         <v>33</v>
@@ -20008,7 +20008,7 @@
         <v>32</v>
       </c>
       <c r="D932" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E932" s="2" t="s">
         <v>33</v>
@@ -20025,7 +20025,7 @@
         <v>32</v>
       </c>
       <c r="D933" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E933" s="2" t="s">
         <v>33</v>
@@ -20042,7 +20042,7 @@
         <v>32</v>
       </c>
       <c r="D934" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E934" s="2" t="s">
         <v>33</v>
@@ -20059,7 +20059,7 @@
         <v>32</v>
       </c>
       <c r="D935" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E935" s="2" t="s">
         <v>33</v>
@@ -20076,7 +20076,7 @@
         <v>32</v>
       </c>
       <c r="D936" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E936" s="2" t="s">
         <v>33</v>
@@ -20093,7 +20093,7 @@
         <v>32</v>
       </c>
       <c r="D937" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E937" s="2" t="s">
         <v>33</v>
@@ -20110,7 +20110,7 @@
         <v>32</v>
       </c>
       <c r="D938" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E938" s="2" t="s">
         <v>33</v>
@@ -20127,7 +20127,7 @@
         <v>32</v>
       </c>
       <c r="D939" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E939" s="2" t="s">
         <v>33</v>
@@ -20144,7 +20144,7 @@
         <v>32</v>
       </c>
       <c r="D940" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E940" s="2" t="s">
         <v>33</v>
@@ -20178,7 +20178,7 @@
         <v>32</v>
       </c>
       <c r="D942" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E942" s="2" t="s">
         <v>33</v>
@@ -20195,7 +20195,7 @@
         <v>32</v>
       </c>
       <c r="D943" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E943" s="2" t="s">
         <v>33</v>
@@ -20212,7 +20212,7 @@
         <v>32</v>
       </c>
       <c r="D944" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E944" s="2" t="s">
         <v>33</v>
@@ -20229,7 +20229,7 @@
         <v>32</v>
       </c>
       <c r="D945" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E945" s="2" t="s">
         <v>33</v>
@@ -20246,7 +20246,7 @@
         <v>32</v>
       </c>
       <c r="D946" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E946" s="2" t="s">
         <v>33</v>
@@ -20263,7 +20263,7 @@
         <v>32</v>
       </c>
       <c r="D947" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E947" s="2" t="s">
         <v>33</v>
@@ -20280,7 +20280,7 @@
         <v>32</v>
       </c>
       <c r="D948" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E948" s="2" t="s">
         <v>33</v>
@@ -20297,7 +20297,7 @@
         <v>32</v>
       </c>
       <c r="D949" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E949" s="2" t="s">
         <v>33</v>
@@ -20314,7 +20314,7 @@
         <v>32</v>
       </c>
       <c r="D950" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E950" s="2" t="s">
         <v>33</v>
@@ -20331,7 +20331,7 @@
         <v>32</v>
       </c>
       <c r="D951" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E951" s="2" t="s">
         <v>33</v>
@@ -20348,7 +20348,7 @@
         <v>32</v>
       </c>
       <c r="D952" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E952" s="2" t="s">
         <v>33</v>
@@ -20365,7 +20365,7 @@
         <v>32</v>
       </c>
       <c r="D953" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E953" s="2" t="s">
         <v>33</v>
@@ -20382,7 +20382,7 @@
         <v>32</v>
       </c>
       <c r="D954" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E954" s="2" t="s">
         <v>33</v>
@@ -20399,7 +20399,7 @@
         <v>32</v>
       </c>
       <c r="D955" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E955" s="2" t="s">
         <v>33</v>
@@ -20433,7 +20433,7 @@
         <v>32</v>
       </c>
       <c r="D957" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E957" s="2" t="s">
         <v>33</v>
@@ -20450,7 +20450,7 @@
         <v>32</v>
       </c>
       <c r="D958" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E958" s="2" t="s">
         <v>33</v>
@@ -20484,7 +20484,7 @@
         <v>32</v>
       </c>
       <c r="D960" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E960" s="2" t="s">
         <v>33</v>
@@ -20501,7 +20501,7 @@
         <v>32</v>
       </c>
       <c r="D961" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E961" s="2" t="s">
         <v>33</v>
@@ -20518,7 +20518,7 @@
         <v>32</v>
       </c>
       <c r="D962" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E962" s="2" t="s">
         <v>33</v>
@@ -20535,7 +20535,7 @@
         <v>32</v>
       </c>
       <c r="D963" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E963" s="2" t="s">
         <v>33</v>
@@ -20552,7 +20552,7 @@
         <v>32</v>
       </c>
       <c r="D964" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E964" s="2" t="s">
         <v>33</v>
@@ -20569,7 +20569,7 @@
         <v>32</v>
       </c>
       <c r="D965" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E965" s="2" t="s">
         <v>33</v>
@@ -20586,7 +20586,7 @@
         <v>32</v>
       </c>
       <c r="D966" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E966" s="2" t="s">
         <v>33</v>
@@ -20603,7 +20603,7 @@
         <v>32</v>
       </c>
       <c r="D967" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E967" s="2" t="s">
         <v>33</v>
@@ -20620,7 +20620,7 @@
         <v>32</v>
       </c>
       <c r="D968" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E968" s="2" t="s">
         <v>33</v>
@@ -20637,7 +20637,7 @@
         <v>32</v>
       </c>
       <c r="D969" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E969" s="2" t="s">
         <v>33</v>
@@ -20654,7 +20654,7 @@
         <v>32</v>
       </c>
       <c r="D970" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E970" s="2" t="s">
         <v>33</v>
@@ -20671,7 +20671,7 @@
         <v>32</v>
       </c>
       <c r="D971" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E971" s="2" t="s">
         <v>33</v>
@@ -20688,7 +20688,7 @@
         <v>32</v>
       </c>
       <c r="D972" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E972" s="2" t="s">
         <v>33</v>
@@ -20705,7 +20705,7 @@
         <v>32</v>
       </c>
       <c r="D973" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E973" s="2" t="s">
         <v>33</v>
@@ -20722,7 +20722,7 @@
         <v>32</v>
       </c>
       <c r="D974" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E974" s="2" t="s">
         <v>33</v>
@@ -20756,7 +20756,7 @@
         <v>32</v>
       </c>
       <c r="D976" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E976" s="2" t="s">
         <v>33</v>
@@ -20773,7 +20773,7 @@
         <v>32</v>
       </c>
       <c r="D977" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E977" s="2" t="s">
         <v>33</v>
@@ -20790,7 +20790,7 @@
         <v>32</v>
       </c>
       <c r="D978" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E978" s="2" t="s">
         <v>33</v>
@@ -20807,7 +20807,7 @@
         <v>32</v>
       </c>
       <c r="D979" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E979" s="2" t="s">
         <v>33</v>
@@ -20824,7 +20824,7 @@
         <v>32</v>
       </c>
       <c r="D980" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E980" s="2" t="s">
         <v>33</v>
@@ -20841,7 +20841,7 @@
         <v>32</v>
       </c>
       <c r="D981" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E981" s="2" t="s">
         <v>33</v>
@@ -20858,7 +20858,7 @@
         <v>32</v>
       </c>
       <c r="D982" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E982" s="2" t="s">
         <v>33</v>
@@ -20875,7 +20875,7 @@
         <v>32</v>
       </c>
       <c r="D983" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E983" s="2" t="s">
         <v>33</v>
@@ -20892,7 +20892,7 @@
         <v>32</v>
       </c>
       <c r="D984" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E984" s="2" t="s">
         <v>33</v>
@@ -20909,7 +20909,7 @@
         <v>32</v>
       </c>
       <c r="D985" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E985" s="2" t="s">
         <v>33</v>
@@ -20926,7 +20926,7 @@
         <v>32</v>
       </c>
       <c r="D986" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E986" s="2" t="s">
         <v>33</v>
@@ -20943,7 +20943,7 @@
         <v>32</v>
       </c>
       <c r="D987" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E987" s="2" t="s">
         <v>33</v>
@@ -20960,7 +20960,7 @@
         <v>32</v>
       </c>
       <c r="D988" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E988" s="2" t="s">
         <v>33</v>
@@ -20977,7 +20977,7 @@
         <v>32</v>
       </c>
       <c r="D989" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E989" s="2" t="s">
         <v>33</v>
@@ -20994,7 +20994,7 @@
         <v>32</v>
       </c>
       <c r="D990" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E990" s="2" t="s">
         <v>33</v>
@@ -21011,7 +21011,7 @@
         <v>32</v>
       </c>
       <c r="D991" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E991" s="2" t="s">
         <v>33</v>
@@ -21028,7 +21028,7 @@
         <v>32</v>
       </c>
       <c r="D992" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E992" s="2" t="s">
         <v>33</v>
@@ -21045,7 +21045,7 @@
         <v>32</v>
       </c>
       <c r="D993" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E993" s="2" t="s">
         <v>33</v>
@@ -21062,7 +21062,7 @@
         <v>32</v>
       </c>
       <c r="D994" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E994" s="2" t="s">
         <v>33</v>
@@ -21079,7 +21079,7 @@
         <v>32</v>
       </c>
       <c r="D995" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E995" s="2" t="s">
         <v>33</v>
@@ -21096,7 +21096,7 @@
         <v>32</v>
       </c>
       <c r="D996" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E996" s="2" t="s">
         <v>33</v>
@@ -21113,7 +21113,7 @@
         <v>32</v>
       </c>
       <c r="D997" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E997" s="2" t="s">
         <v>33</v>
@@ -21130,7 +21130,7 @@
         <v>32</v>
       </c>
       <c r="D998" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E998" s="2" t="s">
         <v>33</v>
@@ -21147,7 +21147,7 @@
         <v>32</v>
       </c>
       <c r="D999" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E999" s="2" t="s">
         <v>33</v>
@@ -21164,7 +21164,7 @@
         <v>32</v>
       </c>
       <c r="D1000" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E1000" s="2" t="s">
         <v>33</v>
@@ -21181,7 +21181,7 @@
         <v>32</v>
       </c>
       <c r="D1001" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1001" s="2" t="s">
         <v>33</v>
@@ -21198,7 +21198,7 @@
         <v>32</v>
       </c>
       <c r="D1002" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E1002" s="2" t="s">
         <v>33</v>
@@ -21215,7 +21215,7 @@
         <v>32</v>
       </c>
       <c r="D1003" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E1003" s="2" t="s">
         <v>33</v>
@@ -21249,7 +21249,7 @@
         <v>32</v>
       </c>
       <c r="D1005" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1005" s="2" t="s">
         <v>33</v>
@@ -21266,7 +21266,7 @@
         <v>32</v>
       </c>
       <c r="D1006" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1006" s="2" t="s">
         <v>33</v>
@@ -21283,7 +21283,7 @@
         <v>32</v>
       </c>
       <c r="D1007" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1007" s="2" t="s">
         <v>33</v>
@@ -21300,7 +21300,7 @@
         <v>32</v>
       </c>
       <c r="D1008" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1008" s="2" t="s">
         <v>33</v>
@@ -21317,7 +21317,7 @@
         <v>32</v>
       </c>
       <c r="D1009" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E1009" s="2" t="s">
         <v>33</v>
@@ -21334,7 +21334,7 @@
         <v>32</v>
       </c>
       <c r="D1010" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E1010" s="2" t="s">
         <v>33</v>
@@ -21351,7 +21351,7 @@
         <v>32</v>
       </c>
       <c r="D1011" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1011" s="2" t="s">
         <v>33</v>
@@ -21368,7 +21368,7 @@
         <v>32</v>
       </c>
       <c r="D1012" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1012" s="2" t="s">
         <v>33</v>
@@ -21385,7 +21385,7 @@
         <v>32</v>
       </c>
       <c r="D1013" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E1013" s="2" t="s">
         <v>33</v>
@@ -21402,7 +21402,7 @@
         <v>32</v>
       </c>
       <c r="D1014" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E1014" s="2" t="s">
         <v>33</v>
@@ -21419,7 +21419,7 @@
         <v>32</v>
       </c>
       <c r="D1015" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E1015" s="2" t="s">
         <v>33</v>
@@ -21436,7 +21436,7 @@
         <v>32</v>
       </c>
       <c r="D1016" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E1016" s="2" t="s">
         <v>33</v>
@@ -21453,7 +21453,7 @@
         <v>32</v>
       </c>
       <c r="D1017" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E1017" s="2" t="s">
         <v>33</v>
@@ -21470,7 +21470,7 @@
         <v>32</v>
       </c>
       <c r="D1018" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E1018" s="2" t="s">
         <v>33</v>
@@ -21487,7 +21487,7 @@
         <v>32</v>
       </c>
       <c r="D1019" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E1019" s="2" t="s">
         <v>33</v>
@@ -21504,7 +21504,7 @@
         <v>32</v>
       </c>
       <c r="D1020" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E1020" s="2" t="s">
         <v>33</v>
@@ -21521,7 +21521,7 @@
         <v>32</v>
       </c>
       <c r="D1021" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1021" s="2" t="s">
         <v>33</v>
@@ -21538,7 +21538,7 @@
         <v>32</v>
       </c>
       <c r="D1022" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1022" s="2" t="s">
         <v>33</v>
@@ -21555,7 +21555,7 @@
         <v>32</v>
       </c>
       <c r="D1023" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1023" s="2" t="s">
         <v>33</v>
@@ -21572,7 +21572,7 @@
         <v>32</v>
       </c>
       <c r="D1024" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E1024" s="2" t="s">
         <v>33</v>
@@ -21589,7 +21589,7 @@
         <v>32</v>
       </c>
       <c r="D1025" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E1025" s="2" t="s">
         <v>33</v>
@@ -21606,7 +21606,7 @@
         <v>32</v>
       </c>
       <c r="D1026" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1026" s="2" t="s">
         <v>33</v>
@@ -21623,7 +21623,7 @@
         <v>32</v>
       </c>
       <c r="D1027" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E1027" s="2" t="s">
         <v>33</v>
@@ -21640,7 +21640,7 @@
         <v>32</v>
       </c>
       <c r="D1028" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1028" s="2" t="s">
         <v>33</v>
@@ -21657,7 +21657,7 @@
         <v>32</v>
       </c>
       <c r="D1029" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E1029" s="2" t="s">
         <v>33</v>
@@ -21674,7 +21674,7 @@
         <v>32</v>
       </c>
       <c r="D1030" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1030" s="2" t="s">
         <v>33</v>
@@ -21691,7 +21691,7 @@
         <v>32</v>
       </c>
       <c r="D1031" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E1031" s="2" t="s">
         <v>33</v>
@@ -21708,7 +21708,7 @@
         <v>32</v>
       </c>
       <c r="D1032" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1032" s="2" t="s">
         <v>33</v>
@@ -21725,7 +21725,7 @@
         <v>32</v>
       </c>
       <c r="D1033" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E1033" s="2" t="s">
         <v>33</v>
@@ -21742,7 +21742,7 @@
         <v>32</v>
       </c>
       <c r="D1034" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E1034" s="2" t="s">
         <v>33</v>
@@ -21759,7 +21759,7 @@
         <v>32</v>
       </c>
       <c r="D1035" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E1035" s="2" t="s">
         <v>33</v>
@@ -21793,7 +21793,7 @@
         <v>32</v>
       </c>
       <c r="D1037" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E1037" s="2" t="s">
         <v>33</v>
@@ -21810,7 +21810,7 @@
         <v>32</v>
       </c>
       <c r="D1038" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E1038" s="2" t="s">
         <v>33</v>
@@ -21827,7 +21827,7 @@
         <v>32</v>
       </c>
       <c r="D1039" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E1039" s="2" t="s">
         <v>33</v>
@@ -21844,7 +21844,7 @@
         <v>32</v>
       </c>
       <c r="D1040" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1040" s="2" t="s">
         <v>33</v>
@@ -21861,7 +21861,7 @@
         <v>32</v>
       </c>
       <c r="D1041" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1041" s="2" t="s">
         <v>33</v>
@@ -21878,7 +21878,7 @@
         <v>32</v>
       </c>
       <c r="D1042" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E1042" s="2" t="s">
         <v>33</v>
@@ -21895,7 +21895,7 @@
         <v>32</v>
       </c>
       <c r="D1043" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E1043" s="2" t="s">
         <v>33</v>
@@ -21912,7 +21912,7 @@
         <v>32</v>
       </c>
       <c r="D1044" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E1044" s="2" t="s">
         <v>33</v>
@@ -21929,7 +21929,7 @@
         <v>32</v>
       </c>
       <c r="D1045" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E1045" s="2" t="s">
         <v>33</v>
@@ -21963,7 +21963,7 @@
         <v>32</v>
       </c>
       <c r="D1047" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E1047" s="2" t="s">
         <v>33</v>
@@ -21980,7 +21980,7 @@
         <v>32</v>
       </c>
       <c r="D1048" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1048" s="2" t="s">
         <v>33</v>
@@ -21997,7 +21997,7 @@
         <v>32</v>
       </c>
       <c r="D1049" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E1049" s="2" t="s">
         <v>33</v>
@@ -22014,7 +22014,7 @@
         <v>32</v>
       </c>
       <c r="D1050" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1050" s="2" t="s">
         <v>33</v>
@@ -22031,7 +22031,7 @@
         <v>32</v>
       </c>
       <c r="D1051" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E1051" s="2" t="s">
         <v>33</v>
@@ -22048,7 +22048,7 @@
         <v>32</v>
       </c>
       <c r="D1052" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1052" s="2" t="s">
         <v>33</v>
@@ -22065,7 +22065,7 @@
         <v>32</v>
       </c>
       <c r="D1053" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1053" s="2" t="s">
         <v>33</v>
@@ -22082,7 +22082,7 @@
         <v>32</v>
       </c>
       <c r="D1054" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E1054" s="2" t="s">
         <v>33</v>
@@ -22099,7 +22099,7 @@
         <v>32</v>
       </c>
       <c r="D1055" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E1055" s="2" t="s">
         <v>33</v>
@@ -22116,7 +22116,7 @@
         <v>32</v>
       </c>
       <c r="D1056" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E1056" s="2" t="s">
         <v>33</v>
@@ -22133,7 +22133,7 @@
         <v>32</v>
       </c>
       <c r="D1057" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E1057" s="2" t="s">
         <v>33</v>
@@ -22150,7 +22150,7 @@
         <v>32</v>
       </c>
       <c r="D1058" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E1058" s="2" t="s">
         <v>33</v>
@@ -22167,7 +22167,7 @@
         <v>32</v>
       </c>
       <c r="D1059" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E1059" s="2" t="s">
         <v>33</v>
@@ -22184,7 +22184,7 @@
         <v>32</v>
       </c>
       <c r="D1060" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E1060" s="2" t="s">
         <v>33</v>
@@ -22201,7 +22201,7 @@
         <v>32</v>
       </c>
       <c r="D1061" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1061" s="2" t="s">
         <v>33</v>
@@ -22218,7 +22218,7 @@
         <v>32</v>
       </c>
       <c r="D1062" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E1062" s="2" t="s">
         <v>33</v>
@@ -22235,7 +22235,7 @@
         <v>32</v>
       </c>
       <c r="D1063" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E1063" s="2" t="s">
         <v>33</v>
@@ -22252,7 +22252,7 @@
         <v>32</v>
       </c>
       <c r="D1064" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E1064" s="2" t="s">
         <v>33</v>
@@ -22269,7 +22269,7 @@
         <v>32</v>
       </c>
       <c r="D1065" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1065" s="2" t="s">
         <v>33</v>
@@ -22286,7 +22286,7 @@
         <v>32</v>
       </c>
       <c r="D1066" s="2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E1066" s="2" t="s">
         <v>33</v>
@@ -22303,7 +22303,7 @@
         <v>32</v>
       </c>
       <c r="D1067" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E1067" s="2" t="s">
         <v>33</v>
@@ -22337,7 +22337,7 @@
         <v>32</v>
       </c>
       <c r="D1069" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E1069" s="2" t="s">
         <v>33</v>
@@ -22354,7 +22354,7 @@
         <v>32</v>
       </c>
       <c r="D1070" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E1070" s="2" t="s">
         <v>33</v>
@@ -22388,7 +22388,7 @@
         <v>32</v>
       </c>
       <c r="D1072" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E1072" s="2" t="s">
         <v>33</v>
@@ -22405,7 +22405,7 @@
         <v>32</v>
       </c>
       <c r="D1073" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1073" s="2" t="s">
         <v>33</v>
@@ -22422,7 +22422,7 @@
         <v>32</v>
       </c>
       <c r="D1074" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E1074" s="2" t="s">
         <v>33</v>
@@ -22439,7 +22439,7 @@
         <v>32</v>
       </c>
       <c r="D1075" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1075" s="2" t="s">
         <v>33</v>
@@ -22456,7 +22456,7 @@
         <v>32</v>
       </c>
       <c r="D1076" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E1076" s="2" t="s">
         <v>33</v>
@@ -22473,7 +22473,7 @@
         <v>32</v>
       </c>
       <c r="D1077" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E1077" s="2" t="s">
         <v>33</v>
@@ -22490,7 +22490,7 @@
         <v>32</v>
       </c>
       <c r="D1078" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1078" s="2" t="s">
         <v>33</v>
@@ -22507,7 +22507,7 @@
         <v>32</v>
       </c>
       <c r="D1079" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E1079" s="2" t="s">
         <v>33</v>
@@ -22524,7 +22524,7 @@
         <v>32</v>
       </c>
       <c r="D1080" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E1080" s="2" t="s">
         <v>33</v>
@@ -22541,7 +22541,7 @@
         <v>32</v>
       </c>
       <c r="D1081" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E1081" s="2" t="s">
         <v>33</v>
@@ -22558,7 +22558,7 @@
         <v>32</v>
       </c>
       <c r="D1082" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E1082" s="2" t="s">
         <v>33</v>
@@ -22575,7 +22575,7 @@
         <v>32</v>
       </c>
       <c r="D1083" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1083" s="2" t="s">
         <v>33</v>
@@ -22592,7 +22592,7 @@
         <v>32</v>
       </c>
       <c r="D1084" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1084" s="2" t="s">
         <v>33</v>
@@ -22609,7 +22609,7 @@
         <v>32</v>
       </c>
       <c r="D1085" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E1085" s="2" t="s">
         <v>33</v>
@@ -22626,7 +22626,7 @@
         <v>32</v>
       </c>
       <c r="D1086" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E1086" s="2" t="s">
         <v>33</v>
@@ -22643,7 +22643,7 @@
         <v>32</v>
       </c>
       <c r="D1087" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E1087" s="2" t="s">
         <v>33</v>
@@ -22660,7 +22660,7 @@
         <v>32</v>
       </c>
       <c r="D1088" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E1088" s="2" t="s">
         <v>33</v>
@@ -22677,7 +22677,7 @@
         <v>32</v>
       </c>
       <c r="D1089" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E1089" s="2" t="s">
         <v>33</v>
@@ -22694,7 +22694,7 @@
         <v>32</v>
       </c>
       <c r="D1090" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E1090" s="2" t="s">
         <v>33</v>
@@ -22711,7 +22711,7 @@
         <v>32</v>
       </c>
       <c r="D1091" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1091" s="2" t="s">
         <v>33</v>
@@ -22728,7 +22728,7 @@
         <v>32</v>
       </c>
       <c r="D1092" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1092" s="2" t="s">
         <v>33</v>
@@ -22745,7 +22745,7 @@
         <v>32</v>
       </c>
       <c r="D1093" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E1093" s="2" t="s">
         <v>33</v>
@@ -22762,7 +22762,7 @@
         <v>32</v>
       </c>
       <c r="D1094" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E1094" s="2" t="s">
         <v>33</v>
@@ -22779,7 +22779,7 @@
         <v>32</v>
       </c>
       <c r="D1095" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E1095" s="2" t="s">
         <v>33</v>
@@ -22796,7 +22796,7 @@
         <v>32</v>
       </c>
       <c r="D1096" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E1096" s="2" t="s">
         <v>33</v>
@@ -22813,7 +22813,7 @@
         <v>32</v>
       </c>
       <c r="D1097" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E1097" s="2" t="s">
         <v>33</v>
@@ -22830,7 +22830,7 @@
         <v>32</v>
       </c>
       <c r="D1098" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E1098" s="2" t="s">
         <v>33</v>
@@ -22847,7 +22847,7 @@
         <v>32</v>
       </c>
       <c r="D1099" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E1099" s="2" t="s">
         <v>33</v>
@@ -22881,7 +22881,7 @@
         <v>32</v>
       </c>
       <c r="D1101" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E1101" s="2" t="s">
         <v>33</v>
@@ -22898,7 +22898,7 @@
         <v>32</v>
       </c>
       <c r="D1102" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E1102" s="2" t="s">
         <v>33</v>
@@ -22915,7 +22915,7 @@
         <v>32</v>
       </c>
       <c r="D1103" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E1103" s="2" t="s">
         <v>33</v>
@@ -22932,7 +22932,7 @@
         <v>32</v>
       </c>
       <c r="D1104" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E1104" s="2" t="s">
         <v>33</v>
@@ -22966,7 +22966,7 @@
         <v>32</v>
       </c>
       <c r="D1106" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E1106" s="2" t="s">
         <v>33</v>
@@ -22983,7 +22983,7 @@
         <v>32</v>
       </c>
       <c r="D1107" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E1107" s="2" t="s">
         <v>33</v>
@@ -23000,7 +23000,7 @@
         <v>32</v>
       </c>
       <c r="D1108" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E1108" s="2" t="s">
         <v>33</v>
@@ -23017,7 +23017,7 @@
         <v>32</v>
       </c>
       <c r="D1109" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E1109" s="2" t="s">
         <v>33</v>
@@ -23034,7 +23034,7 @@
         <v>32</v>
       </c>
       <c r="D1110" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E1110" s="2" t="s">
         <v>33</v>
@@ -23051,7 +23051,7 @@
         <v>32</v>
       </c>
       <c r="D1111" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1111" s="2" t="s">
         <v>33</v>
@@ -23068,7 +23068,7 @@
         <v>32</v>
       </c>
       <c r="D1112" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E1112" s="2" t="s">
         <v>33</v>
